--- a/MSC_skewness_lt.xlsx
+++ b/MSC_skewness_lt.xlsx
@@ -21,13 +21,13 @@
     <t>skew_lt_msc</t>
   </si>
   <si>
-    <t>skew_resid_lt_msc</t>
+    <t>skew_resid_lt_power_msc</t>
   </si>
   <si>
     <t>skew_lt_msc_ma</t>
   </si>
   <si>
-    <t>skew_resid_lt_msc_ma</t>
+    <t>skew_resid_lt_power_msc_ma</t>
   </si>
 </sst>
 </file>
@@ -75,7 +75,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E569"/>
+  <dimension ref="A1:E577"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -219,15 +219,11 @@
       <c r="B15" s="2">
         <v>0.48721683025360107</v>
       </c>
-      <c r="C15" s="2">
-        <v>0.4073021411895752</v>
-      </c>
+      <c r="C15" s="2"/>
       <c r="D15" s="2">
         <v>0.48721683025360107</v>
       </c>
-      <c r="E15" s="2">
-        <v>0.4073021411895752</v>
-      </c>
+      <c r="E15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" s="1">
@@ -335,15 +331,11 @@
       <c r="B27" s="2">
         <v>-0.79306507110595703</v>
       </c>
-      <c r="C27" s="2">
-        <v>-0.83650583028793335</v>
-      </c>
+      <c r="C27" s="2"/>
       <c r="D27" s="2">
         <v>-0.79306507110595703</v>
       </c>
-      <c r="E27" s="2">
-        <v>-0.83650583028793335</v>
-      </c>
+      <c r="E27" s="2"/>
     </row>
     <row r="28">
       <c r="A28" s="1">
@@ -397,15 +389,11 @@
       <c r="B33" s="2">
         <v>-0.22174668312072754</v>
       </c>
-      <c r="C33" s="2">
-        <v>-0.23377403616905212</v>
-      </c>
+      <c r="C33" s="2"/>
       <c r="D33" s="2">
         <v>-0.33302110433578491</v>
       </c>
-      <c r="E33" s="2">
-        <v>-0.32764306664466858</v>
-      </c>
+      <c r="E33" s="2"/>
     </row>
     <row r="34">
       <c r="A34" s="1">
@@ -414,15 +402,11 @@
       <c r="B34" s="2">
         <v>-0.44429555535316467</v>
       </c>
-      <c r="C34" s="2">
-        <v>-0.42151209712028503</v>
-      </c>
+      <c r="C34" s="2"/>
       <c r="D34" s="2">
         <v>-0.3046528697013855</v>
       </c>
-      <c r="E34" s="2">
-        <v>-0.29747381806373596</v>
-      </c>
+      <c r="E34" s="2"/>
     </row>
     <row r="35">
       <c r="A35" s="1">
@@ -458,15 +442,11 @@
       <c r="B38" s="2">
         <v>-0.24791635572910309</v>
       </c>
-      <c r="C38" s="2">
-        <v>-0.23713533580303192</v>
-      </c>
+      <c r="C38" s="2"/>
       <c r="D38" s="2">
         <v>-0.31482520699501038</v>
       </c>
-      <c r="E38" s="2">
-        <v>-0.28103885054588318</v>
-      </c>
+      <c r="E38" s="2"/>
     </row>
     <row r="39">
       <c r="A39" s="1">
@@ -475,15 +455,11 @@
       <c r="B39" s="2">
         <v>-0.15508043766021729</v>
       </c>
-      <c r="C39" s="2">
-        <v>0.0043082665652036667</v>
-      </c>
+      <c r="C39" s="2"/>
       <c r="D39" s="2">
         <v>-0.27166840434074402</v>
       </c>
-      <c r="E39" s="2">
-        <v>-0.23421443998813629</v>
-      </c>
+      <c r="E39" s="2"/>
     </row>
     <row r="40">
       <c r="A40" s="1">
@@ -492,15 +468,11 @@
       <c r="B40" s="2">
         <v>-0.41200843453407288</v>
       </c>
-      <c r="C40" s="2">
-        <v>-0.46981623768806458</v>
-      </c>
+      <c r="C40" s="2"/>
       <c r="D40" s="2">
         <v>-0.32901236414909363</v>
       </c>
-      <c r="E40" s="2">
-        <v>-0.31137335300445557</v>
-      </c>
+      <c r="E40" s="2"/>
     </row>
     <row r="41">
       <c r="A41" s="1">
@@ -536,15 +508,11 @@
       <c r="B44" s="2">
         <v>-0.50104427337646484</v>
       </c>
-      <c r="C44" s="2">
-        <v>-0.54285013675689697</v>
-      </c>
+      <c r="C44" s="2"/>
       <c r="D44" s="2">
         <v>-0.24545113742351532</v>
       </c>
-      <c r="E44" s="2">
-        <v>-0.2985624372959137</v>
-      </c>
+      <c r="E44" s="2"/>
     </row>
     <row r="45">
       <c r="A45" s="1">
@@ -553,15 +521,11 @@
       <c r="B45" s="2">
         <v>0.075489185750484467</v>
       </c>
-      <c r="C45" s="2">
-        <v>0.010060127824544907</v>
-      </c>
+      <c r="C45" s="2"/>
       <c r="D45" s="2">
         <v>-0.18993203341960907</v>
       </c>
-      <c r="E45" s="2">
-        <v>-0.2414778470993042</v>
-      </c>
+      <c r="E45" s="2"/>
     </row>
     <row r="46">
       <c r="A46" s="1">
@@ -570,15 +534,11 @@
       <c r="B46" s="2">
         <v>-0.14424102008342743</v>
       </c>
-      <c r="C46" s="2">
-        <v>-0.19164355099201202</v>
-      </c>
+      <c r="C46" s="2"/>
       <c r="D46" s="2">
         <v>-0.18249821662902832</v>
       </c>
-      <c r="E46" s="2">
-        <v>-0.23623974621295929</v>
-      </c>
+      <c r="E46" s="2"/>
     </row>
     <row r="47">
       <c r="A47" s="1">
@@ -614,15 +574,11 @@
       <c r="B50" s="2">
         <v>-0.16019675135612488</v>
       </c>
-      <c r="C50" s="2">
-        <v>-0.22052544355392456</v>
-      </c>
+      <c r="C50" s="2"/>
       <c r="D50" s="2">
         <v>-0.09411485493183136</v>
       </c>
-      <c r="E50" s="2">
-        <v>-0.13831205666065216</v>
-      </c>
+      <c r="E50" s="2"/>
     </row>
     <row r="51">
       <c r="A51" s="1">
@@ -631,15 +587,11 @@
       <c r="B51" s="2">
         <v>0.17857199907302856</v>
       </c>
-      <c r="C51" s="2">
-        <v>0.11774870753288269</v>
-      </c>
+      <c r="C51" s="2"/>
       <c r="D51" s="2">
         <v>-0.077406130731105804</v>
       </c>
-      <c r="E51" s="2">
-        <v>-0.12053489685058594</v>
-      </c>
+      <c r="E51" s="2"/>
     </row>
     <row r="52">
       <c r="A52" s="1">
@@ -648,15 +600,11 @@
       <c r="B52" s="2">
         <v>-0.2505936324596405</v>
       </c>
-      <c r="C52" s="2">
-        <v>-0.25882795453071594</v>
-      </c>
+      <c r="C52" s="2"/>
       <c r="D52" s="2">
         <v>-0.093132704496383667</v>
       </c>
-      <c r="E52" s="2">
-        <v>-0.13068999350070953</v>
-      </c>
+      <c r="E52" s="2"/>
     </row>
     <row r="53">
       <c r="A53" s="1">
@@ -692,15 +640,11 @@
       <c r="B56" s="2">
         <v>-0.14031241834163666</v>
       </c>
-      <c r="C56" s="2">
-        <v>-0.16115526854991913</v>
-      </c>
+      <c r="C56" s="2"/>
       <c r="D56" s="2">
         <v>-0.23431406915187836</v>
       </c>
-      <c r="E56" s="2">
-        <v>-0.24283106625080109</v>
-      </c>
+      <c r="E56" s="2"/>
     </row>
     <row r="57">
       <c r="A57" s="1">
@@ -709,15 +653,11 @@
       <c r="B57" s="2">
         <v>-0.11747535318136215</v>
       </c>
-      <c r="C57" s="2">
-        <v>-0.18652364611625671</v>
-      </c>
+      <c r="C57" s="2"/>
       <c r="D57" s="2">
         <v>-0.22888755798339844</v>
       </c>
-      <c r="E57" s="2">
-        <v>-0.23749877512454987</v>
-      </c>
+      <c r="E57" s="2"/>
     </row>
     <row r="58">
       <c r="A58" s="1">
@@ -726,15 +666,11 @@
       <c r="B58" s="2">
         <v>-0.42887488007545471</v>
       </c>
-      <c r="C58" s="2">
-        <v>-0.36481741070747375</v>
-      </c>
+      <c r="C58" s="2"/>
       <c r="D58" s="2">
         <v>-0.25738048553466797</v>
       </c>
-      <c r="E58" s="2">
-        <v>-0.26828578114509583</v>
-      </c>
+      <c r="E58" s="2"/>
     </row>
     <row r="59">
       <c r="A59" s="1">
@@ -770,15 +706,11 @@
       <c r="B62" s="2">
         <v>-0.34285926818847656</v>
       </c>
-      <c r="C62" s="2">
-        <v>-0.3606468141078949</v>
-      </c>
+      <c r="C62" s="2"/>
       <c r="D62" s="2">
         <v>-0.1554538905620575</v>
       </c>
-      <c r="E62" s="2">
-        <v>-0.1054404079914093</v>
-      </c>
+      <c r="E62" s="2"/>
     </row>
     <row r="63">
       <c r="A63" s="1">
@@ -787,15 +719,11 @@
       <c r="B63" s="2">
         <v>0.047747939825057983</v>
       </c>
-      <c r="C63" s="2">
-        <v>0.15900245308876038</v>
-      </c>
+      <c r="C63" s="2"/>
       <c r="D63" s="2">
         <v>-0.064313560724258423</v>
       </c>
-      <c r="E63" s="2">
-        <v>-0.018981402739882469</v>
-      </c>
+      <c r="E63" s="2"/>
     </row>
     <row r="64">
       <c r="A64" s="1">
@@ -804,15 +732,11 @@
       <c r="B64" s="2">
         <v>0.10217063874006271</v>
       </c>
-      <c r="C64" s="2">
-        <v>0.14470015466213226</v>
-      </c>
+      <c r="C64" s="2"/>
       <c r="D64" s="2">
         <v>-0.033212229609489441</v>
       </c>
-      <c r="E64" s="2">
-        <v>-0.011190880089998245</v>
-      </c>
+      <c r="E64" s="2"/>
     </row>
     <row r="65">
       <c r="A65" s="1">
@@ -848,15 +772,11 @@
       <c r="B68" s="2">
         <v>0.060091778635978699</v>
       </c>
-      <c r="C68" s="2">
-        <v>0.012180687859654427</v>
-      </c>
+      <c r="C68" s="2"/>
       <c r="D68" s="2">
         <v>0.17404548823833466</v>
       </c>
-      <c r="E68" s="2">
-        <v>0.14926931262016296</v>
-      </c>
+      <c r="E68" s="2"/>
     </row>
     <row r="69">
       <c r="A69" s="1">
@@ -865,15 +785,11 @@
       <c r="B69" s="2">
         <v>0.84347176551818848</v>
       </c>
-      <c r="C69" s="2">
-        <v>0.79569447040557861</v>
-      </c>
+      <c r="C69" s="2"/>
       <c r="D69" s="2">
         <v>0.19800376892089844</v>
       </c>
-      <c r="E69" s="2">
-        <v>0.15079236030578613</v>
-      </c>
+      <c r="E69" s="2"/>
     </row>
     <row r="70">
       <c r="A70" s="1">
@@ -882,15 +798,11 @@
       <c r="B70" s="2">
         <v>-0.30955222249031067</v>
       </c>
-      <c r="C70" s="2">
-        <v>-0.35549807548522949</v>
-      </c>
+      <c r="C70" s="2"/>
       <c r="D70" s="2">
         <v>0.247781902551651</v>
       </c>
-      <c r="E70" s="2">
-        <v>0.19468580186367035</v>
-      </c>
+      <c r="E70" s="2"/>
     </row>
     <row r="71">
       <c r="A71" s="1">
@@ -926,15 +838,11 @@
       <c r="B74" s="2">
         <v>0.3971162736415863</v>
       </c>
-      <c r="C74" s="2">
-        <v>0.326366126537323</v>
-      </c>
+      <c r="C74" s="2"/>
       <c r="D74" s="2">
         <v>0.33261632919311523</v>
       </c>
-      <c r="E74" s="2">
-        <v>0.28426381945610046</v>
-      </c>
+      <c r="E74" s="2"/>
     </row>
     <row r="75">
       <c r="A75" s="1">
@@ -943,15 +851,11 @@
       <c r="B75" s="2">
         <v>0.66018062829971313</v>
       </c>
-      <c r="C75" s="2">
-        <v>0.61486893892288208</v>
-      </c>
+      <c r="C75" s="2"/>
       <c r="D75" s="2">
         <v>0.54667246341705322</v>
       </c>
-      <c r="E75" s="2">
-        <v>0.49751779437065125</v>
-      </c>
+      <c r="E75" s="2"/>
     </row>
     <row r="76">
       <c r="A76" s="1">
@@ -960,15 +864,11 @@
       <c r="B76" s="2">
         <v>0.58272057771682739</v>
       </c>
-      <c r="C76" s="2">
-        <v>0.55131828784942627</v>
-      </c>
+      <c r="C76" s="2"/>
       <c r="D76" s="2">
         <v>0.41343611478805542</v>
       </c>
-      <c r="E76" s="2">
-        <v>0.36352059245109558</v>
-      </c>
+      <c r="E76" s="2"/>
     </row>
     <row r="77">
       <c r="A77" s="1">
@@ -1004,15 +904,11 @@
       <c r="B80" s="2">
         <v>0.013726954348385334</v>
       </c>
-      <c r="C80" s="2">
-        <v>-0.038470935076475143</v>
-      </c>
+      <c r="C80" s="2"/>
       <c r="D80" s="2">
         <v>0.60395681858062744</v>
       </c>
-      <c r="E80" s="2">
-        <v>0.5672488808631897</v>
-      </c>
+      <c r="E80" s="2"/>
     </row>
     <row r="81">
       <c r="A81" s="1">
@@ -1021,15 +917,11 @@
       <c r="B81" s="2">
         <v>0.91950523853302002</v>
       </c>
-      <c r="C81" s="2">
-        <v>0.88710570335388184</v>
-      </c>
+      <c r="C81" s="2"/>
       <c r="D81" s="2">
         <v>0.61103558540344238</v>
       </c>
-      <c r="E81" s="2">
-        <v>0.57255911827087402</v>
-      </c>
+      <c r="E81" s="2"/>
     </row>
     <row r="82">
       <c r="A82" s="1">
@@ -1038,15 +930,11 @@
       <c r="B82" s="2">
         <v>0.89987456798553467</v>
       </c>
-      <c r="C82" s="2">
-        <v>0.86904257535934448</v>
-      </c>
+      <c r="C82" s="2"/>
       <c r="D82" s="2">
         <v>0.57460242509841919</v>
       </c>
-      <c r="E82" s="2">
-        <v>0.52065658569335938</v>
-      </c>
+      <c r="E82" s="2"/>
     </row>
     <row r="83">
       <c r="A83" s="1">
@@ -1082,15 +970,11 @@
       <c r="B86" s="2">
         <v>0.46530294418334961</v>
       </c>
-      <c r="C86" s="2">
-        <v>0.36494904756546021</v>
-      </c>
+      <c r="C86" s="2"/>
       <c r="D86" s="2">
         <v>0.37695962190628052</v>
       </c>
-      <c r="E86" s="2">
-        <v>0.38106486201286316</v>
-      </c>
+      <c r="E86" s="2"/>
     </row>
     <row r="87">
       <c r="A87" s="1">
@@ -1099,15 +983,11 @@
       <c r="B87" s="2">
         <v>0.10031627863645554</v>
       </c>
-      <c r="C87" s="2">
-        <v>0.27869310975074768</v>
-      </c>
+      <c r="C87" s="2"/>
       <c r="D87" s="2">
         <v>0.202654629945755</v>
       </c>
-      <c r="E87" s="2">
-        <v>0.21840560436248779</v>
-      </c>
+      <c r="E87" s="2"/>
     </row>
     <row r="88">
       <c r="A88" s="1">
@@ -1116,15 +996,11 @@
       <c r="B88" s="2">
         <v>0.042344652116298676</v>
       </c>
-      <c r="C88" s="2">
-        <v>0.011574678122997284</v>
-      </c>
+      <c r="C88" s="2"/>
       <c r="D88" s="2">
         <v>0.32980158925056458</v>
       </c>
-      <c r="E88" s="2">
-        <v>0.32569882273674011</v>
-      </c>
+      <c r="E88" s="2"/>
     </row>
     <row r="89">
       <c r="A89" s="1">
@@ -1160,15 +1036,11 @@
       <c r="B92" s="2">
         <v>0.71124249696731567</v>
       </c>
-      <c r="C92" s="2">
-        <v>0.64757841825485229</v>
-      </c>
+      <c r="C92" s="2"/>
       <c r="D92" s="2">
         <v>0.53669047355651855</v>
       </c>
-      <c r="E92" s="2">
-        <v>0.49696403741836548</v>
-      </c>
+      <c r="E92" s="2"/>
     </row>
     <row r="93">
       <c r="A93" s="1">
@@ -1177,15 +1049,11 @@
       <c r="B93" s="2">
         <v>0.80356293916702271</v>
       </c>
-      <c r="C93" s="2">
-        <v>0.78683966398239136</v>
-      </c>
+      <c r="C93" s="2"/>
       <c r="D93" s="2">
         <v>0.70147240161895752</v>
       </c>
-      <c r="E93" s="2">
-        <v>0.65876048803329468</v>
-      </c>
+      <c r="E93" s="2"/>
     </row>
     <row r="94">
       <c r="A94" s="1">
@@ -1194,15 +1062,11 @@
       <c r="B94" s="2">
         <v>0.58961182832717896</v>
       </c>
-      <c r="C94" s="2">
-        <v>0.54186344146728516</v>
-      </c>
+      <c r="C94" s="2"/>
       <c r="D94" s="2">
         <v>0.70147240161895752</v>
       </c>
-      <c r="E94" s="2">
-        <v>0.65876048803329468</v>
-      </c>
+      <c r="E94" s="2"/>
     </row>
     <row r="95">
       <c r="A95" s="1">
@@ -1256,15 +1120,11 @@
       <c r="B100" s="2">
         <v>0.14898569881916046</v>
       </c>
-      <c r="C100" s="2">
-        <v>0.63549858331680298</v>
-      </c>
+      <c r="C100" s="2"/>
       <c r="D100" s="2">
         <v>0.73300236463546753</v>
       </c>
-      <c r="E100" s="2">
-        <v>1.1129164695739746</v>
-      </c>
+      <c r="E100" s="2"/>
     </row>
     <row r="101">
       <c r="A101" s="1">
@@ -1291,15 +1151,11 @@
       <c r="B103" s="2">
         <v>1.317018985748291</v>
       </c>
-      <c r="C103" s="2">
-        <v>1.590334415435791</v>
-      </c>
+      <c r="C103" s="2"/>
       <c r="D103" s="2">
         <v>0.93625760078430176</v>
       </c>
-      <c r="E103" s="2">
-        <v>1.1739858388900757</v>
-      </c>
+      <c r="E103" s="2"/>
     </row>
     <row r="104">
       <c r="A104" s="1">
@@ -1326,15 +1182,11 @@
       <c r="B106" s="2">
         <v>1.3427680730819702</v>
       </c>
-      <c r="C106" s="2">
-        <v>1.2961245775222778</v>
-      </c>
+      <c r="C106" s="2"/>
       <c r="D106" s="2">
         <v>1.0980263948440552</v>
       </c>
-      <c r="E106" s="2">
-        <v>1.1929287910461426</v>
-      </c>
+      <c r="E106" s="2"/>
     </row>
     <row r="107">
       <c r="A107" s="1">
@@ -1361,15 +1213,11 @@
       <c r="B109" s="2">
         <v>0.63429200649261475</v>
       </c>
-      <c r="C109" s="2">
-        <v>0.69232732057571411</v>
-      </c>
+      <c r="C109" s="2"/>
       <c r="D109" s="2">
         <v>0.90486323833465576</v>
       </c>
-      <c r="E109" s="2">
-        <v>0.94614744186401367</v>
-      </c>
+      <c r="E109" s="2"/>
     </row>
     <row r="110">
       <c r="A110" s="1">
@@ -1396,15 +1244,11 @@
       <c r="B112" s="2">
         <v>0.7375296950340271</v>
       </c>
-      <c r="C112" s="2">
-        <v>0.8499903678894043</v>
-      </c>
+      <c r="C112" s="2"/>
       <c r="D112" s="2">
         <v>0.62356847524642944</v>
       </c>
-      <c r="E112" s="2">
-        <v>0.64742404222488403</v>
-      </c>
+      <c r="E112" s="2"/>
     </row>
     <row r="113">
       <c r="A113" s="1">
@@ -1431,15 +1275,11 @@
       <c r="B115" s="2">
         <v>0.49888375401496887</v>
       </c>
-      <c r="C115" s="2">
-        <v>0.39995446801185608</v>
-      </c>
+      <c r="C115" s="2"/>
       <c r="D115" s="2">
         <v>0.71733814477920532</v>
       </c>
-      <c r="E115" s="2">
-        <v>0.6836235523223877</v>
-      </c>
+      <c r="E115" s="2"/>
     </row>
     <row r="116">
       <c r="A116" s="1">
@@ -1466,15 +1306,11 @@
       <c r="B118" s="2">
         <v>0.91560101509094238</v>
       </c>
-      <c r="C118" s="2">
-        <v>0.80092591047286987</v>
-      </c>
+      <c r="C118" s="2"/>
       <c r="D118" s="2">
         <v>0.12220177054405212</v>
       </c>
-      <c r="E118" s="2">
-        <v>-0.0081436336040496826</v>
-      </c>
+      <c r="E118" s="2"/>
     </row>
     <row r="119">
       <c r="A119" s="1">
@@ -1501,15 +1337,11 @@
       <c r="B121" s="2">
         <v>-1.0478794574737549</v>
       </c>
-      <c r="C121" s="2">
-        <v>-1.225311279296875</v>
-      </c>
+      <c r="C121" s="2"/>
       <c r="D121" s="2">
         <v>-0.06613922119140625</v>
       </c>
-      <c r="E121" s="2">
-        <v>-0.21219268441200256</v>
-      </c>
+      <c r="E121" s="2"/>
     </row>
     <row r="122">
       <c r="A122" s="1">
@@ -1761,15 +1593,11 @@
       <c r="B149" s="2">
         <v>0.57158887386322021</v>
       </c>
-      <c r="C149" s="2">
-        <v>0.48275718092918396</v>
-      </c>
+      <c r="C149" s="2"/>
       <c r="D149" s="2">
         <v>0.91426771879196167</v>
       </c>
-      <c r="E149" s="2">
-        <v>0.83547013998031616</v>
-      </c>
+      <c r="E149" s="2"/>
     </row>
     <row r="150">
       <c r="A150" s="1">
@@ -1778,15 +1606,11 @@
       <c r="B150" s="2">
         <v>0.36666730046272278</v>
       </c>
-      <c r="C150" s="2">
-        <v>0.24994364380836487</v>
-      </c>
+      <c r="C150" s="2"/>
       <c r="D150" s="2">
         <v>0.96478313207626343</v>
       </c>
-      <c r="E150" s="2">
-        <v>0.87963038682937622</v>
-      </c>
+      <c r="E150" s="2"/>
     </row>
     <row r="151">
       <c r="A151" s="1">
@@ -1795,15 +1619,11 @@
       <c r="B151" s="2">
         <v>1.2443603277206421</v>
       </c>
-      <c r="C151" s="2">
-        <v>1.1911708116531372</v>
-      </c>
+      <c r="C151" s="2"/>
       <c r="D151" s="2">
         <v>1.0068825483322144</v>
       </c>
-      <c r="E151" s="2">
-        <v>0.90947556495666504</v>
-      </c>
+      <c r="E151" s="2"/>
     </row>
     <row r="152">
       <c r="A152" s="1">
@@ -1812,15 +1632,11 @@
       <c r="B152" s="2">
         <v>1.0197614431381226</v>
       </c>
-      <c r="C152" s="2">
-        <v>0.9260445237159729</v>
-      </c>
+      <c r="C152" s="2"/>
       <c r="D152" s="2">
         <v>0.95357203483581543</v>
       </c>
-      <c r="E152" s="2">
-        <v>0.83888870477676392</v>
-      </c>
+      <c r="E152" s="2"/>
     </row>
     <row r="153">
       <c r="A153" s="1">
@@ -1829,15 +1645,11 @@
       <c r="B153" s="2">
         <v>1.3689607381820679</v>
       </c>
-      <c r="C153" s="2">
-        <v>1.3274345397949219</v>
-      </c>
+      <c r="C153" s="2"/>
       <c r="D153" s="2">
         <v>0.91129863262176514</v>
       </c>
-      <c r="E153" s="2">
-        <v>0.80744433403015137</v>
-      </c>
+      <c r="E153" s="2"/>
     </row>
     <row r="154">
       <c r="A154" s="1">
@@ -1846,15 +1658,11 @@
       <c r="B154" s="2">
         <v>1.217360258102417</v>
       </c>
-      <c r="C154" s="2">
-        <v>1.1004315614700317</v>
-      </c>
+      <c r="C154" s="2"/>
       <c r="D154" s="2">
         <v>0.79970943927764893</v>
       </c>
-      <c r="E154" s="2">
-        <v>0.76240205764770508</v>
-      </c>
+      <c r="E154" s="2"/>
     </row>
     <row r="155">
       <c r="A155" s="1">
@@ -1863,15 +1671,11 @@
       <c r="B155" s="2">
         <v>1.2594789266586304</v>
       </c>
-      <c r="C155" s="2">
-        <v>1.0885467529296875</v>
-      </c>
+      <c r="C155" s="2"/>
       <c r="D155" s="2">
         <v>0.81263875961303711</v>
       </c>
-      <c r="E155" s="2">
-        <v>0.78032475709915161</v>
-      </c>
+      <c r="E155" s="2"/>
     </row>
     <row r="156">
       <c r="A156" s="1">
@@ -1880,15 +1684,11 @@
       <c r="B156" s="2">
         <v>0.58039820194244385</v>
       </c>
-      <c r="C156" s="2">
-        <v>0.3447805643081665</v>
-      </c>
+      <c r="C156" s="2"/>
       <c r="D156" s="2">
         <v>0.83177149295806885</v>
       </c>
-      <c r="E156" s="2">
-        <v>0.79776173830032349</v>
-      </c>
+      <c r="E156" s="2"/>
     </row>
     <row r="157">
       <c r="A157" s="1">
@@ -1897,15 +1697,11 @@
       <c r="B157" s="2">
         <v>0.57311147451400757</v>
       </c>
-      <c r="C157" s="2">
-        <v>0.55588918924331665</v>
-      </c>
+      <c r="C157" s="2"/>
       <c r="D157" s="2">
         <v>0.87028408050537109</v>
       </c>
-      <c r="E157" s="2">
-        <v>0.84344768524169922</v>
-      </c>
+      <c r="E157" s="2"/>
     </row>
     <row r="158">
       <c r="A158" s="1">
@@ -1914,15 +1710,11 @@
       <c r="B158" s="2">
         <v>-0.43271350860595703</v>
       </c>
-      <c r="C158" s="2">
-        <v>0.077377043664455414</v>
-      </c>
+      <c r="C158" s="2"/>
       <c r="D158" s="2">
         <v>0.81277155876159668</v>
       </c>
-      <c r="E158" s="2">
-        <v>0.77521538734436035</v>
-      </c>
+      <c r="E158" s="2"/>
     </row>
     <row r="159">
       <c r="A159" s="1">
@@ -1931,15 +1723,11 @@
       <c r="B159" s="2">
         <v>0.483030766248703</v>
       </c>
-      <c r="C159" s="2">
-        <v>0.41124773025512695</v>
-      </c>
+      <c r="C159" s="2"/>
       <c r="D159" s="2">
-        <v>0.85266071557998657</v>
-      </c>
-      <c r="E159" s="2">
-        <v>0.81297886371612549</v>
-      </c>
+        <v>0.85333257913589478</v>
+      </c>
+      <c r="E159" s="2"/>
     </row>
     <row r="160">
       <c r="A160" s="1">
@@ -1948,15 +1736,11 @@
       <c r="B160" s="2">
         <v>1.4165554046630859</v>
       </c>
-      <c r="C160" s="2">
-        <v>1.3481035232543945</v>
-      </c>
+      <c r="C160" s="2"/>
       <c r="D160" s="2">
-        <v>0.84335935115814209</v>
-      </c>
-      <c r="E160" s="2">
-        <v>0.80308091640472412</v>
-      </c>
+        <v>0.84403127431869507</v>
+      </c>
+      <c r="E160" s="2"/>
     </row>
     <row r="161">
       <c r="A161" s="1">
@@ -1965,15 +1749,11 @@
       <c r="B161" s="2">
         <v>1.3663743734359741</v>
       </c>
-      <c r="C161" s="2">
-        <v>1.3372185230255127</v>
-      </c>
+      <c r="C161" s="2"/>
       <c r="D161" s="2">
-        <v>0.86715131998062134</v>
-      </c>
-      <c r="E161" s="2">
-        <v>0.85659575462341309</v>
-      </c>
+        <v>0.86782318353652954</v>
+      </c>
+      <c r="E161" s="2"/>
     </row>
     <row r="162">
       <c r="A162" s="1">
@@ -1982,32 +1762,24 @@
       <c r="B162" s="2">
         <v>0.85134798288345337</v>
       </c>
-      <c r="C162" s="2">
-        <v>0.71334338188171387</v>
-      </c>
+      <c r="C162" s="2"/>
       <c r="D162" s="2">
-        <v>0.69092398881912231</v>
-      </c>
-      <c r="E162" s="2">
-        <v>0.63568133115768433</v>
-      </c>
+        <v>0.69159585237503052</v>
+      </c>
+      <c r="E162" s="2"/>
     </row>
     <row r="163">
       <c r="A163" s="1">
         <v>33390</v>
       </c>
       <c r="B163" s="2">
-        <v>1.5763626098632812</v>
-      </c>
-      <c r="C163" s="2">
-        <v>1.4403032064437866</v>
-      </c>
+        <v>1.5824096202850342</v>
+      </c>
+      <c r="C163" s="2"/>
       <c r="D163" s="2">
-        <v>0.89624702930450439</v>
-      </c>
-      <c r="E163" s="2">
-        <v>0.79531025886535645</v>
-      </c>
+        <v>0.89691895246505737</v>
+      </c>
+      <c r="E163" s="2"/>
     </row>
     <row r="164">
       <c r="A164" s="1">
@@ -2016,15 +1788,11 @@
       <c r="B164" s="2">
         <v>1.1757670640945435</v>
       </c>
-      <c r="C164" s="2">
-        <v>0.99946486949920654</v>
-      </c>
+      <c r="C164" s="2"/>
       <c r="D164" s="2">
-        <v>0.92782658338546753</v>
-      </c>
-      <c r="E164" s="2">
-        <v>0.88855165243148804</v>
-      </c>
+        <v>0.92849844694137573</v>
+      </c>
+      <c r="E164" s="2"/>
     </row>
     <row r="165">
       <c r="A165" s="1">
@@ -2033,15 +1801,11 @@
       <c r="B165" s="2">
         <v>0.7945256233215332</v>
       </c>
-      <c r="C165" s="2">
-        <v>0.82641428709030151</v>
-      </c>
+      <c r="C165" s="2"/>
       <c r="D165" s="2">
-        <v>0.84742128849029541</v>
-      </c>
-      <c r="E165" s="2">
-        <v>0.81443405151367188</v>
-      </c>
+        <v>0.84809315204620361</v>
+      </c>
+      <c r="E165" s="2"/>
     </row>
     <row r="166">
       <c r="A166" s="1">
@@ -2050,15 +1814,11 @@
       <c r="B166" s="2">
         <v>-1.0129344463348389</v>
       </c>
-      <c r="C166" s="2">
-        <v>-1.4323407411575317</v>
-      </c>
+      <c r="C166" s="2"/>
       <c r="D166" s="2">
-        <v>0.85329848527908325</v>
-      </c>
-      <c r="E166" s="2">
-        <v>0.82043790817260742</v>
-      </c>
+        <v>0.85397040843963623</v>
+      </c>
+      <c r="E166" s="2"/>
     </row>
     <row r="167">
       <c r="A167" s="1">
@@ -2067,15 +1827,11 @@
       <c r="B167" s="2">
         <v>1.4151941537857056</v>
       </c>
-      <c r="C167" s="2">
-        <v>1.5140373706817627</v>
-      </c>
+      <c r="C167" s="2"/>
       <c r="D167" s="2">
-        <v>0.86927485466003418</v>
-      </c>
-      <c r="E167" s="2">
-        <v>0.84130316972732544</v>
-      </c>
+        <v>0.86994677782058716</v>
+      </c>
+      <c r="E167" s="2"/>
     </row>
     <row r="168">
       <c r="A168" s="1">
@@ -2084,15 +1840,11 @@
       <c r="B168" s="2">
         <v>0.76724648475646973</v>
       </c>
-      <c r="C168" s="2">
-        <v>1.2504206895828247</v>
-      </c>
+      <c r="C168" s="2"/>
       <c r="D168" s="2">
         <v>0.62240105867385864</v>
       </c>
-      <c r="E168" s="2">
-        <v>0.58392012119293213</v>
-      </c>
+      <c r="E168" s="2"/>
     </row>
     <row r="169">
       <c r="A169" s="1">
@@ -2101,15 +1853,11 @@
       <c r="B169" s="2">
         <v>0.69290751218795776</v>
       </c>
-      <c r="C169" s="2">
-        <v>0.68104469776153564</v>
-      </c>
+      <c r="C169" s="2"/>
       <c r="D169" s="2">
         <v>0.48370081186294556</v>
       </c>
-      <c r="E169" s="2">
-        <v>0.47855275869369507</v>
-      </c>
+      <c r="E169" s="2"/>
     </row>
     <row r="170">
       <c r="A170" s="1">
@@ -2118,15 +1866,11 @@
       <c r="B170" s="2">
         <v>1.4192695617675781</v>
       </c>
-      <c r="C170" s="2">
-        <v>1.3912534713745117</v>
-      </c>
+      <c r="C170" s="2"/>
       <c r="D170" s="2">
         <v>0.53009539842605591</v>
       </c>
-      <c r="E170" s="2">
-        <v>0.52829587459564209</v>
-      </c>
+      <c r="E170" s="2"/>
     </row>
     <row r="171">
       <c r="A171" s="1">
@@ -2135,15 +1879,11 @@
       <c r="B171" s="2">
         <v>0.99513536691665649</v>
       </c>
-      <c r="C171" s="2">
-        <v>0.90113049745559692</v>
-      </c>
+      <c r="C171" s="2"/>
       <c r="D171" s="2">
         <v>0.70197927951812744</v>
       </c>
-      <c r="E171" s="2">
-        <v>0.74976509809494019</v>
-      </c>
+      <c r="E171" s="2"/>
     </row>
     <row r="172">
       <c r="A172" s="1">
@@ -2152,15 +1892,11 @@
       <c r="B172" s="2">
         <v>-0.64550179243087769</v>
       </c>
-      <c r="C172" s="2">
-        <v>-0.87614411115646362</v>
-      </c>
+      <c r="C172" s="2"/>
       <c r="D172" s="2">
         <v>0.57080817222595215</v>
       </c>
-      <c r="E172" s="2">
-        <v>0.59232300519943237</v>
-      </c>
+      <c r="E172" s="2"/>
     </row>
     <row r="173">
       <c r="A173" s="1">
@@ -2169,15 +1905,11 @@
       <c r="B173" s="2">
         <v>-0.072535261511802673</v>
       </c>
-      <c r="C173" s="2">
-        <v>0.051158685237169266</v>
-      </c>
+      <c r="C173" s="2"/>
       <c r="D173" s="2">
         <v>0.37555095553398132</v>
       </c>
-      <c r="E173" s="2">
-        <v>0.32264208793640137</v>
-      </c>
+      <c r="E173" s="2"/>
     </row>
     <row r="174">
       <c r="A174" s="1">
@@ -2186,15 +1918,11 @@
       <c r="B174" s="2">
         <v>1.2120770215988159</v>
       </c>
-      <c r="C174" s="2">
-        <v>1.2741022109985352</v>
-      </c>
+      <c r="C174" s="2"/>
       <c r="D174" s="2">
         <v>0.45036458969116211</v>
       </c>
-      <c r="E174" s="2">
-        <v>0.40962055325508118</v>
-      </c>
+      <c r="E174" s="2"/>
     </row>
     <row r="175">
       <c r="A175" s="1">
@@ -2203,15 +1931,11 @@
       <c r="B175" s="2">
         <v>0.53402048349380493</v>
       </c>
-      <c r="C175" s="2">
-        <v>0.56088221073150635</v>
-      </c>
+      <c r="C175" s="2"/>
       <c r="D175" s="2">
         <v>0.43029242753982544</v>
       </c>
-      <c r="E175" s="2">
-        <v>0.39104968309402466</v>
-      </c>
+      <c r="E175" s="2"/>
     </row>
     <row r="176">
       <c r="A176" s="1">
@@ -2220,15 +1944,11 @@
       <c r="B176" s="2">
         <v>0.23465435206890106</v>
       </c>
-      <c r="C176" s="2">
-        <v>0.097058936953544617</v>
-      </c>
+      <c r="C176" s="2"/>
       <c r="D176" s="2">
         <v>0.40371787548065186</v>
       </c>
-      <c r="E176" s="2">
-        <v>0.39530947804450989</v>
-      </c>
+      <c r="E176" s="2"/>
     </row>
     <row r="177">
       <c r="A177" s="1">
@@ -2237,15 +1957,11 @@
       <c r="B177" s="2">
         <v>-0.99006873369216919</v>
       </c>
-      <c r="C177" s="2">
-        <v>-1.1767077445983887</v>
-      </c>
+      <c r="C177" s="2"/>
       <c r="D177" s="2">
         <v>0.62233668565750122</v>
       </c>
-      <c r="E177" s="2">
-        <v>0.62740498781204224</v>
-      </c>
+      <c r="E177" s="2"/>
     </row>
     <row r="178">
       <c r="A178" s="1">
@@ -2254,15 +1970,11 @@
       <c r="B178" s="2">
         <v>1.3662302494049072</v>
       </c>
-      <c r="C178" s="2">
-        <v>1.4638508558273315</v>
-      </c>
+      <c r="C178" s="2"/>
       <c r="D178" s="2">
         <v>0.51801615953445435</v>
       </c>
-      <c r="E178" s="2">
-        <v>0.55955284833908081</v>
-      </c>
+      <c r="E178" s="2"/>
     </row>
     <row r="179">
       <c r="A179" s="1">
@@ -2271,15 +1983,11 @@
       <c r="B179" s="2">
         <v>1.2386200428009033</v>
       </c>
-      <c r="C179" s="2">
-        <v>1.2241154909133911</v>
-      </c>
+      <c r="C179" s="2"/>
       <c r="D179" s="2">
         <v>0.4819599986076355</v>
       </c>
-      <c r="E179" s="2">
-        <v>0.50443834066390991</v>
-      </c>
+      <c r="E179" s="2"/>
     </row>
     <row r="180">
       <c r="A180" s="1">
@@ -2288,15 +1996,11 @@
       <c r="B180" s="2">
         <v>0.75596463680267334</v>
       </c>
-      <c r="C180" s="2">
-        <v>0.9394688606262207</v>
-      </c>
+      <c r="C180" s="2"/>
       <c r="D180" s="2">
         <v>0.54198992252349854</v>
       </c>
-      <c r="E180" s="2">
-        <v>0.54846203327178955</v>
-      </c>
+      <c r="E180" s="2"/>
     </row>
     <row r="181">
       <c r="A181" s="1">
@@ -2305,15 +2009,11 @@
       <c r="B181" s="2">
         <v>1.3220672607421875</v>
       </c>
-      <c r="C181" s="2">
-        <v>1.2127153873443604</v>
-      </c>
+      <c r="C181" s="2"/>
       <c r="D181" s="2">
         <v>0.63616341352462769</v>
       </c>
-      <c r="E181" s="2">
-        <v>0.6328737735748291</v>
-      </c>
+      <c r="E181" s="2"/>
     </row>
     <row r="182">
       <c r="A182" s="1">
@@ -2322,15 +2022,11 @@
       <c r="B182" s="2">
         <v>-1.0114201307296753</v>
       </c>
-      <c r="C182" s="2">
-        <v>-0.55951046943664551</v>
-      </c>
+      <c r="C182" s="2"/>
       <c r="D182" s="2">
         <v>0.80832242965698242</v>
       </c>
-      <c r="E182" s="2">
-        <v>0.81642830371856689</v>
-      </c>
+      <c r="E182" s="2"/>
     </row>
     <row r="183">
       <c r="A183" s="1">
@@ -2339,15 +2035,11 @@
       <c r="B183" s="2">
         <v>0.88757175207138062</v>
       </c>
-      <c r="C183" s="2">
-        <v>0.77807164192199707</v>
-      </c>
+      <c r="C183" s="2"/>
       <c r="D183" s="2">
         <v>0.816234290599823</v>
       </c>
-      <c r="E183" s="2">
-        <v>0.80411642789840698</v>
-      </c>
+      <c r="E183" s="2"/>
     </row>
     <row r="184">
       <c r="A184" s="1">
@@ -2356,15 +2048,11 @@
       <c r="B184" s="2">
         <v>1.0742899179458618</v>
       </c>
-      <c r="C184" s="2">
-        <v>0.95709550380706787</v>
-      </c>
+      <c r="C184" s="2"/>
       <c r="D184" s="2">
         <v>0.84180420637130737</v>
       </c>
-      <c r="E184" s="2">
-        <v>0.78713023662567139</v>
-      </c>
+      <c r="E184" s="2"/>
     </row>
     <row r="185">
       <c r="A185" s="1">
@@ -2373,15 +2061,11 @@
       <c r="B185" s="2">
         <v>1.0822157859802246</v>
       </c>
-      <c r="C185" s="2">
-        <v>0.85676449537277222</v>
-      </c>
+      <c r="C185" s="2"/>
       <c r="D185" s="2">
         <v>0.84736055135726929</v>
       </c>
-      <c r="E185" s="2">
-        <v>0.7402006983757019</v>
-      </c>
+      <c r="E185" s="2"/>
     </row>
     <row r="186">
       <c r="A186" s="1">
@@ -2390,15 +2074,11 @@
       <c r="B186" s="2">
         <v>0.55936235189437866</v>
       </c>
-      <c r="C186" s="2">
-        <v>0.4752826988697052</v>
-      </c>
+      <c r="C186" s="2"/>
       <c r="D186" s="2">
         <v>0.67459487915039062</v>
       </c>
-      <c r="E186" s="2">
-        <v>0.55063700675964355</v>
-      </c>
+      <c r="E186" s="2"/>
     </row>
     <row r="187">
       <c r="A187" s="1">
@@ -2407,15 +2087,11 @@
       <c r="B187" s="2">
         <v>1.4374370574951172</v>
       </c>
-      <c r="C187" s="2">
-        <v>1.3530443906784058</v>
-      </c>
+      <c r="C187" s="2"/>
       <c r="D187" s="2">
         <v>0.89979094266891479</v>
       </c>
-      <c r="E187" s="2">
-        <v>0.75116771459579468</v>
-      </c>
+      <c r="E187" s="2"/>
     </row>
     <row r="188">
       <c r="A188" s="1">
@@ -2424,15 +2100,11 @@
       <c r="B188" s="2">
         <v>1.4687491655349731</v>
       </c>
-      <c r="C188" s="2">
-        <v>1.0712393522262573</v>
-      </c>
+      <c r="C188" s="2"/>
       <c r="D188" s="2">
         <v>0.8301655650138855</v>
       </c>
-      <c r="E188" s="2">
-        <v>0.69207775592803955</v>
-      </c>
+      <c r="E188" s="2"/>
     </row>
     <row r="189">
       <c r="A189" s="1">
@@ -2441,15 +2113,11 @@
       <c r="B189" s="2">
         <v>0.80597198009490967</v>
       </c>
-      <c r="C189" s="2">
-        <v>0.51710325479507446</v>
-      </c>
+      <c r="C189" s="2"/>
       <c r="D189" s="2">
         <v>0.81257057189941406</v>
       </c>
-      <c r="E189" s="2">
-        <v>0.66863620281219482</v>
-      </c>
+      <c r="E189" s="2"/>
     </row>
     <row r="190">
       <c r="A190" s="1">
@@ -2458,15 +2126,11 @@
       <c r="B190" s="2">
         <v>-0.23282408714294434</v>
       </c>
-      <c r="C190" s="2">
-        <v>-0.49335792660713196</v>
-      </c>
+      <c r="C190" s="2"/>
       <c r="D190" s="2">
         <v>0.77534443140029907</v>
       </c>
-      <c r="E190" s="2">
-        <v>0.63134902715682983</v>
-      </c>
+      <c r="E190" s="2"/>
     </row>
     <row r="191">
       <c r="A191" s="1">
@@ -2475,15 +2139,11 @@
       <c r="B191" s="2">
         <v>1.0153443813323975</v>
       </c>
-      <c r="C191" s="2">
-        <v>1.2452661991119385</v>
-      </c>
+      <c r="C191" s="2"/>
       <c r="D191" s="2">
         <v>0.84406983852386475</v>
       </c>
-      <c r="E191" s="2">
-        <v>0.70147055387496948</v>
-      </c>
+      <c r="E191" s="2"/>
     </row>
     <row r="192">
       <c r="A192" s="1">
@@ -2492,15 +2152,11 @@
       <c r="B192" s="2">
         <v>0.26094359159469604</v>
       </c>
-      <c r="C192" s="2">
-        <v>0.24626190960407257</v>
-      </c>
+      <c r="C192" s="2"/>
       <c r="D192" s="2">
         <v>0.5906711220741272</v>
       </c>
-      <c r="E192" s="2">
-        <v>0.39087620377540588</v>
-      </c>
+      <c r="E192" s="2"/>
     </row>
     <row r="193">
       <c r="A193" s="1">
@@ -2509,15 +2165,11 @@
       <c r="B193" s="2">
         <v>0.91593480110168457</v>
       </c>
-      <c r="C193" s="2">
-        <v>0.74612164497375488</v>
-      </c>
+      <c r="C193" s="2"/>
       <c r="D193" s="2">
         <v>0.64727354049682617</v>
       </c>
-      <c r="E193" s="2">
-        <v>0.46264442801475525</v>
-      </c>
+      <c r="E193" s="2"/>
     </row>
     <row r="194">
       <c r="A194" s="1">
@@ -2526,15 +2178,11 @@
       <c r="B194" s="2">
         <v>0.74718040227890015</v>
       </c>
-      <c r="C194" s="2">
-        <v>0.52117979526519775</v>
-      </c>
+      <c r="C194" s="2"/>
       <c r="D194" s="2">
         <v>0.68223839998245239</v>
       </c>
-      <c r="E194" s="2">
-        <v>0.49409797787666321</v>
-      </c>
+      <c r="E194" s="2"/>
     </row>
     <row r="195">
       <c r="A195" s="1">
@@ -2543,15 +2191,11 @@
       <c r="B195" s="2">
         <v>1.1778914928436279</v>
       </c>
-      <c r="C195" s="2">
-        <v>1.1063761711120605</v>
-      </c>
+      <c r="C195" s="2"/>
       <c r="D195" s="2">
         <v>0.84369057416915894</v>
       </c>
-      <c r="E195" s="2">
-        <v>0.6756662130355835</v>
-      </c>
+      <c r="E195" s="2"/>
     </row>
     <row r="196">
       <c r="A196" s="1">
@@ -2560,15 +2204,11 @@
       <c r="B196" s="2">
         <v>-0.84315186738967896</v>
       </c>
-      <c r="C196" s="2">
-        <v>-1.4423044919967651</v>
-      </c>
+      <c r="C196" s="2"/>
       <c r="D196" s="2">
         <v>0.8668481707572937</v>
       </c>
-      <c r="E196" s="2">
-        <v>0.6596333384513855</v>
-      </c>
+      <c r="E196" s="2"/>
     </row>
     <row r="197">
       <c r="A197" s="1">
@@ -2577,15 +2217,11 @@
       <c r="B197" s="2">
         <v>1.9781713485717773</v>
       </c>
-      <c r="C197" s="2">
-        <v>1.7171533107757568</v>
-      </c>
+      <c r="C197" s="2"/>
       <c r="D197" s="2">
         <v>1.02826988697052</v>
       </c>
-      <c r="E197" s="2">
-        <v>0.81713682413101196</v>
-      </c>
+      <c r="E197" s="2"/>
     </row>
     <row r="198">
       <c r="A198" s="1">
@@ -2594,15 +2230,11 @@
       <c r="B198" s="2">
         <v>1.1206554174423218</v>
       </c>
-      <c r="C198" s="2">
-        <v>0.80018508434295654</v>
-      </c>
+      <c r="C198" s="2"/>
       <c r="D198" s="2">
         <v>1.0359407663345337</v>
       </c>
-      <c r="E198" s="2">
-        <v>0.87555795907974243</v>
-      </c>
+      <c r="E198" s="2"/>
     </row>
     <row r="199">
       <c r="A199" s="1">
@@ -2611,15 +2243,11 @@
       <c r="B199" s="2">
         <v>1.2202457189559937</v>
       </c>
-      <c r="C199" s="2">
-        <v>1.140756368637085</v>
-      </c>
+      <c r="C199" s="2"/>
       <c r="D199" s="2">
         <v>1.1254415512084961</v>
       </c>
-      <c r="E199" s="2">
-        <v>0.98728460073471069</v>
-      </c>
+      <c r="E199" s="2"/>
     </row>
     <row r="200">
       <c r="A200" s="1">
@@ -2628,15 +2256,11 @@
       <c r="B200" s="2">
         <v>1.2237625122070312</v>
       </c>
-      <c r="C200" s="2">
-        <v>1.1009703874588013</v>
-      </c>
+      <c r="C200" s="2"/>
       <c r="D200" s="2">
         <v>1.1177159547805786</v>
       </c>
-      <c r="E200" s="2">
-        <v>0.97175747156143188</v>
-      </c>
+      <c r="E200" s="2"/>
     </row>
     <row r="201">
       <c r="A201" s="1">
@@ -2645,15 +2269,11 @@
       <c r="B201" s="2">
         <v>1.713739275932312</v>
       </c>
-      <c r="C201" s="2">
-        <v>1.6637932062149048</v>
-      </c>
+      <c r="C201" s="2"/>
       <c r="D201" s="2">
         <v>1.3274825811386108</v>
       </c>
-      <c r="E201" s="2">
-        <v>1.240725040435791</v>
-      </c>
+      <c r="E201" s="2"/>
     </row>
     <row r="202">
       <c r="A202" s="1">
@@ -2662,15 +2282,11 @@
       <c r="B202" s="2">
         <v>0.98497289419174194</v>
       </c>
-      <c r="C202" s="2">
-        <v>1.27191162109375</v>
-      </c>
+      <c r="C202" s="2"/>
       <c r="D202" s="2">
         <v>1.3351821899414062</v>
       </c>
-      <c r="E202" s="2">
-        <v>1.2628005743026733</v>
-      </c>
+      <c r="E202" s="2"/>
     </row>
     <row r="203">
       <c r="A203" s="1">
@@ -2679,15 +2295,11 @@
       <c r="B203" s="2">
         <v>1.5526868104934692</v>
       </c>
-      <c r="C203" s="2">
-        <v>1.5267195701599121</v>
-      </c>
+      <c r="C203" s="2"/>
       <c r="D203" s="2">
         <v>1.3364373445510864</v>
       </c>
-      <c r="E203" s="2">
-        <v>1.2703970670700073</v>
-      </c>
+      <c r="E203" s="2"/>
     </row>
     <row r="204">
       <c r="A204" s="1">
@@ -2696,15 +2308,11 @@
       <c r="B204" s="2">
         <v>1.1083613634109497</v>
       </c>
-      <c r="C204" s="2">
-        <v>0.96663200855255127</v>
-      </c>
+      <c r="C204" s="2"/>
       <c r="D204" s="2">
         <v>1.2379546165466309</v>
       </c>
-      <c r="E204" s="2">
-        <v>1.13463294506073</v>
-      </c>
+      <c r="E204" s="2"/>
     </row>
     <row r="205">
       <c r="A205" s="1">
@@ -2713,15 +2321,11 @@
       <c r="B205" s="2">
         <v>1.0447477102279663</v>
       </c>
-      <c r="C205" s="2">
-        <v>0.97840368747711182</v>
-      </c>
+      <c r="C205" s="2"/>
       <c r="D205" s="2">
         <v>1.2841290235519409</v>
       </c>
-      <c r="E205" s="2">
-        <v>1.1829663515090942</v>
-      </c>
+      <c r="E205" s="2"/>
     </row>
     <row r="206">
       <c r="A206" s="1">
@@ -2730,15 +2334,11 @@
       <c r="B206" s="2">
         <v>2.0474674701690674</v>
       </c>
-      <c r="C206" s="2">
-        <v>1.9158334732055664</v>
-      </c>
+      <c r="C206" s="2"/>
       <c r="D206" s="2">
         <v>1.1597045660018921</v>
       </c>
-      <c r="E206" s="2">
-        <v>1.0527429580688477</v>
-      </c>
+      <c r="E206" s="2"/>
     </row>
     <row r="207">
       <c r="A207" s="1">
@@ -2747,15 +2347,11 @@
       <c r="B207" s="2">
         <v>1.1319519281387329</v>
       </c>
-      <c r="C207" s="2">
-        <v>0.8685535192489624</v>
-      </c>
+      <c r="C207" s="2"/>
       <c r="D207" s="2">
         <v>1.2399861812591553</v>
       </c>
-      <c r="E207" s="2">
-        <v>1.0943442583084106</v>
-      </c>
+      <c r="E207" s="2"/>
     </row>
     <row r="208">
       <c r="A208" s="1">
@@ -2764,15 +2360,11 @@
       <c r="B208" s="2">
         <v>0.33390182256698608</v>
       </c>
-      <c r="C208" s="2">
-        <v>-0.081120900809764862</v>
-      </c>
+      <c r="C208" s="2"/>
       <c r="D208" s="2">
         <v>1.2080827951431274</v>
       </c>
-      <c r="E208" s="2">
-        <v>1.0463593006134033</v>
-      </c>
+      <c r="E208" s="2"/>
     </row>
     <row r="209">
       <c r="A209" s="1">
@@ -2781,15 +2373,11 @@
       <c r="B209" s="2">
         <v>1.6393320560455322</v>
       </c>
-      <c r="C209" s="2">
-        <v>1.5359708070755005</v>
-      </c>
+      <c r="C209" s="2"/>
       <c r="D209" s="2">
         <v>1.2670102119445801</v>
       </c>
-      <c r="E209" s="2">
-        <v>1.1146552562713623</v>
-      </c>
+      <c r="E209" s="2"/>
     </row>
     <row r="210">
       <c r="A210" s="1">
@@ -2798,15 +2386,11 @@
       <c r="B210" s="2">
         <v>0.59391915798187256</v>
       </c>
-      <c r="C210" s="2">
-        <v>0.49178239703178406</v>
-      </c>
+      <c r="C210" s="2"/>
       <c r="D210" s="2">
         <v>1.3644167184829712</v>
       </c>
-      <c r="E210" s="2">
-        <v>1.2025395631790161</v>
-      </c>
+      <c r="E210" s="2"/>
     </row>
     <row r="211">
       <c r="A211" s="1">
@@ -2815,15 +2399,11 @@
       <c r="B211" s="2">
         <v>1.7075070142745972</v>
       </c>
-      <c r="C211" s="2">
-        <v>1.6463238000869751</v>
-      </c>
+      <c r="C211" s="2"/>
       <c r="D211" s="2">
         <v>1.2260303497314453</v>
       </c>
-      <c r="E211" s="2">
-        <v>1.0568299293518066</v>
-      </c>
+      <c r="E211" s="2"/>
     </row>
     <row r="212">
       <c r="A212" s="1">
@@ -2832,15 +2412,11 @@
       <c r="B212" s="2">
         <v>1.2655562162399292</v>
       </c>
-      <c r="C212" s="2">
-        <v>1.0948547124862671</v>
-      </c>
+      <c r="C212" s="2"/>
       <c r="D212" s="2">
         <v>1.2839332818984985</v>
       </c>
-      <c r="E212" s="2">
-        <v>1.068583607673645</v>
-      </c>
+      <c r="E212" s="2"/>
     </row>
     <row r="213">
       <c r="A213" s="1">
@@ -2849,15 +2425,11 @@
       <c r="B213" s="2">
         <v>1.6387084722518921</v>
       </c>
-      <c r="C213" s="2">
-        <v>1.5812954902648926</v>
-      </c>
+      <c r="C213" s="2"/>
       <c r="D213" s="2">
         <v>1.3926588296890259</v>
       </c>
-      <c r="E213" s="2">
-        <v>1.1988246440887451</v>
-      </c>
+      <c r="E213" s="2"/>
     </row>
     <row r="214">
       <c r="A214" s="1">
@@ -2866,15 +2438,11 @@
       <c r="B214" s="2">
         <v>1.9214067459106445</v>
       </c>
-      <c r="C214" s="2">
-        <v>1.7693629264831543</v>
-      </c>
+      <c r="C214" s="2"/>
       <c r="D214" s="2">
         <v>1.3162360191345215</v>
       </c>
-      <c r="E214" s="2">
-        <v>1.1316704750061035</v>
-      </c>
+      <c r="E214" s="2"/>
     </row>
     <row r="215">
       <c r="A215" s="1">
@@ -2883,15 +2451,11 @@
       <c r="B215" s="2">
         <v>0.80198955535888672</v>
       </c>
-      <c r="C215" s="2">
-        <v>0.6044471263885498</v>
-      </c>
+      <c r="C215" s="2"/>
       <c r="D215" s="2">
         <v>1.3758833408355713</v>
       </c>
-      <c r="E215" s="2">
-        <v>1.1225954294204712</v>
-      </c>
+      <c r="E215" s="2"/>
     </row>
     <row r="216">
       <c r="A216" s="1">
@@ -2900,15 +2464,11 @@
       <c r="B216" s="2">
         <v>1.6530786752700806</v>
       </c>
-      <c r="C216" s="2">
-        <v>0.97433620691299438</v>
-      </c>
+      <c r="C216" s="2"/>
       <c r="D216" s="2">
         <v>1.4042555093765259</v>
       </c>
-      <c r="E216" s="2">
-        <v>1.1438429355621338</v>
-      </c>
+      <c r="E216" s="2"/>
     </row>
     <row r="217">
       <c r="A217" s="1">
@@ -2917,15 +2477,11 @@
       <c r="B217" s="2">
         <v>1.3124315738677979</v>
       </c>
-      <c r="C217" s="2">
-        <v>1.0910482406616211</v>
-      </c>
+      <c r="C217" s="2"/>
       <c r="D217" s="2">
         <v>1.3900672197341919</v>
       </c>
-      <c r="E217" s="2">
-        <v>1.0569641590118408</v>
-      </c>
+      <c r="E217" s="2"/>
     </row>
     <row r="218">
       <c r="A218" s="1">
@@ -2934,15 +2490,11 @@
       <c r="B218" s="2">
         <v>0.95152682065963745</v>
       </c>
-      <c r="C218" s="2">
-        <v>0.93158328533172607</v>
-      </c>
+      <c r="C218" s="2"/>
       <c r="D218" s="2">
         <v>1.397963285446167</v>
       </c>
-      <c r="E218" s="2">
-        <v>1.0719376802444458</v>
-      </c>
+      <c r="E218" s="2"/>
     </row>
     <row r="219">
       <c r="A219" s="1">
@@ -2951,15 +2503,11 @@
       <c r="B219" s="2">
         <v>1.1307454109191895</v>
       </c>
-      <c r="C219" s="2">
-        <v>0.41010758280754089</v>
-      </c>
+      <c r="C219" s="2"/>
       <c r="D219" s="2">
         <v>1.2928874492645264</v>
       </c>
-      <c r="E219" s="2">
-        <v>1.0700051784515381</v>
-      </c>
+      <c r="E219" s="2"/>
     </row>
     <row r="220">
       <c r="A220" s="1">
@@ -2968,15 +2516,11 @@
       <c r="B220" s="2">
         <v>1.9628560543060303</v>
       </c>
-      <c r="C220" s="2">
-        <v>1.8375509977340698</v>
-      </c>
+      <c r="C220" s="2"/>
       <c r="D220" s="2">
         <v>1.4544354677200317</v>
       </c>
-      <c r="E220" s="2">
-        <v>1.2337374687194824</v>
-      </c>
+      <c r="E220" s="2"/>
     </row>
     <row r="221">
       <c r="A221" s="1">
@@ -2985,15 +2529,11 @@
       <c r="B221" s="2">
         <v>1.1378612518310547</v>
       </c>
-      <c r="C221" s="2">
-        <v>0.31294530630111694</v>
-      </c>
+      <c r="C221" s="2"/>
       <c r="D221" s="2">
         <v>1.4848201274871826</v>
       </c>
-      <c r="E221" s="2">
-        <v>1.328874945640564</v>
-      </c>
+      <c r="E221" s="2"/>
     </row>
     <row r="222">
       <c r="A222" s="1">
@@ -3002,15 +2542,11 @@
       <c r="B222" s="2">
         <v>1.7097737789154053</v>
       </c>
-      <c r="C222" s="2">
-        <v>1.716057300567627</v>
-      </c>
+      <c r="C222" s="2"/>
       <c r="D222" s="2">
         <v>1.5098098516464233</v>
       </c>
-      <c r="E222" s="2">
-        <v>1.3623071908950806</v>
-      </c>
+      <c r="E222" s="2"/>
     </row>
     <row r="223">
       <c r="A223" s="1">
@@ -3019,15 +2555,11 @@
       <c r="B223" s="2">
         <v>0.97572356462478638</v>
       </c>
-      <c r="C223" s="2">
-        <v>1.7519700527191162</v>
-      </c>
+      <c r="C223" s="2"/>
       <c r="D223" s="2">
         <v>1.623569130897522</v>
       </c>
-      <c r="E223" s="2">
-        <v>1.4649226665496826</v>
-      </c>
+      <c r="E223" s="2"/>
     </row>
     <row r="224">
       <c r="A224" s="1">
@@ -3036,15 +2568,11 @@
       <c r="B224" s="2">
         <v>2.2559218406677246</v>
       </c>
-      <c r="C224" s="2">
-        <v>2.0780384540557861</v>
-      </c>
+      <c r="C224" s="2"/>
       <c r="D224" s="2">
         <v>1.6346161365509033</v>
       </c>
-      <c r="E224" s="2">
-        <v>1.5463147163391113</v>
-      </c>
+      <c r="E224" s="2"/>
     </row>
     <row r="225">
       <c r="A225" s="1">
@@ -3053,15 +2581,11 @@
       <c r="B225" s="2">
         <v>1.9265403747558594</v>
       </c>
-      <c r="C225" s="2">
-        <v>1.8305730819702148</v>
-      </c>
+      <c r="C225" s="2"/>
       <c r="D225" s="2">
         <v>1.4885809421539307</v>
       </c>
-      <c r="E225" s="2">
-        <v>1.4020793437957764</v>
-      </c>
+      <c r="E225" s="2"/>
     </row>
     <row r="226">
       <c r="A226" s="1">
@@ -3070,15 +2594,11 @@
       <c r="B226" s="2">
         <v>1.5373392105102539</v>
       </c>
-      <c r="C226" s="2">
-        <v>1.3919390439987183</v>
-      </c>
+      <c r="C226" s="2"/>
       <c r="D226" s="2">
         <v>1.5964707136154175</v>
       </c>
-      <c r="E226" s="2">
-        <v>1.5919574499130249</v>
-      </c>
+      <c r="E226" s="2"/>
     </row>
     <row r="227">
       <c r="A227" s="1">
@@ -3087,15 +2607,11 @@
       <c r="B227" s="2">
         <v>1.9753605127334595</v>
       </c>
-      <c r="C227" s="2">
-        <v>1.8551222085952759</v>
-      </c>
+      <c r="C227" s="2"/>
       <c r="D227" s="2">
         <v>1.5929747819900513</v>
       </c>
-      <c r="E227" s="2">
-        <v>1.5661062002182007</v>
-      </c>
+      <c r="E227" s="2"/>
     </row>
     <row r="228">
       <c r="A228" s="1">
@@ -3104,15 +2620,11 @@
       <c r="B228" s="2">
         <v>1.2301684617996216</v>
       </c>
-      <c r="C228" s="2">
-        <v>1.1426362991333008</v>
-      </c>
+      <c r="C228" s="2"/>
       <c r="D228" s="2">
         <v>1.6729639768600464</v>
       </c>
-      <c r="E228" s="2">
-        <v>1.5116254091262817</v>
-      </c>
+      <c r="E228" s="2"/>
     </row>
     <row r="229">
       <c r="A229" s="1">
@@ -3121,15 +2633,11 @@
       <c r="B229" s="2">
         <v>0.64853912591934204</v>
       </c>
-      <c r="C229" s="2">
-        <v>0.53943246603012085</v>
-      </c>
+      <c r="C229" s="2"/>
       <c r="D229" s="2">
         <v>1.4716781377792358</v>
       </c>
-      <c r="E229" s="2">
-        <v>1.3644058704376221</v>
-      </c>
+      <c r="E229" s="2"/>
     </row>
     <row r="230">
       <c r="A230" s="1">
@@ -3138,15 +2646,11 @@
       <c r="B230" s="2">
         <v>2.1088693141937256</v>
       </c>
-      <c r="C230" s="2">
-        <v>2.0218477249145508</v>
-      </c>
+      <c r="C230" s="2"/>
       <c r="D230" s="2">
         <v>1.4309722185134888</v>
       </c>
-      <c r="E230" s="2">
-        <v>1.3081674575805664</v>
-      </c>
+      <c r="E230" s="2"/>
     </row>
     <row r="231">
       <c r="A231" s="1">
@@ -3155,15 +2659,11 @@
       <c r="B231" s="2">
         <v>1.6783111095428467</v>
       </c>
-      <c r="C231" s="2">
-        <v>1.4833962917327881</v>
-      </c>
+      <c r="C231" s="2"/>
       <c r="D231" s="2">
         <v>1.4457551240921021</v>
       </c>
-      <c r="E231" s="2">
-        <v>1.3200341463088989</v>
-      </c>
+      <c r="E231" s="2"/>
     </row>
     <row r="232">
       <c r="A232" s="1">
@@ -3172,15 +2672,11 @@
       <c r="B232" s="2">
         <v>1.6956256628036499</v>
       </c>
-      <c r="C232" s="2">
-        <v>1.2616429328918457</v>
-      </c>
+      <c r="C232" s="2"/>
       <c r="D232" s="2">
         <v>1.3328620195388794</v>
       </c>
-      <c r="E232" s="2">
-        <v>1.1704692840576172</v>
-      </c>
+      <c r="E232" s="2"/>
     </row>
     <row r="233">
       <c r="A233" s="1">
@@ -3189,15 +2685,11 @@
       <c r="B233" s="2">
         <v>0.4443499743938446</v>
       </c>
-      <c r="C233" s="2">
-        <v>0.75306278467178345</v>
-      </c>
+      <c r="C233" s="2"/>
       <c r="D233" s="2">
         <v>1.384427547454834</v>
       </c>
-      <c r="E233" s="2">
-        <v>1.2257899045944214</v>
-      </c>
+      <c r="E233" s="2"/>
     </row>
     <row r="234">
       <c r="A234" s="1">
@@ -3206,15 +2698,11 @@
       <c r="B234" s="2">
         <v>1.5601869821548462</v>
       </c>
-      <c r="C234" s="2">
-        <v>1.3244268894195557</v>
-      </c>
+      <c r="C234" s="2"/>
       <c r="D234" s="2">
         <v>1.3866252899169922</v>
       </c>
-      <c r="E234" s="2">
-        <v>1.2190736532211304</v>
-      </c>
+      <c r="E234" s="2"/>
     </row>
     <row r="235">
       <c r="A235" s="1">
@@ -3223,15 +2711,11 @@
       <c r="B235" s="2">
         <v>1.6703846454620361</v>
       </c>
-      <c r="C235" s="2">
-        <v>1.4987400770187378</v>
-      </c>
+      <c r="C235" s="2"/>
       <c r="D235" s="2">
         <v>1.1621153354644775</v>
       </c>
-      <c r="E235" s="2">
-        <v>0.97391402721405029</v>
-      </c>
+      <c r="E235" s="2"/>
     </row>
     <row r="236">
       <c r="A236" s="1">
@@ -3240,15 +2724,11 @@
       <c r="B236" s="2">
         <v>0.95932298898696899</v>
       </c>
-      <c r="C236" s="2">
-        <v>0.50903856754302979</v>
-      </c>
+      <c r="C236" s="2"/>
       <c r="D236" s="2">
         <v>1.1453301906585693</v>
       </c>
-      <c r="E236" s="2">
-        <v>0.95792633295059204</v>
-      </c>
+      <c r="E236" s="2"/>
     </row>
     <row r="237">
       <c r="A237" s="1">
@@ -3257,15 +2737,11 @@
       <c r="B237" s="2">
         <v>1.6942579746246338</v>
       </c>
-      <c r="C237" s="2">
-        <v>1.6405216455459595</v>
-      </c>
+      <c r="C237" s="2"/>
       <c r="D237" s="2">
         <v>1.1125667095184326</v>
       </c>
-      <c r="E237" s="2">
-        <v>0.95066237449645996</v>
-      </c>
+      <c r="E237" s="2"/>
     </row>
     <row r="238">
       <c r="A238" s="1">
@@ -3274,15 +2750,11 @@
       <c r="B238" s="2">
         <v>0.66831928491592407</v>
       </c>
-      <c r="C238" s="2">
-        <v>0.47898593544960022</v>
-      </c>
+      <c r="C238" s="2"/>
       <c r="D238" s="2">
         <v>1.237261176109314</v>
       </c>
-      <c r="E238" s="2">
-        <v>1.0179896354675293</v>
-      </c>
+      <c r="E238" s="2"/>
     </row>
     <row r="239">
       <c r="A239" s="1">
@@ -3291,15 +2763,11 @@
       <c r="B239" s="2">
         <v>0.088279090821743011</v>
       </c>
-      <c r="C239" s="2">
-        <v>-0.1845887303352356</v>
-      </c>
+      <c r="C239" s="2"/>
       <c r="D239" s="2">
         <v>1.1578308343887329</v>
       </c>
-      <c r="E239" s="2">
-        <v>0.95300012826919556</v>
-      </c>
+      <c r="E239" s="2"/>
     </row>
     <row r="240">
       <c r="A240" s="1">
@@ -3308,15 +2776,11 @@
       <c r="B240" s="2">
         <v>1.5272446870803833</v>
       </c>
-      <c r="C240" s="2">
-        <v>1.3395067453384399</v>
-      </c>
+      <c r="C240" s="2"/>
       <c r="D240" s="2">
         <v>1.1170773506164551</v>
       </c>
-      <c r="E240" s="2">
-        <v>0.92268824577331543</v>
-      </c>
+      <c r="E240" s="2"/>
     </row>
     <row r="241">
       <c r="A241" s="1">
@@ -3325,15 +2789,11 @@
       <c r="B241" s="2">
         <v>1.400754451751709</v>
       </c>
-      <c r="C241" s="2">
-        <v>1.1962673664093018</v>
-      </c>
+      <c r="C241" s="2"/>
       <c r="D241" s="2">
         <v>1.1723089218139648</v>
       </c>
-      <c r="E241" s="2">
-        <v>1.0119190216064453</v>
-      </c>
+      <c r="E241" s="2"/>
     </row>
     <row r="242">
       <c r="A242" s="1">
@@ -3342,15 +2802,11 @@
       <c r="B242" s="2">
         <v>1.5666007995605469</v>
       </c>
-      <c r="C242" s="2">
-        <v>1.3590083122253418</v>
-      </c>
+      <c r="C242" s="2"/>
       <c r="D242" s="2">
         <v>1.1357166767120361</v>
       </c>
-      <c r="E242" s="2">
-        <v>0.94670683145523071</v>
-      </c>
+      <c r="E242" s="2"/>
     </row>
     <row r="243">
       <c r="A243" s="1">
@@ -3359,15 +2815,11 @@
       <c r="B243" s="2">
         <v>0.8453134298324585</v>
       </c>
-      <c r="C243" s="2">
-        <v>0.73952138423919678</v>
-      </c>
+      <c r="C243" s="2"/>
       <c r="D243" s="2">
         <v>1.1881477832794189</v>
       </c>
-      <c r="E243" s="2">
-        <v>1.0002341270446777</v>
-      </c>
+      <c r="E243" s="2"/>
     </row>
     <row r="244">
       <c r="A244" s="1">
@@ -3376,15 +2828,11 @@
       <c r="B244" s="2">
         <v>1.303602933883667</v>
       </c>
-      <c r="C244" s="2">
-        <v>1.2259331941604614</v>
-      </c>
+      <c r="C244" s="2"/>
       <c r="D244" s="2">
         <v>1.3242640495300293</v>
       </c>
-      <c r="E244" s="2">
-        <v>1.1601516008377075</v>
-      </c>
+      <c r="E244" s="2"/>
     </row>
     <row r="245">
       <c r="A245" s="1">
@@ -3393,15 +2841,11 @@
       <c r="B245" s="2">
         <v>1.4564077854156494</v>
       </c>
-      <c r="C245" s="2">
-        <v>1.3121156692504883</v>
-      </c>
+      <c r="C245" s="2"/>
       <c r="D245" s="2">
         <v>1.2350993156433105</v>
       </c>
-      <c r="E245" s="2">
-        <v>1.0251392126083374</v>
-      </c>
+      <c r="E245" s="2"/>
     </row>
     <row r="246">
       <c r="A246" s="1">
@@ -3410,15 +2854,11 @@
       <c r="B246" s="2">
         <v>1.3649272918701172</v>
       </c>
-      <c r="C246" s="2">
-        <v>1.0536116361618042</v>
-      </c>
+      <c r="C246" s="2"/>
       <c r="D246" s="2">
         <v>1.2297667264938354</v>
       </c>
-      <c r="E246" s="2">
-        <v>1.0305960178375244</v>
-      </c>
+      <c r="E246" s="2"/>
     </row>
     <row r="247">
       <c r="A247" s="1">
@@ -3427,15 +2867,11 @@
       <c r="B247" s="2">
         <v>1.1401997804641724</v>
       </c>
-      <c r="C247" s="2">
-        <v>0.96073150634765625</v>
-      </c>
+      <c r="C247" s="2"/>
       <c r="D247" s="2">
         <v>1.2322481870651245</v>
       </c>
-      <c r="E247" s="2">
-        <v>1.0090775489807129</v>
-      </c>
+      <c r="E247" s="2"/>
     </row>
     <row r="248">
       <c r="A248" s="1">
@@ -3444,15 +2880,11 @@
       <c r="B248" s="2">
         <v>1.3133248090744019</v>
       </c>
-      <c r="C248" s="2">
-        <v>1.2546687126159668</v>
-      </c>
+      <c r="C248" s="2"/>
       <c r="D248" s="2">
         <v>1.1537261009216309</v>
       </c>
-      <c r="E248" s="2">
-        <v>0.91261166334152222</v>
-      </c>
+      <c r="E248" s="2"/>
     </row>
     <row r="249">
       <c r="A249" s="1">
@@ -3461,15 +2893,11 @@
       <c r="B249" s="2">
         <v>0.72476279735565186</v>
       </c>
-      <c r="C249" s="2">
-        <v>0.12439494580030441</v>
-      </c>
+      <c r="C249" s="2"/>
       <c r="D249" s="2">
         <v>1.0973280668258667</v>
       </c>
-      <c r="E249" s="2">
-        <v>0.84870052337646484</v>
-      </c>
+      <c r="E249" s="2"/>
     </row>
     <row r="250">
       <c r="A250" s="1">
@@ -3478,15 +2906,11 @@
       <c r="B250" s="2">
         <v>1.3527612686157227</v>
       </c>
-      <c r="C250" s="2">
-        <v>1.2453783750534058</v>
-      </c>
+      <c r="C250" s="2"/>
       <c r="D250" s="2">
         <v>1.1186145544052124</v>
       </c>
-      <c r="E250" s="2">
-        <v>0.87757325172424316</v>
-      </c>
+      <c r="E250" s="2"/>
     </row>
     <row r="251">
       <c r="A251" s="1">
@@ -3495,15 +2919,11 @@
       <c r="B251" s="2">
         <v>1.5889337062835693</v>
       </c>
-      <c r="C251" s="2">
-        <v>1.1653428077697754</v>
-      </c>
+      <c r="C251" s="2"/>
       <c r="D251" s="2">
         <v>1.0637993812561035</v>
       </c>
-      <c r="E251" s="2">
-        <v>0.82347184419631958</v>
-      </c>
+      <c r="E251" s="2"/>
     </row>
     <row r="252">
       <c r="A252" s="1">
@@ -3512,15 +2932,11 @@
       <c r="B252" s="2">
         <v>0.1386144608259201</v>
       </c>
-      <c r="C252" s="2">
-        <v>-0.12867210805416107</v>
-      </c>
+      <c r="C252" s="2"/>
       <c r="D252" s="2">
         <v>0.97546648979187012</v>
       </c>
-      <c r="E252" s="2">
-        <v>0.80263465642929077</v>
-      </c>
+      <c r="E252" s="2"/>
     </row>
     <row r="253">
       <c r="A253" s="1">
@@ -3529,15 +2945,11 @@
       <c r="B253" s="2">
         <v>0.79602092504501343</v>
       </c>
-      <c r="C253" s="2">
-        <v>0.65073329210281372</v>
-      </c>
+      <c r="C253" s="2"/>
       <c r="D253" s="2">
         <v>0.91766738891601562</v>
       </c>
-      <c r="E253" s="2">
-        <v>0.76536065340042114</v>
-      </c>
+      <c r="E253" s="2"/>
     </row>
     <row r="254">
       <c r="A254" s="1">
@@ -3546,15 +2958,11 @@
       <c r="B254" s="2">
         <v>1.6479859352111816</v>
       </c>
-      <c r="C254" s="2">
-        <v>1.5719699859619141</v>
-      </c>
+      <c r="C254" s="2"/>
       <c r="D254" s="2">
         <v>0.99857324361801147</v>
       </c>
-      <c r="E254" s="2">
-        <v>0.90234208106994629</v>
-      </c>
+      <c r="E254" s="2"/>
     </row>
     <row r="255">
       <c r="A255" s="1">
@@ -3563,15 +2971,11 @@
       <c r="B255" s="2">
         <v>0.87159037590026855</v>
       </c>
-      <c r="C255" s="2">
-        <v>0.56669884920120239</v>
-      </c>
+      <c r="C255" s="2"/>
       <c r="D255" s="2">
         <v>1.0063868761062622</v>
       </c>
-      <c r="E255" s="2">
-        <v>0.91209930181503296</v>
-      </c>
+      <c r="E255" s="2"/>
     </row>
     <row r="256">
       <c r="A256" s="1">
@@ -3580,15 +2984,11 @@
       <c r="B256" s="2">
         <v>0.34520411491394043</v>
       </c>
-      <c r="C256" s="2">
-        <v>0.77319705486297607</v>
-      </c>
+      <c r="C256" s="2"/>
       <c r="D256" s="2">
         <v>0.84690463542938232</v>
       </c>
-      <c r="E256" s="2">
-        <v>0.75713616609573364</v>
-      </c>
+      <c r="E256" s="2"/>
     </row>
     <row r="257">
       <c r="A257" s="1">
@@ -3597,15 +2997,11 @@
       <c r="B257" s="2">
         <v>0.7931329607963562</v>
       </c>
-      <c r="C257" s="2">
-        <v>0.91920274496078491</v>
-      </c>
+      <c r="C257" s="2"/>
       <c r="D257" s="2">
         <v>0.97125893831253052</v>
       </c>
-      <c r="E257" s="2">
-        <v>0.89210206270217896</v>
-      </c>
+      <c r="E257" s="2"/>
     </row>
     <row r="258">
       <c r="A258" s="1">
@@ -3614,15 +3010,11 @@
       <c r="B258" s="2">
         <v>1.4529156684875488</v>
       </c>
-      <c r="C258" s="2">
-        <v>1.3572276830673218</v>
-      </c>
+      <c r="C258" s="2"/>
       <c r="D258" s="2">
         <v>1.0330319404602051</v>
       </c>
-      <c r="E258" s="2">
-        <v>0.94061464071273804</v>
-      </c>
+      <c r="E258" s="2"/>
     </row>
     <row r="259">
       <c r="A259" s="1">
@@ -3631,15 +3023,11 @@
       <c r="B259" s="2">
         <v>1.4230834245681763</v>
       </c>
-      <c r="C259" s="2">
-        <v>1.3331936597824097</v>
-      </c>
+      <c r="C259" s="2"/>
       <c r="D259" s="2">
         <v>1.0213062763214111</v>
       </c>
-      <c r="E259" s="2">
-        <v>0.86820513010025024</v>
-      </c>
+      <c r="E259" s="2"/>
     </row>
     <row r="260">
       <c r="A260" s="1">
@@ -3648,15 +3036,11 @@
       <c r="B260" s="2">
         <v>0.15359380841255188</v>
       </c>
-      <c r="C260" s="2">
-        <v>-0.22932547330856323</v>
-      </c>
+      <c r="C260" s="2"/>
       <c r="D260" s="2">
         <v>1.0333116054534912</v>
       </c>
-      <c r="E260" s="2">
-        <v>0.93559753894805908</v>
-      </c>
+      <c r="E260" s="2"/>
     </row>
     <row r="261">
       <c r="A261" s="1">
@@ -3665,15 +3049,11 @@
       <c r="B261" s="2">
         <v>1.2578030824661255</v>
       </c>
-      <c r="C261" s="2">
-        <v>1.0860205888748169</v>
-      </c>
+      <c r="C261" s="2"/>
       <c r="D261" s="2">
         <v>1.0520367622375488</v>
       </c>
-      <c r="E261" s="2">
-        <v>0.84511095285415649</v>
-      </c>
+      <c r="E261" s="2"/>
     </row>
     <row r="262">
       <c r="A262" s="1">
@@ -3682,15 +3062,11 @@
       <c r="B262" s="2">
         <v>1.351978063583374</v>
       </c>
-      <c r="C262" s="2">
-        <v>1.0873464345932007</v>
-      </c>
+      <c r="C262" s="2"/>
       <c r="D262" s="2">
         <v>1.0870660543441772</v>
       </c>
-      <c r="E262" s="2">
-        <v>0.88683003187179565</v>
-      </c>
+      <c r="E262" s="2"/>
     </row>
     <row r="263">
       <c r="A263" s="1">
@@ -3699,15 +3075,11 @@
       <c r="B263" s="2">
         <v>1.5424548387527466</v>
       </c>
-      <c r="C263" s="2">
-        <v>0.92028439044952393</v>
-      </c>
+      <c r="C263" s="2"/>
       <c r="D263" s="2">
         <v>0.95616143941879272</v>
       </c>
-      <c r="E263" s="2">
-        <v>0.74079799652099609</v>
-      </c>
+      <c r="E263" s="2"/>
     </row>
     <row r="264">
       <c r="A264" s="1">
@@ -3716,15 +3088,11 @@
       <c r="B264" s="2">
         <v>0.97963887453079224</v>
       </c>
-      <c r="C264" s="2">
-        <v>1.1732308864593506</v>
-      </c>
+      <c r="C264" s="2"/>
       <c r="D264" s="2">
         <v>0.87969917058944702</v>
       </c>
-      <c r="E264" s="2">
-        <v>0.68102198839187622</v>
-      </c>
+      <c r="E264" s="2"/>
     </row>
     <row r="265">
       <c r="A265" s="1">
@@ -3733,15 +3101,11 @@
       <c r="B265" s="2">
         <v>0.51372969150543213</v>
       </c>
-      <c r="C265" s="2">
-        <v>-0.041182484477758408</v>
-      </c>
+      <c r="C265" s="2"/>
       <c r="D265" s="2">
         <v>1.0744653940200806</v>
       </c>
-      <c r="E265" s="2">
-        <v>0.93705177307128906</v>
-      </c>
+      <c r="E265" s="2"/>
     </row>
     <row r="266">
       <c r="A266" s="1">
@@ -3750,15 +3114,11 @@
       <c r="B266" s="2">
         <v>1.1083972454071045</v>
       </c>
-      <c r="C266" s="2">
-        <v>1.2946743965148926</v>
-      </c>
+      <c r="C266" s="2"/>
       <c r="D266" s="2">
         <v>1.0123846530914307</v>
       </c>
-      <c r="E266" s="2">
-        <v>0.86429935693740845</v>
-      </c>
+      <c r="E266" s="2"/>
     </row>
     <row r="267">
       <c r="A267" s="1">
@@ -3767,15 +3127,11 @@
       <c r="B267" s="2">
         <v>0.27477392554283142</v>
       </c>
-      <c r="C267" s="2">
-        <v>0.042939767241477966</v>
-      </c>
+      <c r="C267" s="2"/>
       <c r="D267" s="2">
         <v>0.9141051173210144</v>
       </c>
-      <c r="E267" s="2">
-        <v>0.75690704584121704</v>
-      </c>
+      <c r="E267" s="2"/>
     </row>
     <row r="268">
       <c r="A268" s="1">
@@ -3784,15 +3140,11 @@
       <c r="B268" s="2">
         <v>0.73492306470870972</v>
       </c>
-      <c r="C268" s="2">
-        <v>0.79520928859710693</v>
-      </c>
+      <c r="C268" s="2"/>
       <c r="D268" s="2">
         <v>0.91679525375366211</v>
       </c>
-      <c r="E268" s="2">
-        <v>0.8127601146697998</v>
-      </c>
+      <c r="E268" s="2"/>
     </row>
     <row r="269">
       <c r="A269" s="1">
@@ -3801,15 +3153,11 @@
       <c r="B269" s="2">
         <v>1.9064894914627075</v>
       </c>
-      <c r="C269" s="2">
-        <v>2.0749428272247314</v>
-      </c>
+      <c r="C269" s="2"/>
       <c r="D269" s="2">
         <v>0.93014359474182129</v>
       </c>
-      <c r="E269" s="2">
-        <v>0.75221824645996094</v>
-      </c>
+      <c r="E269" s="2"/>
     </row>
     <row r="270">
       <c r="A270" s="1">
@@ -3818,15 +3166,11 @@
       <c r="B270" s="2">
         <v>0.69907701015472412</v>
       </c>
-      <c r="C270" s="2">
-        <v>0.43124860525131226</v>
-      </c>
+      <c r="C270" s="2"/>
       <c r="D270" s="2">
         <v>1.0504767894744873</v>
       </c>
-      <c r="E270" s="2">
-        <v>0.92909175157546997</v>
-      </c>
+      <c r="E270" s="2"/>
     </row>
     <row r="271">
       <c r="A271" s="1">
@@ -3835,15 +3179,11 @@
       <c r="B271" s="2">
         <v>0.46746206283569336</v>
       </c>
-      <c r="C271" s="2">
-        <v>0.12081573158502579</v>
-      </c>
+      <c r="C271" s="2"/>
       <c r="D271" s="2">
         <v>1.1118896007537842</v>
       </c>
-      <c r="E271" s="2">
-        <v>0.97747009992599487</v>
-      </c>
+      <c r="E271" s="2"/>
     </row>
     <row r="272">
       <c r="A272" s="1">
@@ -3852,15 +3192,11 @@
       <c r="B272" s="2">
         <v>1.5666657686233521</v>
       </c>
-      <c r="C272" s="2">
-        <v>1.422961950302124</v>
-      </c>
+      <c r="C272" s="2"/>
       <c r="D272" s="2">
         <v>1.3253248929977417</v>
       </c>
-      <c r="E272" s="2">
-        <v>1.1925166845321655</v>
-      </c>
+      <c r="E272" s="2"/>
     </row>
     <row r="273">
       <c r="A273" s="1">
@@ -3869,15 +3205,11 @@
       <c r="B273" s="2">
         <v>1.0997742414474487</v>
       </c>
-      <c r="C273" s="2">
-        <v>0.62835419178009033</v>
-      </c>
+      <c r="C273" s="2"/>
       <c r="D273" s="2">
         <v>1.3130826950073242</v>
       </c>
-      <c r="E273" s="2">
-        <v>1.1424304246902466</v>
-      </c>
+      <c r="E273" s="2"/>
     </row>
     <row r="274">
       <c r="A274" s="1">
@@ -3886,15 +3218,11 @@
       <c r="B274" s="2">
         <v>1.5967279672622681</v>
       </c>
-      <c r="C274" s="2">
-        <v>1.5506792068481445</v>
-      </c>
+      <c r="C274" s="2"/>
       <c r="D274" s="2">
         <v>1.2403908967971802</v>
       </c>
-      <c r="E274" s="2">
-        <v>1.0376049280166626</v>
-      </c>
+      <c r="E274" s="2"/>
     </row>
     <row r="275">
       <c r="A275" s="1">
@@ -3903,15 +3231,11 @@
       <c r="B275" s="2">
         <v>1.6611130237579346</v>
       </c>
-      <c r="C275" s="2">
-        <v>1.7300795316696167</v>
-      </c>
+      <c r="C275" s="2"/>
       <c r="D275" s="2">
         <v>1.2660610675811768</v>
       </c>
-      <c r="E275" s="2">
-        <v>1.0958372354507446</v>
-      </c>
+      <c r="E275" s="2"/>
     </row>
     <row r="276">
       <c r="A276" s="1">
@@ -3920,15 +3244,11 @@
       <c r="B276" s="2">
         <v>2.1956918239593506</v>
       </c>
-      <c r="C276" s="2">
-        <v>1.9783586263656616</v>
-      </c>
+      <c r="C276" s="2"/>
       <c r="D276" s="2">
         <v>1.3297243118286133</v>
       </c>
-      <c r="E276" s="2">
-        <v>1.1750072240829468</v>
-      </c>
+      <c r="E276" s="2"/>
     </row>
     <row r="277">
       <c r="A277" s="1">
@@ -3937,15 +3257,11 @@
       <c r="B277" s="2">
         <v>0.62474262714385986</v>
       </c>
-      <c r="C277" s="2">
-        <v>0.34443262219429016</v>
-      </c>
+      <c r="C277" s="2"/>
       <c r="D277" s="2">
         <v>1.3354830741882324</v>
       </c>
-      <c r="E277" s="2">
-        <v>1.1614859104156494</v>
-      </c>
+      <c r="E277" s="2"/>
     </row>
     <row r="278">
       <c r="A278" s="1">
@@ -3954,15 +3270,11 @@
       <c r="B278" s="2">
         <v>1.2522634267807007</v>
       </c>
-      <c r="C278" s="2">
-        <v>1.1315138339996338</v>
-      </c>
+      <c r="C278" s="2"/>
       <c r="D278" s="2">
         <v>1.3521963357925415</v>
       </c>
-      <c r="E278" s="2">
-        <v>1.1989123821258545</v>
-      </c>
+      <c r="E278" s="2"/>
     </row>
     <row r="279">
       <c r="A279" s="1">
@@ -3971,15 +3283,11 @@
       <c r="B279" s="2">
         <v>0.93010848760604858</v>
       </c>
-      <c r="C279" s="2">
-        <v>0.95533913373947144</v>
-      </c>
+      <c r="C279" s="2"/>
       <c r="D279" s="2">
         <v>1.3701539039611816</v>
       </c>
-      <c r="E279" s="2">
-        <v>1.2332757711410522</v>
-      </c>
+      <c r="E279" s="2"/>
     </row>
     <row r="280">
       <c r="A280" s="1">
@@ -3988,15 +3296,11 @@
       <c r="B280" s="2">
         <v>1.0404309034347534</v>
       </c>
-      <c r="C280" s="2">
-        <v>0.83334589004516602</v>
-      </c>
+      <c r="C280" s="2"/>
       <c r="D280" s="2">
         <v>1.4690201282501221</v>
       </c>
-      <c r="E280" s="2">
-        <v>1.3325581550598145</v>
-      </c>
+      <c r="E280" s="2"/>
     </row>
     <row r="281">
       <c r="A281" s="1">
@@ -4005,15 +3309,11 @@
       <c r="B281" s="2">
         <v>1.6184946298599243</v>
       </c>
-      <c r="C281" s="2">
-        <v>1.3012700080871582</v>
-      </c>
+      <c r="C281" s="2"/>
       <c r="D281" s="2">
         <v>1.3865048885345459</v>
       </c>
-      <c r="E281" s="2">
-        <v>1.2469757795333862</v>
-      </c>
+      <c r="E281" s="2"/>
     </row>
     <row r="282">
       <c r="A282" s="1">
@@ -4022,15 +3322,11 @@
       <c r="B282" s="2">
         <v>1.25019371509552</v>
       </c>
-      <c r="C282" s="2">
-        <v>0.96519303321838379</v>
-      </c>
+      <c r="C282" s="2"/>
       <c r="D282" s="2">
         <v>1.3635100126266479</v>
       </c>
-      <c r="E282" s="2">
-        <v>1.2102401256561279</v>
-      </c>
+      <c r="E282" s="2"/>
     </row>
     <row r="283">
       <c r="A283" s="1">
@@ -4039,15 +3335,11 @@
       <c r="B283" s="2">
         <v>1.7583461999893188</v>
       </c>
-      <c r="C283" s="2">
-        <v>1.8599497079849243</v>
-      </c>
+      <c r="C283" s="2"/>
       <c r="D283" s="2">
         <v>1.2786366939544678</v>
       </c>
-      <c r="E283" s="2">
-        <v>1.1086758375167847</v>
-      </c>
+      <c r="E283" s="2"/>
     </row>
     <row r="284">
       <c r="A284" s="1">
@@ -4056,15 +3348,11 @@
       <c r="B284" s="2">
         <v>2.5509097576141357</v>
       </c>
-      <c r="C284" s="2">
-        <v>2.6236209869384766</v>
-      </c>
+      <c r="C284" s="2"/>
       <c r="D284" s="2">
         <v>1.2541571855545044</v>
       </c>
-      <c r="E284" s="2">
-        <v>1.0076248645782471</v>
-      </c>
+      <c r="E284" s="2"/>
     </row>
     <row r="285">
       <c r="A285" s="1">
@@ -4073,15 +3361,11 @@
       <c r="B285" s="2">
         <v>1.4530540704727173</v>
       </c>
-      <c r="C285" s="2">
-        <v>1.2081171274185181</v>
-      </c>
+      <c r="C285" s="2"/>
       <c r="D285" s="2">
         <v>1.080778956413269</v>
       </c>
-      <c r="E285" s="2">
-        <v>0.8283543586730957</v>
-      </c>
+      <c r="E285" s="2"/>
     </row>
     <row r="286">
       <c r="A286" s="1">
@@ -4090,15 +3374,11 @@
       <c r="B286" s="2">
         <v>0.41778936982154846</v>
       </c>
-      <c r="C286" s="2">
-        <v>0.013811036944389343</v>
-      </c>
+      <c r="C286" s="2"/>
       <c r="D286" s="2">
         <v>1.0790601968765259</v>
       </c>
-      <c r="E286" s="2">
-        <v>0.846466064453125</v>
-      </c>
+      <c r="E286" s="2"/>
     </row>
     <row r="287">
       <c r="A287" s="1">
@@ -4107,15 +3387,11 @@
       <c r="B287" s="2">
         <v>0.48840361833572388</v>
       </c>
-      <c r="C287" s="2">
-        <v>0.21743591129779816</v>
-      </c>
+      <c r="C287" s="2"/>
       <c r="D287" s="2">
         <v>0.99301004409790039</v>
       </c>
-      <c r="E287" s="2">
-        <v>0.79570448398590088</v>
-      </c>
+      <c r="E287" s="2"/>
     </row>
     <row r="288">
       <c r="A288" s="1">
@@ -4124,15 +3400,11 @@
       <c r="B288" s="2">
         <v>0.70979189872741699</v>
       </c>
-      <c r="C288" s="2">
-        <v>0.045880593359470367</v>
-      </c>
+      <c r="C288" s="2"/>
       <c r="D288" s="2">
         <v>0.85004186630249023</v>
       </c>
-      <c r="E288" s="2">
-        <v>0.61174094676971436</v>
-      </c>
+      <c r="E288" s="2"/>
     </row>
     <row r="289">
       <c r="A289" s="1">
@@ -4141,15 +3413,11 @@
       <c r="B289" s="2">
         <v>-0.51997315883636475</v>
       </c>
-      <c r="C289" s="2">
-        <v>-0.78008937835693359</v>
-      </c>
+      <c r="C289" s="2"/>
       <c r="D289" s="2">
         <v>0.80765068531036377</v>
       </c>
-      <c r="E289" s="2">
-        <v>0.53381061553955078</v>
-      </c>
+      <c r="E289" s="2"/>
     </row>
     <row r="290">
       <c r="A290" s="1">
@@ -4158,15 +3426,11 @@
       <c r="B290" s="2">
         <v>1.6030266284942627</v>
       </c>
-      <c r="C290" s="2">
-        <v>1.4642753601074219</v>
-      </c>
+      <c r="C290" s="2"/>
       <c r="D290" s="2">
         <v>0.82293063402175903</v>
       </c>
-      <c r="E290" s="2">
-        <v>0.55177152156829834</v>
-      </c>
+      <c r="E290" s="2"/>
     </row>
     <row r="291">
       <c r="A291" s="1">
@@ -4175,15 +3439,11 @@
       <c r="B291" s="2">
         <v>0.47574183344841003</v>
       </c>
-      <c r="C291" s="2">
-        <v>0.50833892822265625</v>
-      </c>
+      <c r="C291" s="2"/>
       <c r="D291" s="2">
         <v>0.88260281085968018</v>
       </c>
-      <c r="E291" s="2">
-        <v>0.62182193994522095</v>
-      </c>
+      <c r="E291" s="2"/>
     </row>
     <row r="292">
       <c r="A292" s="1">
@@ -4192,15 +3452,11 @@
       <c r="B292" s="2">
         <v>0.47163292765617371</v>
       </c>
-      <c r="C292" s="2">
-        <v>0.20427796244621277</v>
-      </c>
+      <c r="C292" s="2"/>
       <c r="D292" s="2">
         <v>0.90585345029830933</v>
       </c>
-      <c r="E292" s="2">
-        <v>0.64134126901626587</v>
-      </c>
+      <c r="E292" s="2"/>
     </row>
     <row r="293">
       <c r="A293" s="1">
@@ -4209,15 +3465,11 @@
       <c r="B293" s="2">
         <v>2.169389009475708</v>
       </c>
-      <c r="C293" s="2">
-        <v>1.9222481250762939</v>
-      </c>
+      <c r="C293" s="2"/>
       <c r="D293" s="2">
         <v>0.99328809976577759</v>
       </c>
-      <c r="E293" s="2">
-        <v>0.77296894788742065</v>
-      </c>
+      <c r="E293" s="2"/>
     </row>
     <row r="294">
       <c r="A294" s="1">
@@ -4226,15 +3478,11 @@
       <c r="B294" s="2">
         <v>1.5905734300613403</v>
       </c>
-      <c r="C294" s="2">
-        <v>1.3697652816772461</v>
-      </c>
+      <c r="C294" s="2"/>
       <c r="D294" s="2">
         <v>1.1772722005844116</v>
       </c>
-      <c r="E294" s="2">
-        <v>0.95826274156570435</v>
-      </c>
+      <c r="E294" s="2"/>
     </row>
     <row r="295">
       <c r="A295" s="1">
@@ -4243,15 +3491,11 @@
       <c r="B295" s="2">
         <v>0.95483887195587158</v>
       </c>
-      <c r="C295" s="2">
-        <v>0.644264817237854</v>
-      </c>
+      <c r="C295" s="2"/>
       <c r="D295" s="2">
         <v>1.0827399492263794</v>
       </c>
-      <c r="E295" s="2">
-        <v>0.82907462120056152</v>
-      </c>
+      <c r="E295" s="2"/>
     </row>
     <row r="296">
       <c r="A296" s="1">
@@ -4260,15 +3504,11 @@
       <c r="B296" s="2">
         <v>0.69765973091125488</v>
       </c>
-      <c r="C296" s="2">
-        <v>0.39310979843139648</v>
-      </c>
+      <c r="C296" s="2"/>
       <c r="D296" s="2">
         <v>1.2303216457366943</v>
       </c>
-      <c r="E296" s="2">
-        <v>0.95239889621734619</v>
-      </c>
+      <c r="E296" s="2"/>
     </row>
     <row r="297">
       <c r="A297" s="1">
@@ -4277,15 +3517,11 @@
       <c r="B297" s="2">
         <v>1.4967035055160522</v>
       </c>
-      <c r="C297" s="2">
-        <v>1.2305294275283813</v>
-      </c>
+      <c r="C297" s="2"/>
       <c r="D297" s="2">
         <v>1.1550716161727905</v>
       </c>
-      <c r="E297" s="2">
-        <v>0.87700515985488892</v>
-      </c>
+      <c r="E297" s="2"/>
     </row>
     <row r="298">
       <c r="A298" s="1">
@@ -4294,15 +3530,11 @@
       <c r="B298" s="2">
         <v>1.1358842849731445</v>
       </c>
-      <c r="C298" s="2">
-        <v>0.88755476474761963</v>
-      </c>
+      <c r="C298" s="2"/>
       <c r="D298" s="2">
         <v>1.0595005750656128</v>
       </c>
-      <c r="E298" s="2">
-        <v>0.80836498737335205</v>
-      </c>
+      <c r="E298" s="2"/>
     </row>
     <row r="299">
       <c r="A299" s="1">
@@ -4311,15 +3543,11 @@
       <c r="B299" s="2">
         <v>0.75223612785339355</v>
       </c>
-      <c r="C299" s="2">
-        <v>0.3015824556350708</v>
-      </c>
+      <c r="C299" s="2"/>
       <c r="D299" s="2">
         <v>0.92929434776306152</v>
       </c>
-      <c r="E299" s="2">
-        <v>0.69969654083251953</v>
-      </c>
+      <c r="E299" s="2"/>
     </row>
     <row r="300">
       <c r="A300" s="1">
@@ -4328,15 +3556,11 @@
       <c r="B300" s="2">
         <v>1.8039766550064087</v>
       </c>
-      <c r="C300" s="2">
-        <v>1.6182571649551392</v>
-      </c>
+      <c r="C300" s="2"/>
       <c r="D300" s="2">
         <v>0.92470461130142212</v>
       </c>
-      <c r="E300" s="2">
-        <v>0.69052267074584961</v>
-      </c>
+      <c r="E300" s="2"/>
     </row>
     <row r="301">
       <c r="A301" s="1">
@@ -4345,15 +3569,11 @@
       <c r="B301" s="2">
         <v>-0.20561701059341431</v>
       </c>
-      <c r="C301" s="2">
-        <v>-0.47426533699035645</v>
-      </c>
+      <c r="C301" s="2"/>
       <c r="D301" s="2">
         <v>0.99573558568954468</v>
       </c>
-      <c r="E301" s="2">
-        <v>0.7126166820526123</v>
-      </c>
+      <c r="E301" s="2"/>
     </row>
     <row r="302">
       <c r="A302" s="1">
@@ -4362,15 +3582,11 @@
       <c r="B302" s="2">
         <v>1.3092491626739502</v>
       </c>
-      <c r="C302" s="2">
-        <v>1.3044862747192383</v>
-      </c>
+      <c r="C302" s="2"/>
       <c r="D302" s="2">
         <v>0.98348772525787354</v>
       </c>
-      <c r="E302" s="2">
-        <v>0.71766781806945801</v>
-      </c>
+      <c r="E302" s="2"/>
     </row>
     <row r="303">
       <c r="A303" s="1">
@@ -4379,15 +3595,11 @@
       <c r="B303" s="2">
         <v>0.41871783137321472</v>
       </c>
-      <c r="C303" s="2">
-        <v>0.39174947142601013</v>
-      </c>
+      <c r="C303" s="2"/>
       <c r="D303" s="2">
         <v>0.76769578456878662</v>
       </c>
-      <c r="E303" s="2">
-        <v>0.49433112144470215</v>
-      </c>
+      <c r="E303" s="2"/>
     </row>
     <row r="304">
       <c r="A304" s="1">
@@ -4396,15 +3608,11 @@
       <c r="B304" s="2">
         <v>0.91353130340576172</v>
       </c>
-      <c r="C304" s="2">
-        <v>0.56170016527175903</v>
-      </c>
+      <c r="C304" s="2"/>
       <c r="D304" s="2">
         <v>0.7285504937171936</v>
       </c>
-      <c r="E304" s="2">
-        <v>0.49916517734527588</v>
-      </c>
+      <c r="E304" s="2"/>
     </row>
     <row r="305">
       <c r="A305" s="1">
@@ -4413,15 +3621,11 @@
       <c r="B305" s="2">
         <v>1.3369383811950684</v>
       </c>
-      <c r="C305" s="2">
-        <v>0.59195566177368164</v>
-      </c>
+      <c r="C305" s="2"/>
       <c r="D305" s="2">
         <v>0.47426274418830872</v>
       </c>
-      <c r="E305" s="2">
-        <v>0.23976373672485352</v>
-      </c>
+      <c r="E305" s="2"/>
     </row>
     <row r="306">
       <c r="A306" s="1">
@@ -4430,15 +3634,11 @@
       <c r="B306" s="2">
         <v>1.3864729404449463</v>
       </c>
-      <c r="C306" s="2">
-        <v>1.2759895324707031</v>
-      </c>
+      <c r="C306" s="2"/>
       <c r="D306" s="2">
         <v>0.60978662967681885</v>
       </c>
-      <c r="E306" s="2">
-        <v>0.39023444056510925</v>
-      </c>
+      <c r="E306" s="2"/>
     </row>
     <row r="307">
       <c r="A307" s="1">
@@ -4447,15 +3647,11 @@
       <c r="B307" s="2">
         <v>-0.80624306201934814</v>
       </c>
-      <c r="C307" s="2">
-        <v>-1.1224753856658936</v>
-      </c>
+      <c r="C307" s="2"/>
       <c r="D307" s="2">
         <v>0.6389230489730835</v>
       </c>
-      <c r="E307" s="2">
-        <v>0.41447257995605469</v>
-      </c>
+      <c r="E307" s="2"/>
     </row>
     <row r="308">
       <c r="A308" s="1">
@@ -4464,15 +3660,11 @@
       <c r="B308" s="2">
         <v>0.39992815256118774</v>
       </c>
-      <c r="C308" s="2">
-        <v>0.34508916735649109</v>
-      </c>
+      <c r="C308" s="2"/>
       <c r="D308" s="2">
         <v>0.77143740653991699</v>
       </c>
-      <c r="E308" s="2">
-        <v>0.55842787027359009</v>
-      </c>
+      <c r="E308" s="2"/>
     </row>
     <row r="309">
       <c r="A309" s="1">
@@ -4481,15 +3673,11 @@
       <c r="B309" s="2">
         <v>-0.48461303114891052</v>
       </c>
-      <c r="C309" s="2">
-        <v>-0.71635591983795166</v>
-      </c>
+      <c r="C309" s="2"/>
       <c r="D309" s="2">
         <v>0.7330508828163147</v>
       </c>
-      <c r="E309" s="2">
-        <v>0.60790199041366577</v>
-      </c>
+      <c r="E309" s="2"/>
     </row>
     <row r="310">
       <c r="A310" s="1">
@@ -4498,15 +3686,11 @@
       <c r="B310" s="2">
         <v>1.0140981674194336</v>
       </c>
-      <c r="C310" s="2">
-        <v>0.87997108697891235</v>
-      </c>
+      <c r="C310" s="2"/>
       <c r="D310" s="2">
         <v>0.75815600156784058</v>
       </c>
-      <c r="E310" s="2">
-        <v>0.70406079292297363</v>
-      </c>
+      <c r="E310" s="2"/>
     </row>
     <row r="311">
       <c r="A311" s="1">
@@ -4515,15 +3699,11 @@
       <c r="B311" s="2">
         <v>1.5714768171310425</v>
       </c>
-      <c r="C311" s="2">
-        <v>1.5226294994354248</v>
-      </c>
+      <c r="C311" s="2"/>
       <c r="D311" s="2">
         <v>0.68625617027282715</v>
       </c>
-      <c r="E311" s="2">
-        <v>0.61144167184829712</v>
-      </c>
+      <c r="E311" s="2"/>
     </row>
     <row r="312">
       <c r="A312" s="1">
@@ -4532,15 +3712,11 @@
       <c r="B312" s="2">
         <v>1.6113471984863281</v>
       </c>
-      <c r="C312" s="2">
-        <v>1.6873468160629272</v>
-      </c>
+      <c r="C312" s="2"/>
       <c r="D312" s="2">
         <v>0.81754857301712036</v>
       </c>
-      <c r="E312" s="2">
-        <v>0.75736212730407715</v>
-      </c>
+      <c r="E312" s="2"/>
     </row>
     <row r="313">
       <c r="A313" s="1">
@@ -4549,15 +3725,11 @@
       <c r="B313" s="2">
         <v>0.56805253028869629</v>
       </c>
-      <c r="C313" s="2">
-        <v>1.006967306137085</v>
-      </c>
+      <c r="C313" s="2"/>
       <c r="D313" s="2">
         <v>0.93562400341033936</v>
       </c>
-      <c r="E313" s="2">
-        <v>0.86657577753067017</v>
-      </c>
+      <c r="E313" s="2"/>
     </row>
     <row r="314">
       <c r="A314" s="1">
@@ -4566,15 +3738,11 @@
       <c r="B314" s="2">
         <v>1.5628843307495117</v>
       </c>
-      <c r="C314" s="2">
-        <v>1.4573849439620972</v>
-      </c>
+      <c r="C314" s="2"/>
       <c r="D314" s="2">
         <v>1.0999102592468262</v>
       </c>
-      <c r="E314" s="2">
-        <v>1.023052453994751</v>
-      </c>
+      <c r="E314" s="2"/>
     </row>
     <row r="315">
       <c r="A315" s="1">
@@ -4583,15 +3751,11 @@
       <c r="B315" s="2">
         <v>0.73937433958053589</v>
       </c>
-      <c r="C315" s="2">
-        <v>0.44241747260093689</v>
-      </c>
+      <c r="C315" s="2"/>
       <c r="D315" s="2">
         <v>1.1503597497940063</v>
       </c>
-      <c r="E315" s="2">
-        <v>1.0446130037307739</v>
-      </c>
+      <c r="E315" s="2"/>
     </row>
     <row r="316">
       <c r="A316" s="1">
@@ -4600,15 +3764,11 @@
       <c r="B316" s="2">
         <v>0.37538883090019226</v>
       </c>
-      <c r="C316" s="2">
-        <v>0.19080853462219238</v>
-      </c>
+      <c r="C316" s="2"/>
       <c r="D316" s="2">
         <v>1.1143773794174194</v>
       </c>
-      <c r="E316" s="2">
-        <v>1.002194881439209</v>
-      </c>
+      <c r="E316" s="2"/>
     </row>
     <row r="317">
       <c r="A317" s="1">
@@ -4617,15 +3777,11 @@
       <c r="B317" s="2">
         <v>1.46260666847229</v>
       </c>
-      <c r="C317" s="2">
-        <v>1.3280123472213745</v>
-      </c>
+      <c r="C317" s="2"/>
       <c r="D317" s="2">
         <v>0.94556421041488647</v>
       </c>
-      <c r="E317" s="2">
-        <v>0.81461447477340698</v>
-      </c>
+      <c r="E317" s="2"/>
     </row>
     <row r="318">
       <c r="A318" s="1">
@@ -4634,15 +3790,11 @@
       <c r="B318" s="2">
         <v>0.99396336078643799</v>
       </c>
-      <c r="C318" s="2">
-        <v>0.69193416833877563</v>
-      </c>
+      <c r="C318" s="2"/>
       <c r="D318" s="2">
         <v>0.9559025764465332</v>
       </c>
-      <c r="E318" s="2">
-        <v>0.73759037256240845</v>
-      </c>
+      <c r="E318" s="2"/>
     </row>
     <row r="319">
       <c r="A319" s="1">
@@ -4651,15 +3803,11 @@
       <c r="B319" s="2">
         <v>1.4681437015533447</v>
       </c>
-      <c r="C319" s="2">
-        <v>1.0740162134170532</v>
-      </c>
+      <c r="C319" s="2"/>
       <c r="D319" s="2">
         <v>0.93070501089096069</v>
       </c>
-      <c r="E319" s="2">
-        <v>0.68168771266937256</v>
-      </c>
+      <c r="E319" s="2"/>
     </row>
     <row r="320">
       <c r="A320" s="1">
@@ -4668,15 +3816,11 @@
       <c r="B320" s="2">
         <v>1.2476351261138916</v>
       </c>
-      <c r="C320" s="2">
-        <v>1.1408666372299194</v>
-      </c>
+      <c r="C320" s="2"/>
       <c r="D320" s="2">
         <v>1.000348687171936</v>
       </c>
-      <c r="E320" s="2">
-        <v>0.76055121421813965</v>
-      </c>
+      <c r="E320" s="2"/>
     </row>
     <row r="321">
       <c r="A321" s="1">
@@ -4685,15 +3829,11 @@
       <c r="B321" s="2">
         <v>0.092029169201850891</v>
       </c>
-      <c r="C321" s="2">
-        <v>-0.00087755493586882949</v>
-      </c>
+      <c r="C321" s="2"/>
       <c r="D321" s="2">
         <v>1.0339717864990234</v>
       </c>
-      <c r="E321" s="2">
-        <v>0.87148898839950562</v>
-      </c>
+      <c r="E321" s="2"/>
     </row>
     <row r="322">
       <c r="A322" s="1">
@@ -4702,15 +3842,11 @@
       <c r="B322" s="2">
         <v>0.66109788417816162</v>
       </c>
-      <c r="C322" s="2">
-        <v>0.31375044584274292</v>
-      </c>
+      <c r="C322" s="2"/>
       <c r="D322" s="2">
         <v>0.93579024076461792</v>
       </c>
-      <c r="E322" s="2">
-        <v>0.76535683870315552</v>
-      </c>
+      <c r="E322" s="2"/>
     </row>
     <row r="323">
       <c r="A323" s="1">
@@ -4719,15 +3855,11 @@
       <c r="B323" s="2">
         <v>1.3361060619354248</v>
       </c>
-      <c r="C323" s="2">
-        <v>0.95426100492477417</v>
-      </c>
+      <c r="C323" s="2"/>
       <c r="D323" s="2">
         <v>0.92109745740890503</v>
       </c>
-      <c r="E323" s="2">
-        <v>0.76116359233856201</v>
-      </c>
+      <c r="E323" s="2"/>
     </row>
     <row r="324">
       <c r="A324" s="1">
@@ -4736,15 +3868,11 @@
       <c r="B324" s="2">
         <v>1.3661671876907349</v>
       </c>
-      <c r="C324" s="2">
-        <v>1.1521888971328735</v>
-      </c>
+      <c r="C324" s="2"/>
       <c r="D324" s="2">
         <v>0.85225611925125122</v>
       </c>
-      <c r="E324" s="2">
-        <v>0.72567915916442871</v>
-      </c>
+      <c r="E324" s="2"/>
     </row>
     <row r="325">
       <c r="A325" s="1">
@@ -4753,15 +3881,11 @@
       <c r="B325" s="2">
         <v>0.67799729108810425</v>
       </c>
-      <c r="C325" s="2">
-        <v>1.18924880027771</v>
-      </c>
+      <c r="C325" s="2"/>
       <c r="D325" s="2">
         <v>0.81152629852294922</v>
       </c>
-      <c r="E325" s="2">
-        <v>0.69232404232025146</v>
-      </c>
+      <c r="E325" s="2"/>
     </row>
     <row r="326">
       <c r="A326" s="1">
@@ -4770,15 +3894,11 @@
       <c r="B326" s="2">
         <v>0.5789724588394165</v>
       </c>
-      <c r="C326" s="2">
-        <v>0.37282314896583557</v>
-      </c>
+      <c r="C326" s="2"/>
       <c r="D326" s="2">
         <v>0.93742728233337402</v>
       </c>
-      <c r="E326" s="2">
-        <v>0.81334578990936279</v>
-      </c>
+      <c r="E326" s="2"/>
     </row>
     <row r="327">
       <c r="A327" s="1">
@@ -4787,15 +3907,11 @@
       <c r="B327" s="2">
         <v>0.8617284893989563</v>
       </c>
-      <c r="C327" s="2">
-        <v>0.65419453382492065</v>
-      </c>
+      <c r="C327" s="2"/>
       <c r="D327" s="2">
         <v>0.97826093435287476</v>
       </c>
-      <c r="E327" s="2">
-        <v>0.86945265531539917</v>
-      </c>
+      <c r="E327" s="2"/>
     </row>
     <row r="328">
       <c r="A328" s="1">
@@ -4804,15 +3920,11 @@
       <c r="B328" s="2">
         <v>0.84857147932052612</v>
       </c>
-      <c r="C328" s="2">
-        <v>0.75465631484985352</v>
-      </c>
+      <c r="C328" s="2"/>
       <c r="D328" s="2">
         <v>0.93273746967315674</v>
       </c>
-      <c r="E328" s="2">
-        <v>0.86889553070068359</v>
-      </c>
+      <c r="E328" s="2"/>
     </row>
     <row r="329">
       <c r="A329" s="1">
@@ -4821,15 +3933,11 @@
       <c r="B329" s="2">
         <v>0.88106644153594971</v>
       </c>
-      <c r="C329" s="2">
-        <v>0.84067100286483765</v>
-      </c>
+      <c r="C329" s="2"/>
       <c r="D329" s="2">
         <v>0.82271802425384521</v>
       </c>
-      <c r="E329" s="2">
-        <v>0.79350042343139648</v>
-      </c>
+      <c r="E329" s="2"/>
     </row>
     <row r="330">
       <c r="A330" s="1">
@@ -4838,15 +3946,11 @@
       <c r="B330" s="2">
         <v>1.2251380681991577</v>
       </c>
-      <c r="C330" s="2">
-        <v>1.0883182287216187</v>
-      </c>
+      <c r="C330" s="2"/>
       <c r="D330" s="2">
         <v>0.85231399536132812</v>
       </c>
-      <c r="E330" s="2">
-        <v>0.7465059757232666</v>
-      </c>
+      <c r="E330" s="2"/>
     </row>
     <row r="331">
       <c r="A331" s="1">
@@ -4855,15 +3959,11 @@
       <c r="B331" s="2">
         <v>1.0286011695861816</v>
       </c>
-      <c r="C331" s="2">
-        <v>0.81871217489242554</v>
-      </c>
+      <c r="C331" s="2"/>
       <c r="D331" s="2">
         <v>0.89910435676574707</v>
       </c>
-      <c r="E331" s="2">
-        <v>0.80867111682891846</v>
-      </c>
+      <c r="E331" s="2"/>
     </row>
     <row r="332">
       <c r="A332" s="1">
@@ -4872,15 +3972,11 @@
       <c r="B332" s="2">
         <v>0.92639487981796265</v>
       </c>
-      <c r="C332" s="2">
-        <v>0.94924646615982056</v>
-      </c>
+      <c r="C332" s="2"/>
       <c r="D332" s="2">
         <v>0.97743362188339233</v>
       </c>
-      <c r="E332" s="2">
-        <v>0.85973912477493286</v>
-      </c>
+      <c r="E332" s="2"/>
     </row>
     <row r="333">
       <c r="A333" s="1">
@@ -4889,15 +3985,11 @@
       <c r="B333" s="2">
         <v>0.37599179148674011</v>
       </c>
-      <c r="C333" s="2">
-        <v>0.47363311052322388</v>
-      </c>
+      <c r="C333" s="2"/>
       <c r="D333" s="2">
         <v>1.0743964910507202</v>
       </c>
-      <c r="E333" s="2">
-        <v>0.94190371036529541</v>
-      </c>
+      <c r="E333" s="2"/>
     </row>
     <row r="334">
       <c r="A334" s="1">
@@ -4906,15 +3998,11 @@
       <c r="B334" s="2">
         <v>0.94436109066009521</v>
       </c>
-      <c r="C334" s="2">
-        <v>0.76629865169525146</v>
-      </c>
+      <c r="C334" s="2"/>
       <c r="D334" s="2">
         <v>0.97155135869979858</v>
       </c>
-      <c r="E334" s="2">
-        <v>0.79959815740585327</v>
-      </c>
+      <c r="E334" s="2"/>
     </row>
     <row r="335">
       <c r="A335" s="1">
@@ -4923,15 +4011,11 @@
       <c r="B335" s="2">
         <v>1.0000859498977661</v>
       </c>
-      <c r="C335" s="2">
-        <v>0.93230932950973511</v>
-      </c>
+      <c r="C335" s="2"/>
       <c r="D335" s="2">
         <v>1.0137605667114258</v>
       </c>
-      <c r="E335" s="2">
-        <v>0.83588439226150513</v>
-      </c>
+      <c r="E335" s="2"/>
     </row>
     <row r="336">
       <c r="A336" s="1">
@@ -4940,15 +4024,11 @@
       <c r="B336" s="2">
         <v>1.5666918754577637</v>
       </c>
-      <c r="C336" s="2">
-        <v>1.1138069629669189</v>
-      </c>
+      <c r="C336" s="2"/>
       <c r="D336" s="2">
         <v>0.86322373151779175</v>
       </c>
-      <c r="E336" s="2">
-        <v>0.69397157430648804</v>
-      </c>
+      <c r="E336" s="2"/>
     </row>
     <row r="337">
       <c r="A337" s="1">
@@ -4957,15 +4037,11 @@
       <c r="B337" s="2">
         <v>1.7212371826171875</v>
       </c>
-      <c r="C337" s="2">
-        <v>1.4941374063491821</v>
-      </c>
+      <c r="C337" s="2"/>
       <c r="D337" s="2">
         <v>0.95414084196090698</v>
       </c>
-      <c r="E337" s="2">
-        <v>0.76701760292053223</v>
-      </c>
+      <c r="E337" s="2"/>
     </row>
     <row r="338">
       <c r="A338" s="1">
@@ -4974,15 +4050,11 @@
       <c r="B338" s="2">
         <v>-0.04453996941447258</v>
       </c>
-      <c r="C338" s="2">
-        <v>-0.44007870554924011</v>
-      </c>
+      <c r="C338" s="2"/>
       <c r="D338" s="2">
         <v>1.1469392776489258</v>
       </c>
-      <c r="E338" s="2">
-        <v>0.93724614381790161</v>
-      </c>
+      <c r="E338" s="2"/>
     </row>
     <row r="339">
       <c r="A339" s="1">
@@ -4991,15 +4063,11 @@
       <c r="B339" s="2">
         <v>1.6050214767456055</v>
       </c>
-      <c r="C339" s="2">
-        <v>1.4148939847946167</v>
-      </c>
+      <c r="C339" s="2"/>
       <c r="D339" s="2">
         <v>1.1296859979629517</v>
       </c>
-      <c r="E339" s="2">
-        <v>0.89395779371261597</v>
-      </c>
+      <c r="E339" s="2"/>
     </row>
     <row r="340">
       <c r="A340" s="1">
@@ -5008,15 +4076,11 @@
       <c r="B340" s="2">
         <v>-0.32623058557510376</v>
       </c>
-      <c r="C340" s="2">
-        <v>-0.45850294828414917</v>
-      </c>
+      <c r="C340" s="2"/>
       <c r="D340" s="2">
         <v>1.1529141664505005</v>
       </c>
-      <c r="E340" s="2">
-        <v>0.91653072834014893</v>
-      </c>
+      <c r="E340" s="2"/>
     </row>
     <row r="341">
       <c r="A341" s="1">
@@ -5025,15 +4089,11 @@
       <c r="B341" s="2">
         <v>1.7446486949920654</v>
       </c>
-      <c r="C341" s="2">
-        <v>1.6066607236862183</v>
-      </c>
+      <c r="C341" s="2"/>
       <c r="D341" s="2">
         <v>0.88070487976074219</v>
       </c>
-      <c r="E341" s="2">
-        <v>0.62792599201202393</v>
-      </c>
+      <c r="E341" s="2"/>
     </row>
     <row r="342">
       <c r="A342" s="1">
@@ -5042,15 +4102,11 @@
       <c r="B342" s="2">
         <v>2.1111781597137451</v>
       </c>
-      <c r="C342" s="2">
-        <v>2.0056898593902588</v>
-      </c>
+      <c r="C342" s="2"/>
       <c r="D342" s="2">
         <v>0.74200582504272461</v>
       </c>
-      <c r="E342" s="2">
-        <v>0.51640266180038452</v>
-      </c>
+      <c r="E342" s="2"/>
     </row>
     <row r="343">
       <c r="A343" s="1">
@@ -5059,15 +4115,11 @@
       <c r="B343" s="2">
         <v>0.78908157348632812</v>
       </c>
-      <c r="C343" s="2">
-        <v>0.37670367956161499</v>
-      </c>
+      <c r="C343" s="2"/>
       <c r="D343" s="2">
         <v>0.83294153213500977</v>
       </c>
-      <c r="E343" s="2">
-        <v>0.62403368949890137</v>
-      </c>
+      <c r="E343" s="2"/>
     </row>
     <row r="344">
       <c r="A344" s="1">
@@ -5076,15 +4128,11 @@
       <c r="B344" s="2">
         <v>1.209139347076416</v>
       </c>
-      <c r="C344" s="2">
-        <v>1.1354653835296631</v>
-      </c>
+      <c r="C344" s="2"/>
       <c r="D344" s="2">
         <v>0.8226657509803772</v>
       </c>
-      <c r="E344" s="2">
-        <v>0.61523270606994629</v>
-      </c>
+      <c r="E344" s="2"/>
     </row>
     <row r="345">
       <c r="A345" s="1">
@@ -5093,15 +4141,11 @@
       <c r="B345" s="2">
         <v>-0.88319182395935059</v>
       </c>
-      <c r="C345" s="2">
-        <v>-1.4836351871490479</v>
-      </c>
+      <c r="C345" s="2"/>
       <c r="D345" s="2">
         <v>0.9124876856803894</v>
       </c>
-      <c r="E345" s="2">
-        <v>0.69536876678466797</v>
-      </c>
+      <c r="E345" s="2"/>
     </row>
     <row r="346">
       <c r="A346" s="1">
@@ -5110,15 +4154,11 @@
       <c r="B346" s="2">
         <v>0.47294574975967407</v>
       </c>
-      <c r="C346" s="2">
-        <v>0.49042704701423645</v>
-      </c>
+      <c r="C346" s="2"/>
       <c r="D346" s="2">
         <v>0.83863216638565063</v>
       </c>
-      <c r="E346" s="2">
-        <v>0.62233215570449829</v>
-      </c>
+      <c r="E346" s="2"/>
     </row>
     <row r="347">
       <c r="A347" s="1">
@@ -5127,15 +4167,11 @@
       <c r="B347" s="2">
         <v>0.77388107776641846</v>
       </c>
-      <c r="C347" s="2">
-        <v>0.52860063314437866</v>
-      </c>
+      <c r="C347" s="2"/>
       <c r="D347" s="2">
         <v>0.76935845613479614</v>
       </c>
-      <c r="E347" s="2">
-        <v>0.52217066287994385</v>
-      </c>
+      <c r="E347" s="2"/>
     </row>
     <row r="348">
       <c r="A348" s="1">
@@ -5144,15 +4180,11 @@
       <c r="B348" s="2">
         <v>1.5125393867492676</v>
       </c>
-      <c r="C348" s="2">
-        <v>1.3356850147247314</v>
-      </c>
+      <c r="C348" s="2"/>
       <c r="D348" s="2">
         <v>0.84573310613632202</v>
       </c>
-      <c r="E348" s="2">
-        <v>0.62971985340118408</v>
-      </c>
+      <c r="E348" s="2"/>
     </row>
     <row r="349">
       <c r="A349" s="1">
@@ -5161,15 +4193,11 @@
       <c r="B349" s="2">
         <v>0.48216709494590759</v>
       </c>
-      <c r="C349" s="2">
-        <v>0.26272189617156982</v>
-      </c>
+      <c r="C349" s="2"/>
       <c r="D349" s="2">
         <v>0.85027694702148438</v>
       </c>
-      <c r="E349" s="2">
-        <v>0.64445489645004272</v>
-      </c>
+      <c r="E349" s="2"/>
     </row>
     <row r="350">
       <c r="A350" s="1">
@@ -5178,15 +4206,11 @@
       <c r="B350" s="2">
         <v>1.0799490213394165</v>
       </c>
-      <c r="C350" s="2">
-        <v>0.94933122396469116</v>
-      </c>
+      <c r="C350" s="2"/>
       <c r="D350" s="2">
         <v>1.050269603729248</v>
       </c>
-      <c r="E350" s="2">
-        <v>0.94154632091522217</v>
-      </c>
+      <c r="E350" s="2"/>
     </row>
     <row r="351">
       <c r="A351" s="1">
@@ -5195,15 +4219,11 @@
       <c r="B351" s="2">
         <v>1.4877148866653442</v>
       </c>
-      <c r="C351" s="2">
-        <v>1.1042362451553345</v>
-      </c>
+      <c r="C351" s="2"/>
       <c r="D351" s="2">
         <v>1.1629682779312134</v>
       </c>
-      <c r="E351" s="2">
-        <v>1.0574268102645874</v>
-      </c>
+      <c r="E351" s="2"/>
     </row>
     <row r="352">
       <c r="A352" s="1">
@@ -5212,15 +4232,11 @@
       <c r="B352" s="2">
         <v>1.4764531850814819</v>
       </c>
-      <c r="C352" s="2">
-        <v>1.3446465730667114</v>
-      </c>
+      <c r="C352" s="2"/>
       <c r="D352" s="2">
         <v>1.2526540756225586</v>
       </c>
-      <c r="E352" s="2">
-        <v>1.1606042385101318</v>
-      </c>
+      <c r="E352" s="2"/>
     </row>
     <row r="353">
       <c r="A353" s="1">
@@ -5229,15 +4245,11 @@
       <c r="B353" s="2">
         <v>1.250033974647522</v>
       </c>
-      <c r="C353" s="2">
-        <v>1.268080472946167</v>
-      </c>
+      <c r="C353" s="2"/>
       <c r="D353" s="2">
         <v>1.2666057348251343</v>
       </c>
-      <c r="E353" s="2">
-        <v>1.1968966722488403</v>
-      </c>
+      <c r="E353" s="2"/>
     </row>
     <row r="354">
       <c r="A354" s="1">
@@ -5246,15 +4258,11 @@
       <c r="B354" s="2">
         <v>0.91674226522445679</v>
       </c>
-      <c r="C354" s="2">
-        <v>1.190187931060791</v>
-      </c>
+      <c r="C354" s="2"/>
       <c r="D354" s="2">
         <v>1.327772855758667</v>
       </c>
-      <c r="E354" s="2">
-        <v>1.2599914073944092</v>
-      </c>
+      <c r="E354" s="2"/>
     </row>
     <row r="355">
       <c r="A355" s="1">
@@ -5263,15 +4271,11 @@
       <c r="B355" s="2">
         <v>1.4872337579727173</v>
       </c>
-      <c r="C355" s="2">
-        <v>1.5333511829376221</v>
-      </c>
+      <c r="C355" s="2"/>
       <c r="D355" s="2">
         <v>1.3739309310913086</v>
       </c>
-      <c r="E355" s="2">
-        <v>1.3115658760070801</v>
-      </c>
+      <c r="E355" s="2"/>
     </row>
     <row r="356">
       <c r="A356" s="1">
@@ -5280,15 +4284,11 @@
       <c r="B356" s="2">
         <v>1.5810526609420776</v>
       </c>
-      <c r="C356" s="2">
-        <v>1.4571973085403442</v>
-      </c>
+      <c r="C356" s="2"/>
       <c r="D356" s="2">
         <v>1.1782811880111694</v>
       </c>
-      <c r="E356" s="2">
-        <v>1.1484150886535645</v>
-      </c>
+      <c r="E356" s="2"/>
     </row>
     <row r="357">
       <c r="A357" s="1">
@@ -5297,15 +4297,11 @@
       <c r="B357" s="2">
         <v>1.6381043195724487</v>
       </c>
-      <c r="C357" s="2">
-        <v>1.6623167991638184</v>
-      </c>
+      <c r="C357" s="2"/>
       <c r="D357" s="2">
         <v>1.1397476196289062</v>
       </c>
-      <c r="E357" s="2">
-        <v>1.1053452491760254</v>
-      </c>
+      <c r="E357" s="2"/>
     </row>
     <row r="358">
       <c r="A358" s="1">
@@ -5314,15 +4310,11 @@
       <c r="B358" s="2">
         <v>1.0326718091964722</v>
       </c>
-      <c r="C358" s="2">
-        <v>0.83057540655136108</v>
-      </c>
+      <c r="C358" s="2"/>
       <c r="D358" s="2">
         <v>1.1061015129089355</v>
       </c>
-      <c r="E358" s="2">
-        <v>1.0463287830352783</v>
-      </c>
+      <c r="E358" s="2"/>
     </row>
     <row r="359">
       <c r="A359" s="1">
@@ -5331,15 +4323,11 @@
       <c r="B359" s="2">
         <v>1.4953709840774536</v>
       </c>
-      <c r="C359" s="2">
-        <v>1.4135009050369263</v>
-      </c>
+      <c r="C359" s="2"/>
       <c r="D359" s="2">
         <v>1.0519428253173828</v>
       </c>
-      <c r="E359" s="2">
-        <v>0.94903564453125</v>
-      </c>
+      <c r="E359" s="2"/>
     </row>
     <row r="360">
       <c r="A360" s="1">
@@ -5348,15 +4336,11 @@
       <c r="B360" s="2">
         <v>-0.27313265204429626</v>
       </c>
-      <c r="C360" s="2">
-        <v>-0.3641202449798584</v>
-      </c>
+      <c r="C360" s="2"/>
       <c r="D360" s="2">
         <v>0.94394612312316895</v>
       </c>
-      <c r="E360" s="2">
-        <v>0.83029556274414062</v>
-      </c>
+      <c r="E360" s="2"/>
     </row>
     <row r="361">
       <c r="A361" s="1">
@@ -5365,15 +4349,11 @@
       <c r="B361" s="2">
         <v>1.1296514272689819</v>
       </c>
-      <c r="C361" s="2">
-        <v>0.95701694488525391</v>
-      </c>
+      <c r="C361" s="2"/>
       <c r="D361" s="2">
         <v>0.76388567686080933</v>
       </c>
-      <c r="E361" s="2">
-        <v>0.72353672981262207</v>
-      </c>
+      <c r="E361" s="2"/>
     </row>
     <row r="362">
       <c r="A362" s="1">
@@ -5382,15 +4362,11 @@
       <c r="B362" s="2">
         <v>0.9472193717956543</v>
       </c>
-      <c r="C362" s="2">
-        <v>0.73693317174911499</v>
-      </c>
+      <c r="C362" s="2"/>
       <c r="D362" s="2">
         <v>0.54172438383102417</v>
       </c>
-      <c r="E362" s="2">
-        <v>0.47640141844749451</v>
-      </c>
+      <c r="E362" s="2"/>
     </row>
     <row r="363">
       <c r="A363" s="1">
@@ -5399,15 +4375,11 @@
       <c r="B363" s="2">
         <v>0.42931383848190308</v>
       </c>
-      <c r="C363" s="2">
-        <v>0.31454935669898987</v>
-      </c>
+      <c r="C363" s="2"/>
       <c r="D363" s="2">
         <v>0.4697323739528656</v>
       </c>
-      <c r="E363" s="2">
-        <v>0.39300641417503357</v>
-      </c>
+      <c r="E363" s="2"/>
     </row>
     <row r="364">
       <c r="A364" s="1">
@@ -5416,15 +4388,11 @@
       <c r="B364" s="2">
         <v>0.51526331901550293</v>
       </c>
-      <c r="C364" s="2">
-        <v>0.46469020843505859</v>
-      </c>
+      <c r="C364" s="2"/>
       <c r="D364" s="2">
         <v>0.28652283549308777</v>
       </c>
-      <c r="E364" s="2">
-        <v>0.19845953583717346</v>
-      </c>
+      <c r="E364" s="2"/>
     </row>
     <row r="365">
       <c r="A365" s="1">
@@ -5433,15 +4401,11 @@
       <c r="B365" s="2">
         <v>-0.039491485804319382</v>
       </c>
-      <c r="C365" s="2">
-        <v>0.49636822938919067</v>
-      </c>
+      <c r="C365" s="2"/>
       <c r="D365" s="2">
         <v>0.40503662824630737</v>
       </c>
-      <c r="E365" s="2">
-        <v>0.31291726231575012</v>
-      </c>
+      <c r="E365" s="2"/>
     </row>
     <row r="366">
       <c r="A366" s="1">
@@ -5450,15 +4414,11 @@
       <c r="B366" s="2">
         <v>-0.3613470196723938</v>
       </c>
-      <c r="C366" s="2">
-        <v>-0.56190133094787598</v>
-      </c>
+      <c r="C366" s="2"/>
       <c r="D366" s="2">
         <v>0.3030422031879425</v>
       </c>
-      <c r="E366" s="2">
-        <v>0.20293912291526794</v>
-      </c>
+      <c r="E366" s="2"/>
     </row>
     <row r="367">
       <c r="A367" s="1">
@@ -5467,15 +4427,11 @@
       <c r="B367" s="2">
         <v>0.38474345207214355</v>
       </c>
-      <c r="C367" s="2">
-        <v>0.08002038300037384</v>
-      </c>
+      <c r="C367" s="2"/>
       <c r="D367" s="2">
         <v>0.192133828997612</v>
       </c>
-      <c r="E367" s="2">
-        <v>0.089006736874580383</v>
-      </c>
+      <c r="E367" s="2"/>
     </row>
     <row r="368">
       <c r="A368" s="1">
@@ -5484,15 +4440,11 @@
       <c r="B368" s="2">
         <v>-0.15351486206054688</v>
       </c>
-      <c r="C368" s="2">
-        <v>-0.33742085099220276</v>
-      </c>
+      <c r="C368" s="2"/>
       <c r="D368" s="2">
         <v>0.21625897288322449</v>
       </c>
-      <c r="E368" s="2">
-        <v>0.10970260947942734</v>
-      </c>
+      <c r="E368" s="2"/>
     </row>
     <row r="369">
       <c r="A369" s="1">
@@ -5501,15 +4453,11 @@
       <c r="B369" s="2">
         <v>0.79349154233932495</v>
       </c>
-      <c r="C369" s="2">
-        <v>0.66599923372268677</v>
-      </c>
+      <c r="C369" s="2"/>
       <c r="D369" s="2">
         <v>0.1829356849193573</v>
       </c>
-      <c r="E369" s="2">
-        <v>0.055508371442556381</v>
-      </c>
+      <c r="E369" s="2"/>
     </row>
     <row r="370">
       <c r="A370" s="1">
@@ -5518,15 +4466,11 @@
       <c r="B370" s="2">
         <v>0.21170161664485931</v>
       </c>
-      <c r="C370" s="2">
-        <v>-0.032786339521408081</v>
-      </c>
+      <c r="C370" s="2"/>
       <c r="D370" s="2">
         <v>0.33001428842544556</v>
       </c>
-      <c r="E370" s="2">
-        <v>0.13136550784111023</v>
-      </c>
+      <c r="E370" s="2"/>
     </row>
     <row r="371">
       <c r="A371" s="1">
@@ -5535,15 +4479,11 @@
       <c r="B371" s="2">
         <v>-0.05095590278506279</v>
       </c>
-      <c r="C371" s="2">
-        <v>-0.28845828771591187</v>
-      </c>
+      <c r="C371" s="2"/>
       <c r="D371" s="2">
         <v>0.45911511778831482</v>
       </c>
-      <c r="E371" s="2">
-        <v>0.28939399123191833</v>
-      </c>
+      <c r="E371" s="2"/>
     </row>
     <row r="372">
       <c r="A372" s="1">
@@ -5552,15 +4492,11 @@
       <c r="B372" s="2">
         <v>0.64644014835357666</v>
       </c>
-      <c r="C372" s="2">
-        <v>0.50081223249435425</v>
-      </c>
+      <c r="C372" s="2"/>
       <c r="D372" s="2">
         <v>0.4512697160243988</v>
       </c>
-      <c r="E372" s="2">
-        <v>0.2955329418182373</v>
-      </c>
+      <c r="E372" s="2"/>
     </row>
     <row r="373">
       <c r="A373" s="1">
@@ -5569,15 +4505,11 @@
       <c r="B373" s="2">
         <v>0.21535365283489227</v>
       </c>
-      <c r="C373" s="2">
-        <v>-0.023057937622070312</v>
-      </c>
+      <c r="C373" s="2"/>
       <c r="D373" s="2">
         <v>0.61973947286605835</v>
       </c>
-      <c r="E373" s="2">
-        <v>0.45697581768035889</v>
-      </c>
+      <c r="E373" s="2"/>
     </row>
     <row r="374">
       <c r="A374" s="1">
@@ -5586,15 +4518,11 @@
       <c r="B374" s="2">
         <v>1.2842159271240234</v>
       </c>
-      <c r="C374" s="2">
-        <v>1.1790825128555298</v>
-      </c>
+      <c r="C374" s="2"/>
       <c r="D374" s="2">
         <v>0.61039769649505615</v>
       </c>
-      <c r="E374" s="2">
-        <v>0.44167733192443848</v>
-      </c>
+      <c r="E374" s="2"/>
     </row>
     <row r="375">
       <c r="A375" s="1">
@@ -5603,15 +4531,11 @@
       <c r="B375" s="2">
         <v>0.8005605936050415</v>
       </c>
-      <c r="C375" s="2">
-        <v>0.8603549599647522</v>
-      </c>
+      <c r="C375" s="2"/>
       <c r="D375" s="2">
         <v>0.63082516193389893</v>
       </c>
-      <c r="E375" s="2">
-        <v>0.47000139951705933</v>
-      </c>
+      <c r="E375" s="2"/>
     </row>
     <row r="376">
       <c r="A376" s="1">
@@ -5620,15 +4544,11 @@
       <c r="B376" s="2">
         <v>0.31413483619689941</v>
       </c>
-      <c r="C376" s="2">
-        <v>0.13527095317840576</v>
-      </c>
+      <c r="C376" s="2"/>
       <c r="D376" s="2">
         <v>0.62528997659683228</v>
       </c>
-      <c r="E376" s="2">
-        <v>0.49275863170623779</v>
-      </c>
+      <c r="E376" s="2"/>
     </row>
     <row r="377">
       <c r="A377" s="1">
@@ -5637,15 +4557,11 @@
       <c r="B377" s="2">
         <v>1.3627126216888428</v>
       </c>
-      <c r="C377" s="2">
-        <v>1.1155649423599243</v>
-      </c>
+      <c r="C377" s="2"/>
       <c r="D377" s="2">
         <v>0.5664517879486084</v>
       </c>
-      <c r="E377" s="2">
-        <v>0.43640989065170288</v>
-      </c>
+      <c r="E377" s="2"/>
     </row>
     <row r="378">
       <c r="A378" s="1">
@@ -5654,15 +4570,11 @@
       <c r="B378" s="2">
         <v>0.70941591262817383</v>
       </c>
-      <c r="C378" s="2">
-        <v>0.52831292152404785</v>
-      </c>
+      <c r="C378" s="2"/>
       <c r="D378" s="2">
         <v>0.59306252002716064</v>
       </c>
-      <c r="E378" s="2">
-        <v>0.49293631315231323</v>
-      </c>
+      <c r="E378" s="2"/>
     </row>
     <row r="379">
       <c r="A379" s="1">
@@ -5671,15 +4583,11 @@
       <c r="B379" s="2">
         <v>0.39554858207702637</v>
       </c>
-      <c r="C379" s="2">
-        <v>0.22213034331798553</v>
-      </c>
+      <c r="C379" s="2"/>
       <c r="D379" s="2">
         <v>0.44809642434120178</v>
       </c>
-      <c r="E379" s="2">
-        <v>0.342103511095047</v>
-      </c>
+      <c r="E379" s="2"/>
     </row>
     <row r="380">
       <c r="A380" s="1">
@@ -5688,15 +4596,11 @@
       <c r="B380" s="2">
         <v>-0.10077229142189026</v>
       </c>
-      <c r="C380" s="2">
-        <v>-0.083643123507499695</v>
-      </c>
+      <c r="C380" s="2"/>
       <c r="D380" s="2">
         <v>0.40597635507583618</v>
       </c>
-      <c r="E380" s="2">
-        <v>0.26746875047683716</v>
-      </c>
+      <c r="E380" s="2"/>
     </row>
     <row r="381">
       <c r="A381" s="1">
@@ -5705,15 +4609,11 @@
       <c r="B381" s="2">
         <v>0.11689631640911102</v>
       </c>
-      <c r="C381" s="2">
-        <v>-0.0063264518976211548</v>
-      </c>
+      <c r="C381" s="2"/>
       <c r="D381" s="2">
         <v>0.44833150506019592</v>
       </c>
-      <c r="E381" s="2">
-        <v>0.30511674284934998</v>
-      </c>
+      <c r="E381" s="2"/>
     </row>
     <row r="382">
       <c r="A382" s="1">
@@ -5722,15 +4622,11 @@
       <c r="B382" s="2">
         <v>0.45485028624534607</v>
       </c>
-      <c r="C382" s="2">
-        <v>0.4856797456741333</v>
-      </c>
+      <c r="C382" s="2"/>
       <c r="D382" s="2">
         <v>0.29954487085342407</v>
       </c>
-      <c r="E382" s="2">
-        <v>0.10597763955593109</v>
-      </c>
+      <c r="E382" s="2"/>
     </row>
     <row r="383">
       <c r="A383" s="1">
@@ -5739,15 +4635,11 @@
       <c r="B383" s="2">
         <v>-0.020478913560509682</v>
       </c>
-      <c r="C383" s="2">
-        <v>-0.17841270565986633</v>
-      </c>
+      <c r="C383" s="2"/>
       <c r="D383" s="2">
         <v>0.3782193660736084</v>
       </c>
-      <c r="E383" s="2">
-        <v>0.18375280499458313</v>
-      </c>
+      <c r="E383" s="2"/>
     </row>
     <row r="384">
       <c r="A384" s="1">
@@ -5756,15 +4648,11 @@
       <c r="B384" s="2">
         <v>0.42147979140281677</v>
       </c>
-      <c r="C384" s="2">
-        <v>0.18864218890666962</v>
-      </c>
+      <c r="C384" s="2"/>
       <c r="D384" s="2">
         <v>0.33594030141830444</v>
       </c>
-      <c r="E384" s="2">
-        <v>0.12297047674655914</v>
-      </c>
+      <c r="E384" s="2"/>
     </row>
     <row r="385">
       <c r="A385" s="1">
@@ -5773,15 +4661,11 @@
       <c r="B385" s="2">
         <v>0.6953311562538147</v>
       </c>
-      <c r="C385" s="2">
-        <v>0.47410276532173157</v>
-      </c>
+      <c r="C385" s="2"/>
       <c r="D385" s="2">
         <v>0.46171224117279053</v>
       </c>
-      <c r="E385" s="2">
-        <v>0.23441576957702637</v>
-      </c>
+      <c r="E385" s="2"/>
     </row>
     <row r="386">
       <c r="A386" s="1">
@@ -5790,15 +4674,11 @@
       <c r="B386" s="2">
         <v>0.023632992058992386</v>
       </c>
-      <c r="C386" s="2">
-        <v>-0.67668694257736206</v>
-      </c>
+      <c r="C386" s="2"/>
       <c r="D386" s="2">
         <v>0.57530373334884644</v>
       </c>
-      <c r="E386" s="2">
-        <v>0.3378925621509552</v>
-      </c>
+      <c r="E386" s="2"/>
     </row>
     <row r="387">
       <c r="A387" s="1">
@@ -5807,15 +4687,11 @@
       <c r="B387" s="2">
         <v>1.4174864292144775</v>
       </c>
-      <c r="C387" s="2">
-        <v>1.2282894849777222</v>
-      </c>
+      <c r="C387" s="2"/>
       <c r="D387" s="2">
         <v>0.53660774230957031</v>
       </c>
-      <c r="E387" s="2">
-        <v>0.24731849133968353</v>
-      </c>
+      <c r="E387" s="2"/>
     </row>
     <row r="388">
       <c r="A388" s="1">
@@ -5824,15 +4700,11 @@
       <c r="B388" s="2">
         <v>0.01503694336861372</v>
       </c>
-      <c r="C388" s="2">
-        <v>-0.32491067051887512</v>
-      </c>
+      <c r="C388" s="2"/>
       <c r="D388" s="2">
         <v>0.63792628049850464</v>
       </c>
-      <c r="E388" s="2">
-        <v>0.36836981773376465</v>
-      </c>
+      <c r="E388" s="2"/>
     </row>
     <row r="389">
       <c r="A389" s="1">
@@ -5841,15 +4713,11 @@
       <c r="B389" s="2">
         <v>1.0311752557754517</v>
       </c>
-      <c r="C389" s="2">
-        <v>0.91936451196670532</v>
-      </c>
+      <c r="C389" s="2"/>
       <c r="D389" s="2">
         <v>0.74791854619979858</v>
       </c>
-      <c r="E389" s="2">
-        <v>0.52182340621948242</v>
-      </c>
+      <c r="E389" s="2"/>
     </row>
     <row r="390">
       <c r="A390" s="1">
@@ -5858,15 +4726,11 @@
       <c r="B390" s="2">
         <v>1.1392196416854858</v>
       </c>
-      <c r="C390" s="2">
-        <v>0.9249647855758667</v>
-      </c>
+      <c r="C390" s="2"/>
       <c r="D390" s="2">
         <v>0.80796927213668823</v>
       </c>
-      <c r="E390" s="2">
-        <v>0.59228140115737915</v>
-      </c>
+      <c r="E390" s="2"/>
     </row>
     <row r="391">
       <c r="A391" s="1">
@@ -5875,15 +4739,11 @@
       <c r="B391" s="2">
         <v>0.10658663511276245</v>
       </c>
-      <c r="C391" s="2">
-        <v>-0.32948699593544006</v>
-      </c>
+      <c r="C391" s="2"/>
       <c r="D391" s="2">
         <v>0.79914486408233643</v>
       </c>
-      <c r="E391" s="2">
-        <v>0.74695205688476562</v>
-      </c>
+      <c r="E391" s="2"/>
     </row>
     <row r="392">
       <c r="A392" s="1">
@@ -5892,15 +4752,11 @@
       <c r="B392" s="2">
         <v>0.891387939453125</v>
       </c>
-      <c r="C392" s="2">
-        <v>0.9110492467880249</v>
-      </c>
+      <c r="C392" s="2"/>
       <c r="D392" s="2">
         <v>0.70701056718826294</v>
       </c>
-      <c r="E392" s="2">
-        <v>0.65095484256744385</v>
-      </c>
+      <c r="E392" s="2"/>
     </row>
     <row r="393">
       <c r="A393" s="1">
@@ -5909,15 +4765,11 @@
       <c r="B393" s="2">
         <v>1.4114097356796265</v>
       </c>
-      <c r="C393" s="2">
-        <v>1.569724440574646</v>
-      </c>
+      <c r="C393" s="2"/>
       <c r="D393" s="2">
         <v>0.74123650789260864</v>
       </c>
-      <c r="E393" s="2">
-        <v>0.68657439947128296</v>
-      </c>
+      <c r="E393" s="2"/>
     </row>
     <row r="394">
       <c r="A394" s="1">
@@ -5926,15 +4778,11 @@
       <c r="B394" s="2">
         <v>1.2357876300811768</v>
       </c>
-      <c r="C394" s="2">
-        <v>1.1082248687744141</v>
-      </c>
+      <c r="C394" s="2"/>
       <c r="D394" s="2">
         <v>0.6642032265663147</v>
       </c>
-      <c r="E394" s="2">
-        <v>0.59915739297866821</v>
-      </c>
+      <c r="E394" s="2"/>
     </row>
     <row r="395">
       <c r="A395" s="1">
@@ -5943,15 +4791,11 @@
       <c r="B395" s="2">
         <v>-0.055786550045013428</v>
       </c>
-      <c r="C395" s="2">
-        <v>0.71534907817840576</v>
-      </c>
+      <c r="C395" s="2"/>
       <c r="D395" s="2">
         <v>0.66620290279388428</v>
       </c>
-      <c r="E395" s="2">
-        <v>0.61939144134521484</v>
-      </c>
+      <c r="E395" s="2"/>
     </row>
     <row r="396">
       <c r="A396" s="1">
@@ -5960,15 +4804,11 @@
       <c r="B396" s="2">
         <v>0.58827769756317139</v>
       </c>
-      <c r="C396" s="2">
-        <v>0.36431404948234558</v>
-      </c>
+      <c r="C396" s="2"/>
       <c r="D396" s="2">
         <v>0.69698220491409302</v>
       </c>
-      <c r="E396" s="2">
-        <v>0.6600068211555481</v>
-      </c>
+      <c r="E396" s="2"/>
     </row>
     <row r="397">
       <c r="A397" s="1">
@@ -5977,15 +4817,11 @@
       <c r="B397" s="2">
         <v>0.32307064533233643</v>
       </c>
-      <c r="C397" s="2">
-        <v>-0.004334284458309412</v>
-      </c>
+      <c r="C397" s="2"/>
       <c r="D397" s="2">
         <v>0.68773192167282104</v>
       </c>
-      <c r="E397" s="2">
-        <v>0.6352696418762207</v>
-      </c>
+      <c r="E397" s="2"/>
     </row>
     <row r="398">
       <c r="A398" s="1">
@@ -5994,15 +4830,11 @@
       <c r="B398" s="2">
         <v>0.33787578344345093</v>
       </c>
-      <c r="C398" s="2">
-        <v>0.1326114684343338</v>
-      </c>
+      <c r="C398" s="2"/>
       <c r="D398" s="2">
         <v>0.50613391399383545</v>
       </c>
-      <c r="E398" s="2">
-        <v>0.40068092942237854</v>
-      </c>
+      <c r="E398" s="2"/>
     </row>
     <row r="399">
       <c r="A399" s="1">
@@ -6011,15 +4843,11 @@
       <c r="B399" s="2">
         <v>1.1572164297103882</v>
       </c>
-      <c r="C399" s="2">
-        <v>1.1070711612701416</v>
-      </c>
+      <c r="C399" s="2"/>
       <c r="D399" s="2">
         <v>0.42366856336593628</v>
       </c>
-      <c r="E399" s="2">
-        <v>0.31248542666435242</v>
-      </c>
+      <c r="E399" s="2"/>
     </row>
     <row r="400">
       <c r="A400" s="1">
@@ -6028,15 +4856,11 @@
       <c r="B400" s="2">
         <v>0.38360041379928589</v>
       </c>
-      <c r="C400" s="2">
-        <v>0.036051217466592789</v>
-      </c>
+      <c r="C400" s="2"/>
       <c r="D400" s="2">
         <v>0.53439468145370483</v>
       </c>
-      <c r="E400" s="2">
-        <v>0.31624075770378113</v>
-      </c>
+      <c r="E400" s="2"/>
     </row>
     <row r="401">
       <c r="A401" s="1">
@@ -6045,15 +4869,11 @@
       <c r="B401" s="2">
         <v>0.8081355094909668</v>
       </c>
-      <c r="C401" s="2">
-        <v>0.68841469287872314</v>
-      </c>
+      <c r="C401" s="2"/>
       <c r="D401" s="2">
         <v>0.59262543916702271</v>
       </c>
-      <c r="E401" s="2">
-        <v>0.40455174446105957</v>
-      </c>
+      <c r="E401" s="2"/>
     </row>
     <row r="402">
       <c r="A402" s="1">
@@ -6062,15 +4882,11 @@
       <c r="B402" s="2">
         <v>-0.22297209501266479</v>
       </c>
-      <c r="C402" s="2">
-        <v>-0.54157394170761108</v>
-      </c>
+      <c r="C402" s="2"/>
       <c r="D402" s="2">
         <v>0.61332809925079346</v>
       </c>
-      <c r="E402" s="2">
-        <v>0.46817612648010254</v>
-      </c>
+      <c r="E402" s="2"/>
     </row>
     <row r="403">
       <c r="A403" s="1">
@@ -6079,15 +4895,11 @@
       <c r="B403" s="2">
         <v>0.49359923601150513</v>
       </c>
-      <c r="C403" s="2">
-        <v>0.31446540355682373</v>
-      </c>
+      <c r="C403" s="2"/>
       <c r="D403" s="2">
         <v>0.65724086761474609</v>
       </c>
-      <c r="E403" s="2">
-        <v>0.52208203077316284</v>
-      </c>
+      <c r="E403" s="2"/>
     </row>
     <row r="404">
       <c r="A404" s="1">
@@ -6096,15 +4908,11 @@
       <c r="B404" s="2">
         <v>0.94074857234954834</v>
       </c>
-      <c r="C404" s="2">
-        <v>0.74914699792861938</v>
-      </c>
+      <c r="C404" s="2"/>
       <c r="D404" s="2">
         <v>0.68624377250671387</v>
       </c>
-      <c r="E404" s="2">
-        <v>0.52761685848236084</v>
-      </c>
+      <c r="E404" s="2"/>
     </row>
     <row r="405">
       <c r="A405" s="1">
@@ -6113,15 +4921,11 @@
       <c r="B405" s="2">
         <v>1.1123543977737427</v>
       </c>
-      <c r="C405" s="2">
-        <v>1.1591129302978516</v>
-      </c>
+      <c r="C405" s="2"/>
       <c r="D405" s="2">
         <v>0.79494655132293701</v>
       </c>
-      <c r="E405" s="2">
-        <v>0.65890824794769287</v>
-      </c>
+      <c r="E405" s="2"/>
     </row>
     <row r="406">
       <c r="A406" s="1">
@@ -6130,15 +4934,11 @@
       <c r="B406" s="2">
         <v>0.50939470529556274</v>
       </c>
-      <c r="C406" s="2">
-        <v>0.56828528642654419</v>
-      </c>
+      <c r="C406" s="2"/>
       <c r="D406" s="2">
         <v>0.78558570146560669</v>
       </c>
-      <c r="E406" s="2">
-        <v>0.63432925939559937</v>
-      </c>
+      <c r="E406" s="2"/>
     </row>
     <row r="407">
       <c r="A407" s="1">
@@ -6147,15 +4947,11 @@
       <c r="B407" s="2">
         <v>0.73309063911437988</v>
       </c>
-      <c r="C407" s="2">
-        <v>0.61776447296142578</v>
-      </c>
+      <c r="C407" s="2"/>
       <c r="D407" s="2">
         <v>0.89520138502120972</v>
       </c>
-      <c r="E407" s="2">
-        <v>0.7564508318901062</v>
-      </c>
+      <c r="E407" s="2"/>
     </row>
     <row r="408">
       <c r="A408" s="1">
@@ -6164,15 +4960,11 @@
       <c r="B408" s="2">
         <v>1.4182426929473877</v>
       </c>
-      <c r="C408" s="2">
-        <v>1.1568846702575684</v>
-      </c>
+      <c r="C408" s="2"/>
       <c r="D408" s="2">
         <v>1.0172758102416992</v>
       </c>
-      <c r="E408" s="2">
-        <v>0.89154815673828125</v>
-      </c>
+      <c r="E408" s="2"/>
     </row>
     <row r="409">
       <c r="A409" s="1">
@@ -6181,15 +4973,11 @@
       <c r="B409" s="2">
         <v>1.3619253635406494</v>
       </c>
-      <c r="C409" s="2">
-        <v>1.217673659324646</v>
-      </c>
+      <c r="C409" s="2"/>
       <c r="D409" s="2">
         <v>1.0545041561126709</v>
       </c>
-      <c r="E409" s="2">
-        <v>0.95992028713226318</v>
-      </c>
+      <c r="E409" s="2"/>
     </row>
     <row r="410">
       <c r="A410" s="1">
@@ -6198,15 +4986,11 @@
       <c r="B410" s="2">
         <v>0.7238878607749939</v>
       </c>
-      <c r="C410" s="2">
-        <v>0.46720370650291443</v>
-      </c>
+      <c r="C410" s="2"/>
       <c r="D410" s="2">
         <v>0.99352836608886719</v>
       </c>
-      <c r="E410" s="2">
-        <v>0.86975151300430298</v>
-      </c>
+      <c r="E410" s="2"/>
     </row>
     <row r="411">
       <c r="A411" s="1">
@@ -6215,15 +4999,11 @@
       <c r="B411" s="2">
         <v>0.76356881856918335</v>
       </c>
-      <c r="C411" s="2">
-        <v>0.55752038955688477</v>
-      </c>
+      <c r="C411" s="2"/>
       <c r="D411" s="2">
         <v>1.0458958148956299</v>
       </c>
-      <c r="E411" s="2">
-        <v>0.91146451234817505</v>
-      </c>
+      <c r="E411" s="2"/>
     </row>
     <row r="412">
       <c r="A412" s="1">
@@ -6232,15 +5012,11 @@
       <c r="B412" s="2">
         <v>1.5922693014144897</v>
       </c>
-      <c r="C412" s="2">
-        <v>1.5303410291671753</v>
-      </c>
+      <c r="C412" s="2"/>
       <c r="D412" s="2">
         <v>1.0470746755599976</v>
       </c>
-      <c r="E412" s="2">
-        <v>0.91884952783584595</v>
-      </c>
+      <c r="E412" s="2"/>
     </row>
     <row r="413">
       <c r="A413" s="1">
@@ -6249,15 +5025,11 @@
       <c r="B413" s="2">
         <v>1.2758041620254517</v>
       </c>
-      <c r="C413" s="2">
-        <v>1.3644967079162598</v>
-      </c>
+      <c r="C413" s="2"/>
       <c r="D413" s="2">
         <v>0.93214505910873413</v>
       </c>
-      <c r="E413" s="2">
-        <v>0.81774914264678955</v>
-      </c>
+      <c r="E413" s="2"/>
     </row>
     <row r="414">
       <c r="A414" s="1">
@@ -6266,15 +5038,11 @@
       <c r="B414" s="2">
         <v>0.5635717511177063</v>
       </c>
-      <c r="C414" s="2">
-        <v>0.34759390354156494</v>
-      </c>
+      <c r="C414" s="2"/>
       <c r="D414" s="2">
         <v>0.9005395770072937</v>
       </c>
-      <c r="E414" s="2">
-        <v>0.7925000786781311</v>
-      </c>
+      <c r="E414" s="2"/>
     </row>
     <row r="415">
       <c r="A415" s="1">
@@ -6283,15 +5051,11 @@
       <c r="B415" s="2">
         <v>0.98070204257965088</v>
       </c>
-      <c r="C415" s="2">
-        <v>0.94370222091674805</v>
-      </c>
+      <c r="C415" s="2"/>
       <c r="D415" s="2">
         <v>0.97673279047012329</v>
       </c>
-      <c r="E415" s="2">
-        <v>0.87733268737792969</v>
-      </c>
+      <c r="E415" s="2"/>
     </row>
     <row r="416">
       <c r="A416" s="1">
@@ -6300,15 +5064,11 @@
       <c r="B416" s="2">
         <v>0.74370044469833374</v>
       </c>
-      <c r="C416" s="2">
-        <v>0.68422925472259521</v>
-      </c>
+      <c r="C416" s="2"/>
       <c r="D416" s="2">
         <v>0.96143466234207153</v>
       </c>
-      <c r="E416" s="2">
-        <v>0.86794465780258179</v>
-      </c>
+      <c r="E416" s="2"/>
     </row>
     <row r="417">
       <c r="A417" s="1">
@@ -6317,15 +5077,11 @@
       <c r="B417" s="2">
         <v>0.38387599587440491</v>
       </c>
-      <c r="C417" s="2">
-        <v>0.24698130786418915</v>
-      </c>
+      <c r="C417" s="2"/>
       <c r="D417" s="2">
         <v>0.7767069935798645</v>
       </c>
-      <c r="E417" s="2">
-        <v>0.67625951766967773</v>
-      </c>
+      <c r="E417" s="2"/>
     </row>
     <row r="418">
       <c r="A418" s="1">
@@ -6334,15 +5090,11 @@
       <c r="B418" s="2">
         <v>1.0774756669998169</v>
       </c>
-      <c r="C418" s="2">
-        <v>0.99043244123458862</v>
-      </c>
+      <c r="C418" s="2"/>
       <c r="D418" s="2">
         <v>0.82644361257553101</v>
       </c>
-      <c r="E418" s="2">
-        <v>0.68684297800064087</v>
-      </c>
+      <c r="E418" s="2"/>
     </row>
     <row r="419">
       <c r="A419" s="1">
@@ -6351,15 +5103,11 @@
       <c r="B419" s="2">
         <v>1.4096267223358154</v>
       </c>
-      <c r="C419" s="2">
-        <v>1.2306969165802002</v>
-      </c>
+      <c r="C419" s="2"/>
       <c r="D419" s="2">
         <v>0.92773544788360596</v>
       </c>
-      <c r="E419" s="2">
-        <v>0.79019498825073242</v>
-      </c>
+      <c r="E419" s="2"/>
     </row>
     <row r="420">
       <c r="A420" s="1">
@@ -6368,15 +5116,11 @@
       <c r="B420" s="2">
         <v>0.62588596343994141</v>
       </c>
-      <c r="C420" s="2">
-        <v>0.4730282723903656</v>
-      </c>
+      <c r="C420" s="2"/>
       <c r="D420" s="2">
         <v>0.98916065692901611</v>
       </c>
-      <c r="E420" s="2">
-        <v>0.84658801555633545</v>
-      </c>
+      <c r="E420" s="2"/>
     </row>
     <row r="421">
       <c r="A421" s="1">
@@ -6385,15 +5129,11 @@
       <c r="B421" s="2">
         <v>-0.070279665291309357</v>
       </c>
-      <c r="C421" s="2">
-        <v>-0.19482555985450745</v>
-      </c>
+      <c r="C421" s="2"/>
       <c r="D421" s="2">
         <v>1.0333237648010254</v>
       </c>
-      <c r="E421" s="2">
-        <v>0.83011144399642944</v>
-      </c>
+      <c r="E421" s="2"/>
     </row>
     <row r="422">
       <c r="A422" s="1">
@@ -6402,15 +5142,11 @@
       <c r="B422" s="2">
         <v>1.7234337329864502</v>
       </c>
-      <c r="C422" s="2">
-        <v>1.4597480297088623</v>
-      </c>
+      <c r="C422" s="2"/>
       <c r="D422" s="2">
         <v>1.1008400917053223</v>
       </c>
-      <c r="E422" s="2">
-        <v>0.87867414951324463</v>
-      </c>
+      <c r="E422" s="2"/>
     </row>
     <row r="423">
       <c r="A423" s="1">
@@ -6419,15 +5155,11 @@
       <c r="B423" s="2">
         <v>1.4751982688903809</v>
       </c>
-      <c r="C423" s="2">
-        <v>1.2777621746063232</v>
-      </c>
+      <c r="C423" s="2"/>
       <c r="D423" s="2">
         <v>1.1697723865509033</v>
       </c>
-      <c r="E423" s="2">
-        <v>0.94525176286697388</v>
-      </c>
+      <c r="E423" s="2"/>
     </row>
     <row r="424">
       <c r="A424" s="1">
@@ -6436,15 +5168,11 @@
       <c r="B424" s="2">
         <v>1.5335286855697632</v>
       </c>
-      <c r="C424" s="2">
-        <v>1.4512392282485962</v>
-      </c>
+      <c r="C424" s="2"/>
       <c r="D424" s="2">
         <v>1.2344030141830444</v>
       </c>
-      <c r="E424" s="2">
-        <v>1.009896993637085</v>
-      </c>
+      <c r="E424" s="2"/>
     </row>
     <row r="425">
       <c r="A425" s="1">
@@ -6453,15 +5181,11 @@
       <c r="B425" s="2">
         <v>1.1411681175231934</v>
       </c>
-      <c r="C425" s="2">
-        <v>0.53594040870666504</v>
-      </c>
+      <c r="C425" s="2"/>
       <c r="D425" s="2">
         <v>1.4147522449493408</v>
       </c>
-      <c r="E425" s="2">
-        <v>1.1910630464553833</v>
-      </c>
+      <c r="E425" s="2"/>
     </row>
     <row r="426">
       <c r="A426" s="1">
@@ -6470,15 +5194,11 @@
       <c r="B426" s="2">
         <v>0.9915236234664917</v>
       </c>
-      <c r="C426" s="2">
-        <v>0.68404531478881836</v>
-      </c>
+      <c r="C426" s="2"/>
       <c r="D426" s="2">
         <v>1.6246268749237061</v>
       </c>
-      <c r="E426" s="2">
-        <v>1.4132806062698364</v>
-      </c>
+      <c r="E426" s="2"/>
     </row>
     <row r="427">
       <c r="A427" s="1">
@@ -6487,15 +5207,11 @@
       <c r="B427" s="2">
         <v>1.6978662014007568</v>
       </c>
-      <c r="C427" s="2">
-        <v>1.5896308422088623</v>
-      </c>
+      <c r="C427" s="2"/>
       <c r="D427" s="2">
         <v>1.5594413280487061</v>
       </c>
-      <c r="E427" s="2">
-        <v>1.355894923210144</v>
-      </c>
+      <c r="E427" s="2"/>
     </row>
     <row r="428">
       <c r="A428" s="1">
@@ -6504,15 +5220,11 @@
       <c r="B428" s="2">
         <v>1.9913022518157959</v>
       </c>
-      <c r="C428" s="2">
-        <v>1.8125041723251343</v>
-      </c>
+      <c r="C428" s="2"/>
       <c r="D428" s="2">
         <v>1.5896600484848022</v>
       </c>
-      <c r="E428" s="2">
-        <v>1.4097651243209839</v>
-      </c>
+      <c r="E428" s="2"/>
     </row>
     <row r="429">
       <c r="A429" s="1">
@@ -6521,15 +5233,11 @@
       <c r="B429" s="2">
         <v>2.2490286827087402</v>
       </c>
-      <c r="C429" s="2">
-        <v>2.1035225391387939</v>
-      </c>
+      <c r="C429" s="2"/>
       <c r="D429" s="2">
         <v>1.6016759872436523</v>
       </c>
-      <c r="E429" s="2">
-        <v>1.4152941703796387</v>
-      </c>
+      <c r="E429" s="2"/>
     </row>
     <row r="430">
       <c r="A430" s="1">
@@ -6538,15 +5246,11 @@
       <c r="B430" s="2">
         <v>1.8185924291610718</v>
       </c>
-      <c r="C430" s="2">
-        <v>1.8051323890686035</v>
-      </c>
+      <c r="C430" s="2"/>
       <c r="D430" s="2">
         <v>1.6060266494750977</v>
       </c>
-      <c r="E430" s="2">
-        <v>1.4321978092193604</v>
-      </c>
+      <c r="E430" s="2"/>
     </row>
     <row r="431">
       <c r="A431" s="1">
@@ -6555,15 +5259,11 @@
       <c r="B431" s="2">
         <v>1.1367636919021606</v>
       </c>
-      <c r="C431" s="2">
-        <v>0.94327741861343384</v>
-      </c>
+      <c r="C431" s="2"/>
       <c r="D431" s="2">
         <v>1.6725938320159912</v>
       </c>
-      <c r="E431" s="2">
-        <v>1.5262519121170044</v>
-      </c>
+      <c r="E431" s="2"/>
     </row>
     <row r="432">
       <c r="A432" s="1">
@@ -6572,15 +5272,11 @@
       <c r="B432" s="2">
         <v>1.7471667528152466</v>
       </c>
-      <c r="C432" s="2">
-        <v>1.7625942230224609</v>
-      </c>
+      <c r="C432" s="2"/>
       <c r="D432" s="2">
         <v>1.6887087821960449</v>
       </c>
-      <c r="E432" s="2">
-        <v>1.5356364250183105</v>
-      </c>
+      <c r="E432" s="2"/>
     </row>
     <row r="433">
       <c r="A433" s="1">
@@ -6589,15 +5285,11 @@
       <c r="B433" s="2">
         <v>1.6416721343994141</v>
       </c>
-      <c r="C433" s="2">
-        <v>1.5010005235671997</v>
-      </c>
+      <c r="C433" s="2"/>
       <c r="D433" s="2">
         <v>1.6580961942672729</v>
       </c>
-      <c r="E433" s="2">
-        <v>1.5273394584655762</v>
-      </c>
+      <c r="E433" s="2"/>
     </row>
     <row r="434">
       <c r="A434" s="1">
@@ -6606,15 +5298,11 @@
       <c r="B434" s="2">
         <v>1.1803237199783325</v>
       </c>
-      <c r="C434" s="2">
-        <v>0.68807291984558105</v>
-      </c>
+      <c r="C434" s="2"/>
       <c r="D434" s="2">
         <v>1.6355855464935303</v>
       </c>
-      <c r="E434" s="2">
-        <v>1.5072898864746094</v>
-      </c>
+      <c r="E434" s="2"/>
     </row>
     <row r="435">
       <c r="A435" s="1">
@@ -6623,15 +5311,11 @@
       <c r="B435" s="2">
         <v>1.5906288623809814</v>
       </c>
-      <c r="C435" s="2">
-        <v>1.5305324792861938</v>
-      </c>
+      <c r="C435" s="2"/>
       <c r="D435" s="2">
         <v>1.5878397226333618</v>
       </c>
-      <c r="E435" s="2">
-        <v>1.434643030166626</v>
-      </c>
+      <c r="E435" s="2"/>
     </row>
     <row r="436">
       <c r="A436" s="1">
@@ -6640,15 +5324,11 @@
       <c r="B436" s="2">
         <v>1.8429009914398193</v>
       </c>
-      <c r="C436" s="2">
-        <v>1.6740914583206177</v>
-      </c>
+      <c r="C436" s="2"/>
       <c r="D436" s="2">
         <v>1.6132906675338745</v>
       </c>
-      <c r="E436" s="2">
-        <v>1.4652438163757324</v>
-      </c>
+      <c r="E436" s="2"/>
     </row>
     <row r="437">
       <c r="A437" s="1">
@@ -6657,15 +5337,11 @@
       <c r="B437" s="2">
         <v>1.7157884836196899</v>
       </c>
-      <c r="C437" s="2">
-        <v>1.7378308773040771</v>
-      </c>
+      <c r="C437" s="2"/>
       <c r="D437" s="2">
         <v>1.5386582612991333</v>
       </c>
-      <c r="E437" s="2">
-        <v>1.4310444593429565</v>
-      </c>
+      <c r="E437" s="2"/>
     </row>
     <row r="438">
       <c r="A438" s="1">
@@ -6674,15 +5350,11 @@
       <c r="B438" s="2">
         <v>2.0464324951171875</v>
       </c>
-      <c r="C438" s="2">
-        <v>1.9230769872665405</v>
-      </c>
+      <c r="C438" s="2"/>
       <c r="D438" s="2">
         <v>1.534410834312439</v>
       </c>
-      <c r="E438" s="2">
-        <v>1.3738994598388672</v>
-      </c>
+      <c r="E438" s="2"/>
     </row>
     <row r="439">
       <c r="A439" s="1">
@@ -6691,15 +5363,11 @@
       <c r="B439" s="2">
         <v>1.3888800144195557</v>
       </c>
-      <c r="C439" s="2">
-        <v>1.1513099670410156</v>
-      </c>
+      <c r="C439" s="2"/>
       <c r="D439" s="2">
         <v>1.5333327054977417</v>
       </c>
-      <c r="E439" s="2">
-        <v>1.4092950820922852</v>
-      </c>
+      <c r="E439" s="2"/>
     </row>
     <row r="440">
       <c r="A440" s="1">
@@ -6708,15 +5376,11 @@
       <c r="B440" s="2">
         <v>1.3658230304718018</v>
       </c>
-      <c r="C440" s="2">
-        <v>1.2186845541000366</v>
-      </c>
+      <c r="C440" s="2"/>
       <c r="D440" s="2">
         <v>1.4295583963394165</v>
       </c>
-      <c r="E440" s="2">
-        <v>1.256103515625</v>
-      </c>
+      <c r="E440" s="2"/>
     </row>
     <row r="441">
       <c r="A441" s="1">
@@ -6725,15 +5389,11 @@
       <c r="B441" s="2">
         <v>1.0754748582839966</v>
       </c>
-      <c r="C441" s="2">
-        <v>1.4548004865646362</v>
-      </c>
+      <c r="C441" s="2"/>
       <c r="D441" s="2">
         <v>1.4006568193435669</v>
       </c>
-      <c r="E441" s="2">
-        <v>1.2072008848190308</v>
-      </c>
+      <c r="E441" s="2"/>
     </row>
     <row r="442">
       <c r="A442" s="1">
@@ -6742,15 +5402,11 @@
       <c r="B442" s="2">
         <v>1.6034448146820068</v>
       </c>
-      <c r="C442" s="2">
-        <v>0.98669588565826416</v>
-      </c>
+      <c r="C442" s="2"/>
       <c r="D442" s="2">
         <v>1.4128487110137939</v>
       </c>
-      <c r="E442" s="2">
-        <v>1.1761237382888794</v>
-      </c>
+      <c r="E442" s="2"/>
     </row>
     <row r="443">
       <c r="A443" s="1">
@@ -6759,15 +5415,11 @@
       <c r="B443" s="2">
         <v>1.1706207990646362</v>
       </c>
-      <c r="C443" s="2">
-        <v>1.0066332817077637</v>
-      </c>
+      <c r="C443" s="2"/>
       <c r="D443" s="2">
         <v>1.3582217693328857</v>
       </c>
-      <c r="E443" s="2">
-        <v>1.1122422218322754</v>
-      </c>
+      <c r="E443" s="2"/>
     </row>
     <row r="444">
       <c r="A444" s="1">
@@ -6776,15 +5428,11 @@
       <c r="B444" s="2">
         <v>0.65665990114212036</v>
       </c>
-      <c r="C444" s="2">
-        <v>0.1518082469701767</v>
-      </c>
+      <c r="C444" s="2"/>
       <c r="D444" s="2">
         <v>1.3168988227844238</v>
       </c>
-      <c r="E444" s="2">
-        <v>1.070540189743042</v>
-      </c>
+      <c r="E444" s="2"/>
     </row>
     <row r="445">
       <c r="A445" s="1">
@@ -6793,15 +5441,11 @@
       <c r="B445" s="2">
         <v>1.5827873945236206</v>
       </c>
-      <c r="C445" s="2">
-        <v>1.2339674234390259</v>
-      </c>
+      <c r="C445" s="2"/>
       <c r="D445" s="2">
         <v>1.3075152635574341</v>
       </c>
-      <c r="E445" s="2">
-        <v>1.0299227237701416</v>
-      </c>
+      <c r="E445" s="2"/>
     </row>
     <row r="446">
       <c r="A446" s="1">
@@ -6810,15 +5454,11 @@
       <c r="B446" s="2">
         <v>1.8255156278610229</v>
       </c>
-      <c r="C446" s="2">
-        <v>1.4581363201141357</v>
-      </c>
+      <c r="C446" s="2"/>
       <c r="D446" s="2">
         <v>1.2703428268432617</v>
       </c>
-      <c r="E446" s="2">
-        <v>0.96903592348098755</v>
-      </c>
+      <c r="E446" s="2"/>
     </row>
     <row r="447">
       <c r="A447" s="1">
@@ -6827,15 +5467,11 @@
       <c r="B447" s="2">
         <v>1.5547894239425659</v>
       </c>
-      <c r="C447" s="2">
-        <v>1.3481438159942627</v>
-      </c>
+      <c r="C447" s="2"/>
       <c r="D447" s="2">
         <v>1.2818869352340698</v>
       </c>
-      <c r="E447" s="2">
-        <v>1.0042704343795776</v>
-      </c>
+      <c r="E447" s="2"/>
     </row>
     <row r="448">
       <c r="A448" s="1">
@@ -6844,15 +5480,11 @@
       <c r="B448" s="2">
         <v>1.016973614692688</v>
       </c>
-      <c r="C448" s="2">
-        <v>0.77599143981933594</v>
-      </c>
+      <c r="C448" s="2"/>
       <c r="D448" s="2">
         <v>1.346238374710083</v>
       </c>
-      <c r="E448" s="2">
-        <v>1.103585958480835</v>
-      </c>
+      <c r="E448" s="2"/>
     </row>
     <row r="449">
       <c r="A449" s="1">
@@ -6861,15 +5493,11 @@
       <c r="B449" s="2">
         <v>1.2813705205917358</v>
       </c>
-      <c r="C449" s="2">
-        <v>0.85312801599502563</v>
-      </c>
+      <c r="C449" s="2"/>
       <c r="D449" s="2">
         <v>1.4492030143737793</v>
       </c>
-      <c r="E449" s="2">
-        <v>1.2458590269088745</v>
-      </c>
+      <c r="E449" s="2"/>
     </row>
     <row r="450">
       <c r="A450" s="1">
@@ -6878,15 +5506,11 @@
       <c r="B450" s="2">
         <v>0.74092298746109009</v>
       </c>
-      <c r="C450" s="2">
-        <v>0.90681880712509155</v>
-      </c>
+      <c r="C450" s="2"/>
       <c r="D450" s="2">
         <v>1.3789263963699341</v>
       </c>
-      <c r="E450" s="2">
-        <v>1.1885172128677368</v>
-      </c>
+      <c r="E450" s="2"/>
     </row>
     <row r="451">
       <c r="A451" s="1">
@@ -6895,15 +5519,11 @@
       <c r="B451" s="2">
         <v>1.7073423862457275</v>
       </c>
-      <c r="C451" s="2">
-        <v>1.3038070201873779</v>
-      </c>
+      <c r="C451" s="2"/>
       <c r="D451" s="2">
         <v>1.2904049158096313</v>
       </c>
-      <c r="E451" s="2">
-        <v>1.1118972301483154</v>
-      </c>
+      <c r="E451" s="2"/>
     </row>
     <row r="452">
       <c r="A452" s="1">
@@ -6912,15 +5532,11 @@
       <c r="B452" s="2">
         <v>1.7497837543487549</v>
       </c>
-      <c r="C452" s="2">
-        <v>1.9004729986190796</v>
-      </c>
+      <c r="C452" s="2"/>
       <c r="D452" s="2">
         <v>1.1345969438552856</v>
       </c>
-      <c r="E452" s="2">
-        <v>1.1128276586532593</v>
-      </c>
+      <c r="E452" s="2"/>
     </row>
     <row r="453">
       <c r="A453" s="1">
@@ -6929,15 +5545,11 @@
       <c r="B453" s="2">
         <v>1.583341121673584</v>
       </c>
-      <c r="C453" s="2">
-        <v>1.4322652816772461</v>
-      </c>
+      <c r="C453" s="2"/>
       <c r="D453" s="2">
         <v>1.1442145109176636</v>
       </c>
-      <c r="E453" s="2">
-        <v>1.1490483283996582</v>
-      </c>
+      <c r="E453" s="2"/>
     </row>
     <row r="454">
       <c r="A454" s="1">
@@ -6946,15 +5558,11 @@
       <c r="B454" s="2">
         <v>0.9502984881401062</v>
       </c>
-      <c r="C454" s="2">
-        <v>0.71789073944091797</v>
-      </c>
+      <c r="C454" s="2"/>
       <c r="D454" s="2">
         <v>1.1885077953338623</v>
       </c>
-      <c r="E454" s="2">
-        <v>1.2320543527603149</v>
-      </c>
+      <c r="E454" s="2"/>
     </row>
     <row r="455">
       <c r="A455" s="1">
@@ -6963,15 +5571,11 @@
       <c r="B455" s="2">
         <v>1.0288217067718506</v>
       </c>
-      <c r="C455" s="2">
-        <v>0.76855725049972534</v>
-      </c>
+      <c r="C455" s="2"/>
       <c r="D455" s="2">
         <v>1.209709644317627</v>
       </c>
-      <c r="E455" s="2">
-        <v>1.2049440145492554</v>
-      </c>
+      <c r="E455" s="2"/>
     </row>
     <row r="456">
       <c r="A456" s="1">
@@ -6980,15 +5584,11 @@
       <c r="B456" s="2">
         <v>0.1525174081325531</v>
       </c>
-      <c r="C456" s="2">
-        <v>1.3565170764923096</v>
-      </c>
+      <c r="C456" s="2"/>
       <c r="D456" s="2">
         <v>1.2290585041046143</v>
       </c>
-      <c r="E456" s="2">
-        <v>1.2460794448852539</v>
-      </c>
+      <c r="E456" s="2"/>
     </row>
     <row r="457">
       <c r="A457" s="1">
@@ -6997,15 +5597,11 @@
       <c r="B457" s="2">
         <v>1.1035326719284058</v>
       </c>
-      <c r="C457" s="2">
-        <v>1.101978063583374</v>
-      </c>
+      <c r="C457" s="2"/>
       <c r="D457" s="2">
         <v>1.1567924022674561</v>
       </c>
-      <c r="E457" s="2">
-        <v>1.1267958879470825</v>
-      </c>
+      <c r="E457" s="2"/>
     </row>
     <row r="458">
       <c r="A458" s="1">
@@ -7014,15 +5610,11 @@
       <c r="B458" s="2">
         <v>1.6800093650817871</v>
       </c>
-      <c r="C458" s="2">
-        <v>1.6001822948455811</v>
-      </c>
+      <c r="C458" s="2"/>
       <c r="D458" s="2">
         <v>1.1894123554229736</v>
       </c>
-      <c r="E458" s="2">
-        <v>1.1749199628829956</v>
-      </c>
+      <c r="E458" s="2"/>
     </row>
     <row r="459">
       <c r="A459" s="1">
@@ -7031,15 +5623,11 @@
       <c r="B459" s="2">
         <v>0.93174022436141968</v>
       </c>
-      <c r="C459" s="2">
-        <v>0.66282510757446289</v>
-      </c>
+      <c r="C459" s="2"/>
       <c r="D459" s="2">
         <v>1.0903040170669556</v>
       </c>
-      <c r="E459" s="2">
-        <v>1.0616153478622437</v>
-      </c>
+      <c r="E459" s="2"/>
     </row>
     <row r="460">
       <c r="A460" s="1">
@@ -7048,15 +5636,11 @@
       <c r="B460" s="2">
         <v>1.8814822435379028</v>
       </c>
-      <c r="C460" s="2">
-        <v>1.6740258932113647</v>
-      </c>
+      <c r="C460" s="2"/>
       <c r="D460" s="2">
         <v>1.182654857635498</v>
       </c>
-      <c r="E460" s="2">
-        <v>1.1631512641906738</v>
-      </c>
+      <c r="E460" s="2"/>
     </row>
     <row r="461">
       <c r="A461" s="1">
@@ -7065,15 +5649,11 @@
       <c r="B461" s="2">
         <v>1.0993888378143311</v>
       </c>
-      <c r="C461" s="2">
-        <v>0.82692098617553711</v>
-      </c>
+      <c r="C461" s="2"/>
       <c r="D461" s="2">
         <v>1.3846660852432251</v>
       </c>
-      <c r="E461" s="2">
-        <v>1.2132134437561035</v>
-      </c>
+      <c r="E461" s="2"/>
     </row>
     <row r="462">
       <c r="A462" s="1">
@@ -7082,15 +5662,11 @@
       <c r="B462" s="2">
         <v>1.8769205808639526</v>
       </c>
-      <c r="C462" s="2">
-        <v>1.8653820753097534</v>
-      </c>
+      <c r="C462" s="2"/>
       <c r="D462" s="2">
         <v>1.3563092947006226</v>
       </c>
-      <c r="E462" s="2">
-        <v>1.1468513011932373</v>
-      </c>
+      <c r="E462" s="2"/>
     </row>
     <row r="463">
       <c r="A463" s="1">
@@ -7100,13 +5676,13 @@
         <v>0.058323584496974945</v>
       </c>
       <c r="C463" s="2">
-        <v>-0.30185037851333618</v>
+        <v>-0.14296649396419525</v>
       </c>
       <c r="D463" s="2">
         <v>1.3061486482620239</v>
       </c>
       <c r="E463" s="2">
-        <v>1.0813878774642944</v>
+        <v>1.0626716613769531</v>
       </c>
     </row>
     <row r="464">
@@ -7117,13 +5693,13 @@
         <v>1.8599783182144165</v>
       </c>
       <c r="C464" s="2">
-        <v>1.6823804378509521</v>
+        <v>1.7066025733947754</v>
       </c>
       <c r="D464" s="2">
         <v>1.336560845375061</v>
       </c>
       <c r="E464" s="2">
-        <v>1.1015443801879883</v>
+        <v>1.0626716613769531</v>
       </c>
     </row>
     <row r="465">
@@ -7134,13 +5710,13 @@
         <v>1.9706184864044189</v>
       </c>
       <c r="C465" s="2">
-        <v>1.8070765733718872</v>
+        <v>2.0608148574829102</v>
       </c>
       <c r="D465" s="2">
         <v>1.1550354957580566</v>
       </c>
       <c r="E465" s="2">
-        <v>0.92695039510726929</v>
+        <v>1.0626716613769531</v>
       </c>
     </row>
     <row r="466">
@@ -7151,13 +5727,13 @@
         <v>0.84832167625427246</v>
       </c>
       <c r="C466" s="2">
-        <v>0.50471889972686768</v>
+        <v>0.56778919696807861</v>
       </c>
       <c r="D466" s="2">
         <v>1.0597366094589233</v>
       </c>
       <c r="E466" s="2">
-        <v>0.83029276132583618</v>
+        <v>1.0626716613769531</v>
       </c>
     </row>
     <row r="467">
@@ -7168,13 +5744,13 @@
         <v>1.2285635471343994</v>
       </c>
       <c r="C467" s="2">
-        <v>1.0110108852386475</v>
+        <v>1.1211183071136475</v>
       </c>
       <c r="D467" s="2">
         <v>0.85148638486862183</v>
       </c>
       <c r="E467" s="2">
-        <v>0.63069772720336914</v>
+        <v>0.93086451292037964</v>
       </c>
     </row>
     <row r="468">
@@ -7184,15 +5760,11 @@
       <c r="B468" s="2">
         <v>1.205450177192688</v>
       </c>
-      <c r="C468" s="2">
-        <v>0.84423428773880005</v>
-      </c>
+      <c r="C468" s="2"/>
       <c r="D468" s="2">
         <v>0.8869025707244873</v>
       </c>
-      <c r="E468" s="2">
-        <v>0.68083822727203369</v>
-      </c>
+      <c r="E468" s="2"/>
     </row>
     <row r="469">
       <c r="A469" s="1">
@@ -7201,15 +5773,11 @@
       <c r="B469" s="2">
         <v>0.24775438010692596</v>
       </c>
-      <c r="C469" s="2">
-        <v>0.10267985612154007</v>
-      </c>
+      <c r="C469" s="2"/>
       <c r="D469" s="2">
         <v>0.83725899457931519</v>
       </c>
-      <c r="E469" s="2">
-        <v>0.63003784418106079</v>
-      </c>
+      <c r="E469" s="2"/>
     </row>
     <row r="470">
       <c r="A470" s="1">
@@ -7218,15 +5786,11 @@
       <c r="B470" s="2">
         <v>0.24169909954071045</v>
       </c>
-      <c r="C470" s="2">
-        <v>-0.042997937649488449</v>
-      </c>
+      <c r="C470" s="2"/>
       <c r="D470" s="2">
         <v>0.83630985021591187</v>
       </c>
-      <c r="E470" s="2">
-        <v>0.62155872583389282</v>
-      </c>
+      <c r="E470" s="2"/>
     </row>
     <row r="471">
       <c r="A471" s="1">
@@ -7236,13 +5800,13 @@
         <v>0.0026684550102800131</v>
       </c>
       <c r="C471" s="2">
-        <v>0.069026760756969452</v>
+        <v>0.27182880043983459</v>
       </c>
       <c r="D471" s="2">
         <v>0.95090532302856445</v>
       </c>
       <c r="E471" s="2">
-        <v>0.76407772302627563</v>
+        <v>1.1532124280929565</v>
       </c>
     </row>
     <row r="472">
@@ -7253,13 +5817,13 @@
         <v>0.37706887722015381</v>
       </c>
       <c r="C472" s="2">
-        <v>0.1494145393371582</v>
+        <v>0.23465216159820557</v>
       </c>
       <c r="D472" s="2">
         <v>0.96587347984313965</v>
       </c>
       <c r="E472" s="2">
-        <v>0.75730270147323608</v>
+        <v>1.1594845056533813</v>
       </c>
     </row>
     <row r="473">
@@ -7270,13 +5834,13 @@
         <v>1.4131861925125122</v>
       </c>
       <c r="C473" s="2">
-        <v>1.2251769304275513</v>
+        <v>1.4293656349182129</v>
       </c>
       <c r="D473" s="2">
         <v>1.0048611164093018</v>
       </c>
       <c r="E473" s="2">
-        <v>0.81745272874832153</v>
+        <v>1.2053279876708984</v>
       </c>
     </row>
     <row r="474">
@@ -7287,13 +5851,13 @@
         <v>1.9620761871337891</v>
       </c>
       <c r="C474" s="2">
-        <v>1.7307643890380859</v>
+        <v>1.9474371671676636</v>
       </c>
       <c r="D474" s="2">
         <v>1.1697041988372803</v>
       </c>
       <c r="E474" s="2">
-        <v>0.98038798570632935</v>
+        <v>1.2544071674346924</v>
       </c>
     </row>
     <row r="475">
@@ -7304,13 +5868,13 @@
         <v>1.879680871963501</v>
       </c>
       <c r="C475" s="2">
-        <v>1.7873897552490234</v>
+        <v>1.9148721694946289</v>
       </c>
       <c r="D475" s="2">
         <v>1.340476393699646</v>
       </c>
       <c r="E475" s="2">
-        <v>1.1833635568618774</v>
+        <v>1.333680272102356</v>
       </c>
     </row>
     <row r="476">
@@ -7321,13 +5885,13 @@
         <v>1.3632768392562866</v>
       </c>
       <c r="C476" s="2">
-        <v>0.95003581047058105</v>
+        <v>1.158751368522644</v>
       </c>
       <c r="D476" s="2">
         <v>1.4777785539627075</v>
       </c>
       <c r="E476" s="2">
-        <v>1.2932922840118408</v>
+        <v>1.4379844665527344</v>
       </c>
     </row>
     <row r="477">
@@ -7338,13 +5902,13 @@
         <v>1.5563391447067261</v>
       </c>
       <c r="C477" s="2">
-        <v>1.3855842351913452</v>
+        <v>1.480388879776001</v>
       </c>
       <c r="D477" s="2">
         <v>1.5902128219604492</v>
       </c>
       <c r="E477" s="2">
-        <v>1.4054267406463623</v>
+        <v>1.5466715097427368</v>
       </c>
     </row>
     <row r="478">
@@ -7355,13 +5919,13 @@
         <v>1.7313425540924072</v>
       </c>
       <c r="C478" s="2">
-        <v>1.5690973997116089</v>
+        <v>1.5979611873626709</v>
       </c>
       <c r="D478" s="2">
         <v>1.4359936714172363</v>
       </c>
       <c r="E478" s="2">
-        <v>1.1975724697113037</v>
+        <v>1.3315731287002563</v>
       </c>
     </row>
     <row r="479">
@@ -7372,13 +5936,13 @@
         <v>1.7786480188369751</v>
       </c>
       <c r="C479" s="2">
-        <v>1.7837821245193481</v>
+        <v>1.9678654670715332</v>
       </c>
       <c r="D479" s="2">
         <v>1.4113755226135254</v>
       </c>
       <c r="E479" s="2">
-        <v>1.1534088850021362</v>
+        <v>1.2841757535934448</v>
       </c>
     </row>
     <row r="480">
@@ -7389,13 +5953,13 @@
         <v>1.2383887767791748</v>
       </c>
       <c r="C480" s="2">
-        <v>1.0583851337432861</v>
+        <v>1.2105661630630493</v>
       </c>
       <c r="D480" s="2">
         <v>1.4024837017059326</v>
       </c>
       <c r="E480" s="2">
-        <v>1.1301054954528809</v>
+        <v>1.2621215581893921</v>
       </c>
     </row>
     <row r="481">
@@ -7406,13 +5970,13 @@
         <v>1.3889771699905396</v>
       </c>
       <c r="C481" s="2">
-        <v>1.158624529838562</v>
+        <v>1.2128356695175171</v>
       </c>
       <c r="D481" s="2">
         <v>1.4491981267929077</v>
       </c>
       <c r="E481" s="2">
-        <v>1.2022261619567871</v>
+        <v>1.31074059009552</v>
       </c>
     </row>
     <row r="482">
@@ -7423,13 +5987,13 @@
         <v>0.025213660672307014</v>
       </c>
       <c r="C482" s="2">
-        <v>-0.64551109075546265</v>
+        <v>-0.50651949644088745</v>
       </c>
       <c r="D482" s="2">
         <v>1.4207800626754761</v>
       </c>
       <c r="E482" s="2">
-        <v>1.1893788576126099</v>
+        <v>1.3074686527252197</v>
       </c>
     </row>
     <row r="483">
@@ -7440,13 +6004,13 @@
         <v>1.7405130863189697</v>
       </c>
       <c r="C483" s="2">
-        <v>1.3332920074462891</v>
+        <v>1.5208603143692017</v>
       </c>
       <c r="D483" s="2">
         <v>1.2586687803268433</v>
       </c>
       <c r="E483" s="2">
-        <v>1.0410966873168945</v>
+        <v>1.1614243984222412</v>
       </c>
     </row>
     <row r="484">
@@ -7457,13 +6021,13 @@
         <v>1.7996540069580078</v>
       </c>
       <c r="C484" s="2">
-        <v>1.5776594877243042</v>
+        <v>1.7163847684860229</v>
       </c>
       <c r="D484" s="2">
         <v>1.2240520715713501</v>
       </c>
       <c r="E484" s="2">
-        <v>0.98072594404220581</v>
+        <v>1.0964550971984863</v>
       </c>
     </row>
     <row r="485">
@@ -7474,13 +6038,13 @@
         <v>1.7837061882019043</v>
       </c>
       <c r="C485" s="2">
-        <v>1.599122166633606</v>
+        <v>1.5963222980499268</v>
       </c>
       <c r="D485" s="2">
         <v>1.2117211818695068</v>
       </c>
       <c r="E485" s="2">
-        <v>1.0201597213745117</v>
+        <v>1.1346157789230347</v>
       </c>
     </row>
     <row r="486">
@@ -7491,13 +6055,13 @@
         <v>1.3005768060684204</v>
       </c>
       <c r="C486" s="2">
-        <v>1.2699582576751709</v>
+        <v>1.4509416818618774</v>
       </c>
       <c r="D486" s="2">
         <v>1.2174695730209351</v>
       </c>
       <c r="E486" s="2">
-        <v>1.0001362562179565</v>
+        <v>1.1336692571640015</v>
       </c>
     </row>
     <row r="487">
@@ -7508,13 +6072,13 @@
         <v>0.27234089374542236</v>
       </c>
       <c r="C487" s="2">
-        <v>0.23455773293972015</v>
+        <v>0.28356227278709412</v>
       </c>
       <c r="D487" s="2">
         <v>1.3908437490463257</v>
       </c>
       <c r="E487" s="2">
-        <v>1.2226815223693848</v>
+        <v>1.3543961048126221</v>
       </c>
     </row>
     <row r="488">
@@ -7525,13 +6089,13 @@
         <v>1.4670977592468262</v>
       </c>
       <c r="C488" s="2">
-        <v>1.2404450178146362</v>
+        <v>1.3831419944763184</v>
       </c>
       <c r="D488" s="2">
         <v>1.3649774789810181</v>
       </c>
       <c r="E488" s="2">
-        <v>1.2108613252639771</v>
+        <v>1.3244158029556274</v>
       </c>
     </row>
     <row r="489">
@@ -7542,13 +6106,13 @@
         <v>1.1274113655090332</v>
       </c>
       <c r="C489" s="2">
-        <v>1.4132890701293945</v>
+        <v>1.5540128946304321</v>
       </c>
       <c r="D489" s="2">
         <v>1.3125994205474854</v>
       </c>
       <c r="E489" s="2">
-        <v>1.1581566333770752</v>
+        <v>1.2780566215515137</v>
       </c>
     </row>
     <row r="490">
@@ -7559,13 +6123,13 @@
         <v>1.4407123327255249</v>
       </c>
       <c r="C490" s="2">
-        <v>0.97841346263885498</v>
+        <v>1.2043164968490601</v>
       </c>
       <c r="D490" s="2">
         <v>1.211438775062561</v>
       </c>
       <c r="E490" s="2">
-        <v>1.0367476940155029</v>
+        <v>1.1815475225448608</v>
       </c>
     </row>
     <row r="491">
@@ -7576,13 +6140,13 @@
         <v>1.5855816602706909</v>
       </c>
       <c r="C491" s="2">
-        <v>1.3573962450027466</v>
+        <v>1.480022668838501</v>
       </c>
       <c r="D491" s="2">
         <v>1.2296171188354492</v>
       </c>
       <c r="E491" s="2">
-        <v>1.0310949087142944</v>
+        <v>1.1703808307647705</v>
       </c>
     </row>
     <row r="492">
@@ -7593,13 +6157,13 @@
         <v>1.5077159404754639</v>
       </c>
       <c r="C492" s="2">
-        <v>1.2269108295440674</v>
+        <v>1.25103759765625</v>
       </c>
       <c r="D492" s="2">
         <v>1.4379830360412598</v>
       </c>
       <c r="E492" s="2">
-        <v>1.2005047798156738</v>
+        <v>1.3473358154296875</v>
       </c>
     </row>
     <row r="493">
@@ -7610,13 +6174,13 @@
         <v>1.3282513618469238</v>
       </c>
       <c r="C493" s="2">
-        <v>1.1033167839050293</v>
+        <v>1.2991513013839722</v>
       </c>
       <c r="D493" s="2">
         <v>1.4780412912368774</v>
       </c>
       <c r="E493" s="2">
-        <v>1.2300624847412109</v>
+        <v>1.392174243927002</v>
       </c>
     </row>
     <row r="494">
@@ -7627,13 +6191,13 @@
         <v>0.87326037883758545</v>
       </c>
       <c r="C494" s="2">
-        <v>0.50644171237945557</v>
+        <v>0.7277405858039856</v>
       </c>
       <c r="D494" s="2">
         <v>1.5297920703887939</v>
       </c>
       <c r="E494" s="2">
-        <v>1.2867329120635986</v>
+        <v>1.4381743669509888</v>
       </c>
     </row>
     <row r="495">
@@ -7644,13 +6208,13 @@
         <v>1.4641828536987305</v>
       </c>
       <c r="C495" s="2">
-        <v>1.2190828323364258</v>
+        <v>1.3504418134689331</v>
       </c>
       <c r="D495" s="2">
         <v>1.5713450908660889</v>
       </c>
       <c r="E495" s="2">
-        <v>1.2945350408554077</v>
+        <v>1.4323585033416748</v>
       </c>
     </row>
     <row r="496">
@@ -7661,13 +6225,13 @@
         <v>2.1476333141326904</v>
       </c>
       <c r="C496" s="2">
-        <v>1.759246826171875</v>
+        <v>1.8761570453643799</v>
       </c>
       <c r="D496" s="2">
         <v>1.5555629730224609</v>
       </c>
       <c r="E496" s="2">
-        <v>1.2944412231445312</v>
+        <v>1.4200015068054199</v>
       </c>
     </row>
     <row r="497">
@@ -7678,13 +6242,13 @@
         <v>1.8276228904724121</v>
       </c>
       <c r="C497" s="2">
-        <v>1.5064642429351807</v>
+        <v>1.7866880893707275</v>
       </c>
       <c r="D497" s="2">
         <v>1.5597677230834961</v>
       </c>
       <c r="E497" s="2">
-        <v>1.2810249328613281</v>
+        <v>1.4270861148834229</v>
       </c>
     </row>
     <row r="498">
@@ -7695,13 +6259,13 @@
         <v>1.5931683778762817</v>
       </c>
       <c r="C498" s="2">
-        <v>1.9233229160308838</v>
+        <v>1.968014121055603</v>
       </c>
       <c r="D498" s="2">
         <v>1.5833245515823364</v>
       </c>
       <c r="E498" s="2">
-        <v>1.2541232109069824</v>
+        <v>1.3906706571578979</v>
       </c>
     </row>
     <row r="499">
@@ -7712,13 +6276,13 @@
         <v>1.8146886825561523</v>
       </c>
       <c r="C499" s="2">
-        <v>1.0486326217651367</v>
+        <v>1.1519730091094971</v>
       </c>
       <c r="D499" s="2">
         <v>1.6908072233200073</v>
       </c>
       <c r="E499" s="2">
-        <v>1.4034453630447388</v>
+        <v>1.5134179592132568</v>
       </c>
     </row>
     <row r="500">
@@ -7729,13 +6293,13 @@
         <v>1.44354248046875</v>
       </c>
       <c r="C500" s="2">
-        <v>1.3565526008605957</v>
+        <v>1.3688099384307861</v>
       </c>
       <c r="D500" s="2">
         <v>1.5820158720016479</v>
       </c>
       <c r="E500" s="2">
-        <v>1.3765177726745605</v>
+        <v>1.4900176525115967</v>
       </c>
     </row>
     <row r="501">
@@ -7746,13 +6310,13 @@
         <v>1.5455589294433594</v>
       </c>
       <c r="C501" s="2">
-        <v>1.1061640977859497</v>
+        <v>1.3147988319396973</v>
       </c>
       <c r="D501" s="2">
         <v>1.5310840606689453</v>
       </c>
       <c r="E501" s="2">
-        <v>1.3546185493469238</v>
+        <v>1.4650416374206543</v>
       </c>
     </row>
     <row r="502">
@@ -7763,13 +6327,13 @@
         <v>1.5402628183364868</v>
       </c>
       <c r="C502" s="2">
-        <v>0.86120152473449707</v>
+        <v>0.97141218185424805</v>
       </c>
       <c r="D502" s="2">
         <v>1.3925092220306396</v>
       </c>
       <c r="E502" s="2">
-        <v>1.3832757472991943</v>
+        <v>1.4554961919784546</v>
       </c>
     </row>
     <row r="503">
@@ -7780,13 +6344,13 @@
         <v>1.840604305267334</v>
       </c>
       <c r="C503" s="2">
-        <v>1.8503403663635254</v>
+        <v>1.8324663639068604</v>
       </c>
       <c r="D503" s="2">
         <v>1.2746435403823853</v>
       </c>
       <c r="E503" s="2">
-        <v>1.2003471851348877</v>
+        <v>1.2506815195083618</v>
       </c>
     </row>
     <row r="504">
@@ -7797,13 +6361,13 @@
         <v>0.48506104946136475</v>
       </c>
       <c r="C504" s="2">
-        <v>0.97673457860946655</v>
+        <v>1.1398390531539917</v>
       </c>
       <c r="D504" s="2">
         <v>1.3272626399993896</v>
       </c>
       <c r="E504" s="2">
-        <v>1.3346371650695801</v>
+        <v>1.3842952251434326</v>
       </c>
     </row>
     <row r="505">
@@ -7814,13 +6378,13 @@
         <v>1.6892473697662354</v>
       </c>
       <c r="C505" s="2">
-        <v>1.5621545314788818</v>
+        <v>1.6513727903366089</v>
       </c>
       <c r="D505" s="2">
         <v>1.220727801322937</v>
       </c>
       <c r="E505" s="2">
-        <v>1.2526352405548096</v>
+        <v>1.3070602416992188</v>
       </c>
     </row>
     <row r="506">
@@ -7831,13 +6395,13 @@
         <v>0.58044952154159546</v>
       </c>
       <c r="C506" s="2">
-        <v>1.7643786668777466</v>
+        <v>1.7007793188095093</v>
       </c>
       <c r="D506" s="2">
         <v>1.1059097051620483</v>
       </c>
       <c r="E506" s="2">
-        <v>1.162840723991394</v>
+        <v>1.2074590921401978</v>
       </c>
     </row>
     <row r="507">
@@ -7848,13 +6412,13 @@
         <v>0.53237676620483398</v>
       </c>
       <c r="C507" s="2">
-        <v>0.27696555852890015</v>
+        <v>0.12468186765909195</v>
       </c>
       <c r="D507" s="2">
         <v>0.92085391283035278</v>
       </c>
       <c r="E507" s="2">
-        <v>1.0293576717376709</v>
+        <v>1.0728906393051147</v>
       </c>
     </row>
     <row r="508">
@@ -7865,13 +6429,13 @@
         <v>2.2882609367370605</v>
       </c>
       <c r="C508" s="2">
-        <v>2.2572422027587891</v>
+        <v>2.3544962406158447</v>
       </c>
       <c r="D508" s="2">
         <v>0.78365272283554077</v>
       </c>
       <c r="E508" s="2">
-        <v>0.82591640949249268</v>
+        <v>0.86166083812713623</v>
       </c>
     </row>
     <row r="509">
@@ -7882,13 +6446,13 @@
         <v>0.48472899198532104</v>
       </c>
       <c r="C509" s="2">
-        <v>0.61853599548339844</v>
+        <v>0.67369586229324341</v>
       </c>
       <c r="D509" s="2">
         <v>0.82704585790634155</v>
       </c>
       <c r="E509" s="2">
-        <v>0.79465371370315552</v>
+        <v>0.81202340126037598</v>
       </c>
     </row>
     <row r="510">
@@ -7899,13 +6463,13 @@
         <v>0.51219546794891357</v>
       </c>
       <c r="C510" s="2">
-        <v>0.2980131208896637</v>
+        <v>0.41838845610618591</v>
       </c>
       <c r="D510" s="2">
         <v>0.67975717782974243</v>
       </c>
       <c r="E510" s="2">
-        <v>0.63370645046234131</v>
+        <v>0.65123468637466431</v>
       </c>
     </row>
     <row r="511">
@@ -7916,13 +6480,13 @@
         <v>-0.12523932754993439</v>
       </c>
       <c r="C511" s="2">
-        <v>-0.34014624357223511</v>
+        <v>-0.23970429599285126</v>
       </c>
       <c r="D511" s="2">
         <v>0.7368316650390625</v>
       </c>
       <c r="E511" s="2">
-        <v>0.5020328164100647</v>
+        <v>0.54188549518585205</v>
       </c>
     </row>
     <row r="512">
@@ -7933,13 +6497,13 @@
         <v>0.60579395294189453</v>
       </c>
       <c r="C512" s="2">
-        <v>0.019369041547179222</v>
+        <v>-0.068601496517658234</v>
       </c>
       <c r="D512" s="2">
         <v>0.7623942494392395</v>
       </c>
       <c r="E512" s="2">
-        <v>0.54404395818710327</v>
+        <v>0.60891741514205933</v>
       </c>
     </row>
     <row r="513">
@@ -7950,13 +6514,13 @@
         <v>0.87559908628463745</v>
       </c>
       <c r="C513" s="2">
-        <v>0.69537031650543213</v>
+        <v>0.69310200214385986</v>
       </c>
       <c r="D513" s="2">
         <v>0.70471274852752686</v>
       </c>
       <c r="E513" s="2">
-        <v>0.47758841514587402</v>
+        <v>0.54188793897628784</v>
       </c>
     </row>
     <row r="514">
@@ -7967,13 +6531,13 @@
         <v>0.36364918947219849</v>
       </c>
       <c r="C514" s="2">
-        <v>0.11362946778535843</v>
+        <v>0.20427438616752625</v>
       </c>
       <c r="D514" s="2">
         <v>0.75959533452987671</v>
       </c>
       <c r="E514" s="2">
-        <v>0.54727637767791748</v>
+        <v>0.62137198448181152</v>
       </c>
     </row>
     <row r="515">
@@ -7984,13 +6548,13 @@
         <v>1.0941201448440552</v>
       </c>
       <c r="C515" s="2">
-        <v>0.5793156623840332</v>
+        <v>0.71663624048233032</v>
       </c>
       <c r="D515" s="2">
         <v>0.89630365371704102</v>
       </c>
       <c r="E515" s="2">
-        <v>0.69848471879959106</v>
+        <v>0.77286005020141602</v>
       </c>
     </row>
     <row r="516">
@@ -8001,13 +6565,13 @@
         <v>0.76243960857391357</v>
       </c>
       <c r="C516" s="2">
-        <v>0.65506619215011597</v>
+        <v>0.72796928882598877</v>
       </c>
       <c r="D516" s="2">
         <v>1.061773419380188</v>
       </c>
       <c r="E516" s="2">
-        <v>0.88166064023971558</v>
+        <v>0.97839832305908203</v>
       </c>
     </row>
     <row r="517">
@@ -8018,13 +6582,13 @@
         <v>1.769127368927002</v>
       </c>
       <c r="C517" s="2">
-        <v>1.6591422557830811</v>
+        <v>1.7512309551239014</v>
       </c>
       <c r="D517" s="2">
         <v>1.1729536056518555</v>
       </c>
       <c r="E517" s="2">
-        <v>1.0245108604431152</v>
+        <v>1.1526070833206177</v>
       </c>
     </row>
     <row r="518">
@@ -8035,13 +6599,13 @@
         <v>0.97867226600646973</v>
       </c>
       <c r="C518" s="2">
-        <v>1.2457275390625</v>
+        <v>1.3890523910522461</v>
       </c>
       <c r="D518" s="2">
         <v>1.2141772508621216</v>
       </c>
       <c r="E518" s="2">
-        <v>1.0498842000961304</v>
+        <v>1.1978172063827515</v>
       </c>
     </row>
     <row r="519">
@@ -8052,13 +6616,13 @@
         <v>1.7425705194473267</v>
       </c>
       <c r="C519" s="2">
-        <v>1.6588882207870483</v>
+        <v>1.7817807197570801</v>
       </c>
       <c r="D519" s="2">
         <v>1.2767599821090698</v>
       </c>
       <c r="E519" s="2">
-        <v>1.1201741695404053</v>
+        <v>1.2876477241516113</v>
       </c>
     </row>
     <row r="520">
@@ -8069,13 +6633,13 @@
         <v>1.3639882802963257</v>
       </c>
       <c r="C520" s="2">
-        <v>1.3084368705749512</v>
+        <v>1.6101402044296265</v>
       </c>
       <c r="D520" s="2">
         <v>1.2889308929443359</v>
       </c>
       <c r="E520" s="2">
-        <v>1.1832188367843628</v>
+        <v>1.3440127372741699</v>
       </c>
     </row>
     <row r="521">
@@ -8086,13 +6650,13 @@
         <v>1.6064155101776123</v>
       </c>
       <c r="C521" s="2">
-        <v>1.3050211668014526</v>
+        <v>1.4992773532867432</v>
       </c>
       <c r="D521" s="2">
         <v>1.3734084367752075</v>
       </c>
       <c r="E521" s="2">
-        <v>1.2723867893218994</v>
+        <v>1.4172625541687012</v>
       </c>
     </row>
     <row r="522">
@@ -8103,13 +6667,13 @@
         <v>1.246612548828125</v>
       </c>
       <c r="C522" s="2">
-        <v>0.92373067140579224</v>
+        <v>1.0999933481216431</v>
       </c>
       <c r="D522" s="2">
         <v>1.2505203485488892</v>
       </c>
       <c r="E522" s="2">
-        <v>1.0892282724380493</v>
+        <v>1.2321900129318237</v>
       </c>
     </row>
     <row r="523">
@@ -8120,13 +6684,13 @@
         <v>0.92689377069473267</v>
       </c>
       <c r="C523" s="2">
-        <v>0.7462388277053833</v>
+        <v>1.0127494335174561</v>
       </c>
       <c r="D523" s="2">
         <v>1.2303059101104736</v>
       </c>
       <c r="E523" s="2">
-        <v>1.0369600057601929</v>
+        <v>1.1177912950515747</v>
       </c>
     </row>
     <row r="524">
@@ -8137,13 +6701,13 @@
         <v>1.2036579847335815</v>
       </c>
       <c r="C524" s="2">
-        <v>1.14671790599823</v>
+        <v>1.2239208221435547</v>
       </c>
       <c r="D524" s="2">
         <v>1.1386046409606934</v>
       </c>
       <c r="E524" s="2">
-        <v>0.9503980278968811</v>
+        <v>1.0375238656997681</v>
       </c>
     </row>
     <row r="525">
@@ -8154,13 +6718,13 @@
         <v>1.522737979888916</v>
       </c>
       <c r="C525" s="2">
-        <v>1.4575778245925903</v>
+        <v>1.3872179985046387</v>
       </c>
       <c r="D525" s="2">
         <v>1.1521434783935547</v>
       </c>
       <c r="E525" s="2">
-        <v>0.96004331111907959</v>
+        <v>1.0118242502212524</v>
       </c>
     </row>
     <row r="526">
@@ -8171,13 +6735,13 @@
         <v>0.66313391923904419</v>
       </c>
       <c r="C526" s="2">
-        <v>0.010715666227042675</v>
+        <v>0.085577540099620819</v>
       </c>
       <c r="D526" s="2">
         <v>1.0906450748443604</v>
       </c>
       <c r="E526" s="2">
-        <v>0.92026853561401367</v>
+        <v>0.95495247840881348</v>
       </c>
     </row>
     <row r="527">
@@ -8188,13 +6752,13 @@
         <v>0.79674267768859863</v>
       </c>
       <c r="C527" s="2">
-        <v>0.77531296014785767</v>
+        <v>0.35946410894393921</v>
       </c>
       <c r="D527" s="2">
         <v>1.0088629722595215</v>
       </c>
       <c r="E527" s="2">
-        <v>0.85752159357070923</v>
+        <v>0.8707345724105835</v>
       </c>
     </row>
     <row r="528">
@@ -8205,13 +6769,13 @@
         <v>0.91725945472717285</v>
       </c>
       <c r="C528" s="2">
-        <v>0.87983059883117676</v>
+        <v>1.0593739748001099</v>
       </c>
       <c r="D528" s="2">
         <v>1.046733021736145</v>
       </c>
       <c r="E528" s="2">
-        <v>0.88479322195053101</v>
+        <v>0.88033384084701538</v>
       </c>
     </row>
     <row r="529">
@@ -8222,13 +6786,13 @@
         <v>1.4858369827270508</v>
       </c>
       <c r="C529" s="2">
-        <v>1.3952440023422241</v>
+        <v>1.3788431882858276</v>
       </c>
       <c r="D529" s="2">
         <v>1.0142475366592407</v>
       </c>
       <c r="E529" s="2">
-        <v>0.84516370296478271</v>
+        <v>0.83650648593902588</v>
       </c>
     </row>
     <row r="530">
@@ -8239,13 +6803,13 @@
         <v>1.0529301166534424</v>
       </c>
       <c r="C530" s="2">
-        <v>0.9470481276512146</v>
+        <v>0.98743170499801636</v>
       </c>
       <c r="D530" s="2">
         <v>0.83614379167556763</v>
       </c>
       <c r="E530" s="2">
-        <v>0.67033165693283081</v>
+        <v>0.67362499237060547</v>
       </c>
     </row>
     <row r="531">
@@ -8256,13 +6820,13 @@
         <v>0.51057350635528564</v>
       </c>
       <c r="C531" s="2">
-        <v>0.35900866985321045</v>
+        <v>0.34203258156776428</v>
       </c>
       <c r="D531" s="2">
         <v>0.77653384208679199</v>
       </c>
       <c r="E531" s="2">
-        <v>0.68671107292175293</v>
+        <v>0.69135260581970215</v>
       </c>
     </row>
     <row r="532">
@@ -8273,13 +6837,13 @@
         <v>1.2677242755889893</v>
       </c>
       <c r="C532" s="2">
-        <v>0.99168300628662109</v>
+        <v>1.0991429090499878</v>
       </c>
       <c r="D532" s="2">
         <v>0.72515815496444702</v>
       </c>
       <c r="E532" s="2">
-        <v>0.63181334733963013</v>
+        <v>0.69027251005172729</v>
       </c>
     </row>
     <row r="533">
@@ -8290,13 +6854,13 @@
         <v>0.91128849983215332</v>
       </c>
       <c r="C533" s="2">
-        <v>0.79005271196365356</v>
+        <v>0.82947462797164917</v>
       </c>
       <c r="D533" s="2">
         <v>0.69402062892913818</v>
       </c>
       <c r="E533" s="2">
-        <v>0.63767325878143311</v>
+        <v>0.67791908979415894</v>
       </c>
     </row>
     <row r="534">
@@ -8307,13 +6871,13 @@
         <v>-0.080195508897304535</v>
       </c>
       <c r="C534" s="2">
-        <v>-0.11591099202632904</v>
+        <v>-0.078715719282627106</v>
       </c>
       <c r="D534" s="2">
         <v>0.56051582098007202</v>
       </c>
       <c r="E534" s="2">
-        <v>0.48960369825363159</v>
+        <v>0.53675878047943115</v>
       </c>
     </row>
     <row r="535">
@@ -8324,13 +6888,13 @@
         <v>0.12664449214935303</v>
       </c>
       <c r="C535" s="2">
-        <v>0.15813048183917999</v>
+        <v>0.24512602388858795</v>
       </c>
       <c r="D535" s="2">
         <v>0.50359535217285156</v>
       </c>
       <c r="E535" s="2">
-        <v>0.42969438433647156</v>
+        <v>0.48081472516059875</v>
       </c>
     </row>
     <row r="536">
@@ -8341,13 +6905,13 @@
         <v>0.33436131477355957</v>
       </c>
       <c r="C536" s="2">
-        <v>0.28123369812965393</v>
+        <v>0.34974333643913269</v>
       </c>
       <c r="D536" s="2">
         <v>0.46786314249038696</v>
       </c>
       <c r="E536" s="2">
-        <v>0.40456825494766235</v>
+        <v>0.45295917987823486</v>
       </c>
     </row>
     <row r="537">
@@ -8358,13 +6922,13 @@
         <v>0.63702201843261719</v>
       </c>
       <c r="C537" s="2">
-        <v>0.93256938457489014</v>
+        <v>0.94819307327270508</v>
       </c>
       <c r="D537" s="2">
         <v>0.45421925187110901</v>
       </c>
       <c r="E537" s="2">
-        <v>0.3979286253452301</v>
+        <v>0.4466005265712738</v>
       </c>
     </row>
     <row r="538">
@@ -8375,13 +6939,13 @@
         <v>0.28429388999938965</v>
       </c>
       <c r="C538" s="2">
-        <v>0.062618277966976166</v>
+        <v>0.10840068757534027</v>
       </c>
       <c r="D538" s="2">
         <v>0.41505885124206543</v>
       </c>
       <c r="E538" s="2">
-        <v>0.35286188125610352</v>
+        <v>0.39026850461959839</v>
       </c>
     </row>
     <row r="539">
@@ -8392,13 +6956,13 @@
         <v>0.54064565896987915</v>
       </c>
       <c r="C539" s="2">
-        <v>0.40786424279212952</v>
+        <v>0.48393508791923523</v>
       </c>
       <c r="D539" s="2">
         <v>0.49498873949050903</v>
       </c>
       <c r="E539" s="2">
-        <v>0.4055837094783783</v>
+        <v>0.43942642211914062</v>
       </c>
     </row>
     <row r="540">
@@ -8409,13 +6973,13 @@
         <v>0.18898358941078186</v>
       </c>
       <c r="C540" s="2">
-        <v>0.13287346065044403</v>
+        <v>0.091332502663135529</v>
       </c>
       <c r="D540" s="2">
         <v>0.40869230031967163</v>
       </c>
       <c r="E540" s="2">
-        <v>0.28363797068595886</v>
+        <v>0.32177531719207764</v>
       </c>
     </row>
     <row r="541">
@@ -8426,13 +6990,13 @@
         <v>1.1449294090270996</v>
       </c>
       <c r="C541" s="2">
-        <v>0.93192631006240845</v>
+        <v>1.0419151782989502</v>
       </c>
       <c r="D541" s="2">
         <v>0.41527491807937622</v>
       </c>
       <c r="E541" s="2">
-        <v>0.28761130571365356</v>
+        <v>0.31923621892929077</v>
       </c>
     </row>
     <row r="542">
@@ -8443,13 +7007,13 @@
         <v>0.55884474515914917</v>
       </c>
       <c r="C542" s="2">
-        <v>0.38445216417312622</v>
+        <v>0.32248631119728088</v>
       </c>
       <c r="D542" s="2">
         <v>0.33494687080383301</v>
       </c>
       <c r="E542" s="2">
-        <v>0.14292044937610626</v>
+        <v>0.18464414775371552</v>
       </c>
     </row>
     <row r="543">
@@ -8460,13 +7024,13 @@
         <v>0.63917356729507446</v>
       </c>
       <c r="C543" s="2">
-        <v>0.35858538746833801</v>
+        <v>0.36370551586151123</v>
       </c>
       <c r="D543" s="2">
         <v>0.4273969829082489</v>
       </c>
       <c r="E543" s="2">
-        <v>0.23567023873329163</v>
+        <v>0.28991234302520752</v>
       </c>
     </row>
     <row r="544">
@@ -8477,13 +7041,13 @@
         <v>-0.65002357959747314</v>
       </c>
       <c r="C544" s="2">
-        <v>-0.93938112258911133</v>
+        <v>-0.81373381614685059</v>
       </c>
       <c r="D544" s="2">
         <v>0.43956440687179565</v>
       </c>
       <c r="E544" s="2">
-        <v>0.25097635388374329</v>
+        <v>0.30274835228919983</v>
       </c>
     </row>
     <row r="545">
@@ -8494,13 +7058,13 @@
         <v>0.39360508322715759</v>
       </c>
       <c r="C545" s="2">
-        <v>0.31699368357658386</v>
+        <v>0.32689133286476135</v>
       </c>
       <c r="D545" s="2">
         <v>0.53639215230941772</v>
       </c>
       <c r="E545" s="2">
-        <v>0.34402754902839661</v>
+        <v>0.40305796265602112</v>
       </c>
     </row>
     <row r="546">
@@ -8511,13 +7075,13 @@
         <v>-0.085930615663528442</v>
       </c>
       <c r="C546" s="2">
-        <v>-0.36964836716651917</v>
+        <v>-0.26313549280166626</v>
       </c>
       <c r="D546" s="2">
         <v>0.46091747283935547</v>
       </c>
       <c r="E546" s="2">
-        <v>0.26832753419876099</v>
+        <v>0.31675425171852112</v>
       </c>
     </row>
     <row r="547">
@@ -8528,13 +7092,13 @@
         <v>1.1163449287414551</v>
       </c>
       <c r="C547" s="2">
-        <v>0.89736634492874146</v>
+        <v>1.0558143854141235</v>
       </c>
       <c r="D547" s="2">
         <v>0.50878143310546875</v>
       </c>
       <c r="E547" s="2">
-        <v>0.32237100601196289</v>
+        <v>0.38729268312454224</v>
       </c>
     </row>
     <row r="548">
@@ -8545,13 +7109,13 @@
         <v>0.65015262365341187</v>
       </c>
       <c r="C548" s="2">
-        <v>0.54561936855316162</v>
+        <v>0.59945935010910034</v>
       </c>
       <c r="D548" s="2">
         <v>0.40871143341064453</v>
       </c>
       <c r="E548" s="2">
-        <v>0.24045996367931366</v>
+        <v>0.36225327849388123</v>
       </c>
     </row>
     <row r="549">
@@ -8562,13 +7126,13 @@
         <v>1.0604333877563477</v>
       </c>
       <c r="C549" s="2">
-        <v>0.97033411264419556</v>
+        <v>0.99411880970001221</v>
       </c>
       <c r="D549" s="2">
         <v>0.6099013090133667</v>
       </c>
       <c r="E549" s="2">
-        <v>0.47161823511123657</v>
+        <v>0.56880104541778564</v>
       </c>
     </row>
     <row r="550">
@@ -8579,13 +7143,13 @@
         <v>0.46565708518028259</v>
       </c>
       <c r="C550" s="2">
-        <v>0.25062629580497742</v>
+        <v>0.2651817798614502</v>
       </c>
       <c r="D550" s="2">
         <v>0.61072266101837158</v>
       </c>
       <c r="E550" s="2">
-        <v>0.45797127485275269</v>
+        <v>0.56460553407669067</v>
       </c>
     </row>
     <row r="551">
@@ -8596,13 +7160,13 @@
         <v>0.9896206259727478</v>
       </c>
       <c r="C551" s="2">
-        <v>0.87084341049194336</v>
+        <v>0.95733219385147095</v>
       </c>
       <c r="D551" s="2">
         <v>0.67664581537246704</v>
       </c>
       <c r="E551" s="2">
-        <v>0.52128565311431885</v>
+        <v>0.63670498132705688</v>
       </c>
     </row>
     <row r="552">
@@ -8613,13 +7177,13 @@
         <v>-0.26145666837692261</v>
       </c>
       <c r="C552" s="2">
-        <v>-0.37861409783363342</v>
+        <v>0.13835088908672333</v>
       </c>
       <c r="D552" s="2">
         <v>0.62712156772613525</v>
       </c>
       <c r="E552" s="2">
-        <v>0.44365587830543518</v>
+        <v>0.5474969744682312</v>
       </c>
     </row>
     <row r="553">
@@ -8630,13 +7194,13 @@
         <v>1.1606854200363159</v>
       </c>
       <c r="C553" s="2">
-        <v>1.1410433053970337</v>
+        <v>1.0451961755752563</v>
       </c>
       <c r="D553" s="2">
         <v>0.73670518398284912</v>
       </c>
       <c r="E553" s="2">
-        <v>0.51667612791061401</v>
+        <v>0.62088167667388916</v>
       </c>
     </row>
     <row r="554">
@@ -8647,13 +7211,13 @@
         <v>0.40099701285362244</v>
       </c>
       <c r="C554" s="2">
-        <v>0.19417108595371246</v>
+        <v>0.289131760597229</v>
       </c>
       <c r="D554" s="2">
-        <v>0.72065961360931396</v>
+        <v>0.73783719539642334</v>
       </c>
       <c r="E554" s="2">
-        <v>0.46250978112220764</v>
+        <v>0.58500486612319946</v>
       </c>
     </row>
     <row r="555">
@@ -8664,13 +7228,13 @@
         <v>0.5073779821395874</v>
       </c>
       <c r="C555" s="2">
-        <v>0.20018099248409271</v>
+        <v>0.3857593834400177</v>
       </c>
       <c r="D555" s="2">
-        <v>0.78016513586044312</v>
+        <v>0.80832421779632568</v>
       </c>
       <c r="E555" s="2">
-        <v>0.54175817966461182</v>
+        <v>0.67342299222946167</v>
       </c>
     </row>
     <row r="556">
@@ -8681,13 +7245,13 @@
         <v>0.67062681913375854</v>
       </c>
       <c r="C556" s="2">
-        <v>0.19869844615459442</v>
+        <v>0.25294250249862671</v>
       </c>
       <c r="D556" s="2">
-        <v>0.74473816156387329</v>
+        <v>0.77289730310440063</v>
       </c>
       <c r="E556" s="2">
-        <v>0.52492082118988037</v>
+        <v>0.64749783277511597</v>
       </c>
     </row>
     <row r="557">
@@ -8698,13 +7262,13 @@
         <v>1.6364049911499023</v>
       </c>
       <c r="C557" s="2">
-        <v>1.2028017044067383</v>
+        <v>1.259921669960022</v>
       </c>
       <c r="D557" s="2">
-        <v>0.86855810880661011</v>
+        <v>0.89671725034713745</v>
       </c>
       <c r="E557" s="2">
-        <v>0.65283960103988647</v>
+        <v>0.71905618906021118</v>
       </c>
     </row>
     <row r="558">
@@ -8712,16 +7276,16 @@
         <v>45413</v>
       </c>
       <c r="B558" s="2">
-        <v>0.91602325439453125</v>
+        <v>1.0706217288970947</v>
       </c>
       <c r="C558" s="2">
-        <v>0.48283687233924866</v>
+        <v>0.67122745513916016</v>
       </c>
       <c r="D558" s="2">
-        <v>0.86136281490325928</v>
+        <v>0.88952189683914185</v>
       </c>
       <c r="E558" s="2">
-        <v>0.63925498723983765</v>
+        <v>0.72184169292449951</v>
       </c>
     </row>
     <row r="559">
@@ -8729,16 +7293,16 @@
         <v>45444</v>
       </c>
       <c r="B559" s="2">
-        <v>1.0012067556381226</v>
+        <v>1.1000403165817261</v>
       </c>
       <c r="C559" s="2">
-        <v>0.96386206150054932</v>
+        <v>1.0609451532363892</v>
       </c>
       <c r="D559" s="2">
-        <v>0.84766191244125366</v>
+        <v>0.84554469585418701</v>
       </c>
       <c r="E559" s="2">
-        <v>0.63654786348342896</v>
+        <v>0.66733467578887939</v>
       </c>
     </row>
     <row r="560">
@@ -8749,13 +7313,13 @@
         <v>0.67077797651290894</v>
       </c>
       <c r="C560" s="2">
-        <v>0.7193070650100708</v>
+        <v>0.72400540113449097</v>
       </c>
       <c r="D560" s="2">
-        <v>0.76780879497528076</v>
+        <v>0.78410178422927856</v>
       </c>
       <c r="E560" s="2">
-        <v>0.55683737993240356</v>
+        <v>0.57700121402740479</v>
       </c>
     </row>
     <row r="561">
@@ -8766,13 +7330,13 @@
         <v>0.85292279720306396</v>
       </c>
       <c r="C561" s="2">
-        <v>0.77265483140945435</v>
+        <v>0.78237634897232056</v>
       </c>
       <c r="D561" s="2">
-        <v>0.64087635278701782</v>
+        <v>0.64541518688201904</v>
       </c>
       <c r="E561" s="2">
-        <v>0.47575703263282776</v>
+        <v>0.47567412257194519</v>
       </c>
     </row>
     <row r="562">
@@ -8783,13 +7347,13 @@
         <v>1.0959274768829346</v>
       </c>
       <c r="C562" s="2">
-        <v>1.0187817811965942</v>
+        <v>1.070265531539917</v>
       </c>
       <c r="D562" s="2">
-        <v>0.43983876705169678</v>
+        <v>0.45385727286338806</v>
       </c>
       <c r="E562" s="2">
-        <v>0.32432925701141357</v>
+        <v>0.35277450084686279</v>
       </c>
     </row>
     <row r="563">
@@ -8797,16 +7361,16 @@
         <v>45566</v>
       </c>
       <c r="B563" s="2">
-        <v>0.27768927812576294</v>
+        <v>0.0052023408934473991</v>
       </c>
       <c r="C563" s="2">
-        <v>0.16980695724487305</v>
+        <v>-0.20143130421638489</v>
       </c>
       <c r="D563" s="2">
-        <v>0.320068359375</v>
+        <v>0.30979079008102417</v>
       </c>
       <c r="E563" s="2">
-        <v>0.22883628308773041</v>
+        <v>0.23658673465251923</v>
       </c>
     </row>
     <row r="564">
@@ -8814,16 +7378,16 @@
         <v>45597</v>
       </c>
       <c r="B564" s="2">
-        <v>-0.21130028367042542</v>
+        <v>-0.045608449727296829</v>
       </c>
       <c r="C564" s="2">
-        <v>-0.51721334457397461</v>
+        <v>-0.42724204063415527</v>
       </c>
       <c r="D564" s="2">
-        <v>0.20257391035556793</v>
+        <v>0.18139353394508362</v>
       </c>
       <c r="E564" s="2">
-        <v>0.099664539098739624</v>
+        <v>0.095810882747173309</v>
       </c>
     </row>
     <row r="565">
@@ -8831,16 +7395,16 @@
         <v>45627</v>
       </c>
       <c r="B565" s="2">
-        <v>-0.47176510095596313</v>
+        <v>-0.57755255699157715</v>
       </c>
       <c r="C565" s="2">
-        <v>-0.5310247540473938</v>
+        <v>-0.65900117158889771</v>
       </c>
       <c r="D565" s="2">
-        <v>0.13608968257904053</v>
+        <v>0.11597128957509995</v>
       </c>
       <c r="E565" s="2">
-        <v>0.029982356354594231</v>
+        <v>0.02679799497127533</v>
       </c>
     </row>
     <row r="566">
@@ -8848,16 +7412,16 @@
         <v>45658</v>
       </c>
       <c r="B566" s="2">
-        <v>-0.17293313145637512</v>
+        <v>-0.087616100907325745</v>
       </c>
       <c r="C566" s="2">
-        <v>-0.16004827618598938</v>
+        <v>0.15382517874240875</v>
       </c>
       <c r="D566" s="2">
-        <v>0.046485543251037598</v>
+        <v>0.037812042981386185</v>
       </c>
       <c r="E566" s="2">
-        <v>-0.062851704657077789</v>
+        <v>-0.05022156611084938</v>
       </c>
     </row>
     <row r="567">
@@ -8865,16 +7429,16 @@
         <v>45689</v>
       </c>
       <c r="B567" s="2">
-        <v>-0.16191047430038452</v>
+        <v>-0.22597657144069672</v>
       </c>
       <c r="C567" s="2">
-        <v>-0.37659981846809387</v>
+        <v>-0.37446251511573792</v>
       </c>
       <c r="D567" s="2">
-        <v>-0.1034347340464592</v>
+        <v>-0.09706859290599823</v>
       </c>
       <c r="E567" s="2">
-        <v>-0.21737077832221985</v>
+        <v>-0.19709774851799011</v>
       </c>
     </row>
     <row r="568">
@@ -8882,16 +7446,16 @@
         <v>45717</v>
       </c>
       <c r="B568" s="2">
-        <v>-0.05624336376786232</v>
+        <v>-0.055535107851028442</v>
       </c>
       <c r="C568" s="2">
-        <v>-0.19868361949920654</v>
+        <v>-0.20603747665882111</v>
       </c>
       <c r="D568" s="2">
-        <v>-0.16695539653301239</v>
+        <v>-0.035144437104463577</v>
       </c>
       <c r="E568" s="2">
-        <v>-0.28190040588378906</v>
+        <v>-0.10333593189716339</v>
       </c>
     </row>
     <row r="569">
@@ -8899,17 +7463,145 @@
         <v>45748</v>
       </c>
       <c r="B569" s="2">
-        <v>0.07241995632648468</v>
+        <v>0.081977806985378265</v>
       </c>
       <c r="C569" s="2">
-        <v>0.092167451977729797</v>
+        <v>0.10288939625024796</v>
       </c>
       <c r="D569" s="2">
-        <v>-0.15808641910552979</v>
+        <v>-0.013501324690878391</v>
       </c>
       <c r="E569" s="2">
-        <v>-0.23483780026435852</v>
-      </c>
+        <v>-0.056583564728498459</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="1">
+        <v>45778</v>
+      </c>
+      <c r="B570" s="2">
+        <v>0.14948953688144684</v>
+      </c>
+      <c r="C570" s="2">
+        <v>0.089200310409069061</v>
+      </c>
+      <c r="D570" s="2">
+        <v>0.10448721796274185</v>
+      </c>
+      <c r="E570" s="2">
+        <v>0.098709657788276672</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" s="1">
+        <v>45809</v>
+      </c>
+      <c r="B571" s="2">
+        <v>-0.11799823492765427</v>
+      </c>
+      <c r="C571" s="2">
+        <v>-0.25162017345428467</v>
+      </c>
+      <c r="D571" s="2">
+        <v>0.20276598632335663</v>
+      </c>
+      <c r="E571" s="2">
+        <v>0.15576489269733429</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="1">
+        <v>45839</v>
+      </c>
+      <c r="B572" s="2">
+        <v>0.56251972913742065</v>
+      </c>
+      <c r="C572" s="2">
+        <v>0.64242511987686157</v>
+      </c>
+      <c r="D572" s="2">
+        <v>0.25320550799369812</v>
+      </c>
+      <c r="E572" s="2">
+        <v>0.21665087342262268</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="1">
+        <v>45870</v>
+      </c>
+      <c r="B573" s="2">
+        <v>0.14917957782745361</v>
+      </c>
+      <c r="C573" s="2">
+        <v>-0.006470751017332077</v>
+      </c>
+      <c r="D573" s="2">
+        <v>0.29179808497428894</v>
+      </c>
+      <c r="E573" s="2">
+        <v>0.2694869339466095</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="1">
+        <v>45901</v>
+      </c>
+      <c r="B574" s="2">
+        <v>0.48434430360794067</v>
+      </c>
+      <c r="C574" s="2">
+        <v>0.73863780498504639</v>
+      </c>
+      <c r="D574" s="2">
+        <v>0.32177239656448364</v>
+      </c>
+      <c r="E574" s="2">
+        <v>0.29328656196594238</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" s="1">
+        <v>45931</v>
+      </c>
+      <c r="B575" s="2">
+        <v>0.79689282178878784</v>
+      </c>
+      <c r="C575" s="2">
+        <v>0.66732227802276611</v>
+      </c>
+      <c r="D575" s="2">
+        <v>0.35048621892929077</v>
+      </c>
+      <c r="E575" s="2">
+        <v>0.32730093598365784</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" s="1">
+        <v>45962</v>
+      </c>
+      <c r="B576" s="2">
+        <v>0.22797907888889313</v>
+      </c>
+      <c r="C576" s="2">
+        <v>0.17351138591766357</v>
+      </c>
+      <c r="D576" s="2">
+        <v>0.4441831111907959</v>
+      </c>
+      <c r="E576" s="2">
+        <v>0.44308516383171082</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" s="1">
+        <v>45992</v>
+      </c>
+      <c r="B577" s="2"/>
+      <c r="C577" s="2"/>
+      <c r="D577" s="2"/>
+      <c r="E577" s="2"/>
     </row>
   </sheetData>
 </worksheet>
